--- a/research/traditional_assets/database/data/brazil/brazil_advertising.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_advertising.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bovespa_elmd3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,31 +590,31 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.002507788161993769</v>
+        <v>0.08584686774941995</v>
       </c>
       <c r="H2">
-        <v>-0.002507788161993769</v>
+        <v>0.08584686774941995</v>
       </c>
       <c r="I2">
-        <v>-0.09174454828660435</v>
+        <v>0.1121423047177107</v>
       </c>
       <c r="J2">
-        <v>-0.09174454828660435</v>
+        <v>0.05607115235885537</v>
       </c>
       <c r="K2">
-        <v>-6.96</v>
+        <v>-1.51</v>
       </c>
       <c r="L2">
-        <v>-0.108411214953271</v>
+        <v>-0.01167826759474091</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.007995578481945468</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-1.437086092715232</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,76 +626,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>2.17</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>106.8</v>
+        <v>25.4</v>
       </c>
       <c r="V2">
-        <v>0.4280561122244489</v>
+        <v>0.09358879882092852</v>
       </c>
       <c r="W2">
-        <v>-0.3149321266968326</v>
+        <v>-0.01091040462427746</v>
       </c>
       <c r="X2">
-        <v>0.1216896297574028</v>
+        <v>0.2094704380471345</v>
       </c>
       <c r="Y2">
-        <v>-0.4366217564542354</v>
+        <v>-0.2203808426714119</v>
       </c>
       <c r="Z2">
-        <v>1.524940617577196</v>
+        <v>2.105863192182411</v>
       </c>
       <c r="AA2">
-        <v>-0.1399049881235153</v>
+        <v>0.1180781758957655</v>
       </c>
       <c r="AB2">
-        <v>0.09594477472967615</v>
+        <v>0.1626023948213698</v>
       </c>
       <c r="AC2">
-        <v>-0.2358497628531915</v>
+        <v>-0.04452421892560433</v>
       </c>
       <c r="AD2">
-        <v>109.6</v>
+        <v>124.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>109.6</v>
+        <v>124.7</v>
       </c>
       <c r="AG2">
-        <v>2.799999999999997</v>
+        <v>99.30000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.3052074631021999</v>
+        <v>0.3148194900277708</v>
       </c>
       <c r="AI2">
-        <v>0.4419354838709677</v>
+        <v>0.4310404424472866</v>
       </c>
       <c r="AJ2">
-        <v>0.01109789932619896</v>
+        <v>0.2678715942810899</v>
       </c>
       <c r="AK2">
-        <v>0.01983002832861188</v>
+        <v>0.3762788935202729</v>
       </c>
       <c r="AL2">
-        <v>7.26</v>
+        <v>18</v>
       </c>
       <c r="AM2">
-        <v>3.87</v>
+        <v>11.21</v>
       </c>
       <c r="AN2">
-        <v>24.85260770975056</v>
+        <v>4.198653198653199</v>
       </c>
       <c r="AO2">
-        <v>-0.8112947658402203</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="AP2">
-        <v>0.6349206349206342</v>
+        <v>3.343434343434344</v>
       </c>
       <c r="AQ2">
-        <v>-1.521963824289406</v>
+        <v>1.293487957181088</v>
       </c>
     </row>
     <row r="3">
@@ -713,31 +718,31 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.002507788161993769</v>
+        <v>0.08584686774941995</v>
       </c>
       <c r="H3">
-        <v>-0.002507788161993769</v>
+        <v>0.08584686774941995</v>
       </c>
       <c r="I3">
-        <v>-0.09174454828660435</v>
+        <v>0.1121423047177107</v>
       </c>
       <c r="J3">
-        <v>-0.09174454828660435</v>
+        <v>0.05607115235885537</v>
       </c>
       <c r="K3">
-        <v>-6.96</v>
+        <v>-1.51</v>
       </c>
       <c r="L3">
-        <v>-0.108411214953271</v>
+        <v>-0.01167826759474091</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>2.17</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.007995578481945468</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-1.437086092715232</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -749,76 +754,8791 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>2.17</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>106.8</v>
+        <v>25.4</v>
       </c>
       <c r="V3">
-        <v>0.4280561122244489</v>
+        <v>0.09358879882092852</v>
       </c>
       <c r="W3">
-        <v>-0.3149321266968326</v>
+        <v>-0.01091040462427746</v>
       </c>
       <c r="X3">
-        <v>0.1216896297574028</v>
+        <v>0.2094704380471345</v>
       </c>
       <c r="Y3">
-        <v>-0.4366217564542354</v>
+        <v>-0.2203808426714119</v>
       </c>
       <c r="Z3">
-        <v>1.524940617577196</v>
+        <v>2.105863192182411</v>
       </c>
       <c r="AA3">
-        <v>-0.1399049881235153</v>
+        <v>0.1180781758957655</v>
       </c>
       <c r="AB3">
-        <v>0.09594477472967615</v>
+        <v>0.1626023948213698</v>
       </c>
       <c r="AC3">
-        <v>-0.2358497628531915</v>
+        <v>-0.04452421892560433</v>
       </c>
       <c r="AD3">
-        <v>109.6</v>
+        <v>124.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>109.6</v>
+        <v>124.7</v>
       </c>
       <c r="AG3">
-        <v>2.799999999999997</v>
+        <v>99.30000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.3052074631021999</v>
+        <v>0.3148194900277708</v>
       </c>
       <c r="AI3">
-        <v>0.4419354838709677</v>
+        <v>0.4310404424472866</v>
       </c>
       <c r="AJ3">
-        <v>0.01109789932619896</v>
+        <v>0.2678715942810899</v>
       </c>
       <c r="AK3">
-        <v>0.01983002832861188</v>
+        <v>0.3762788935202729</v>
       </c>
       <c r="AL3">
-        <v>7.26</v>
+        <v>18</v>
       </c>
       <c r="AM3">
-        <v>3.87</v>
+        <v>11.21</v>
       </c>
       <c r="AN3">
-        <v>24.85260770975056</v>
+        <v>4.198653198653199</v>
       </c>
       <c r="AO3">
-        <v>-0.8112947658402203</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="AP3">
-        <v>0.6349206349206342</v>
+        <v>3.343434343434344</v>
       </c>
       <c r="AQ3">
-        <v>-1.521963824289406</v>
+        <v>1.293487957181088</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Eletromidia S.A. (BOVESPA:ELMD3)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BOVESPA:ELMD3</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Advertising</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.314819490027771</v>
+      </c>
+      <c r="F2">
+        <v>0.16</v>
+      </c>
+      <c r="G2">
+        <v>271.4</v>
+      </c>
+      <c r="H2">
+        <v>331.304504988336</v>
+      </c>
+      <c r="I2">
+        <v>370.7</v>
+      </c>
+      <c r="J2">
+        <v>369.280504988336</v>
+      </c>
+      <c r="K2">
+        <v>124.7</v>
+      </c>
+      <c r="L2">
+        <v>63.376</v>
+      </c>
+      <c r="M2">
+        <v>0.16260239482137</v>
+      </c>
+      <c r="N2">
+        <v>0.163078284773607</v>
+      </c>
+      <c r="O2">
+        <v>0.0605976880733945</v>
+      </c>
+      <c r="P2">
+        <v>0.04158</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.209470438047134</v>
+      </c>
+      <c r="T2">
+        <v>0.186220815206675</v>
+      </c>
+      <c r="U2">
+        <v>1.5365458380909</v>
+      </c>
+      <c r="V2">
+        <v>1.32722949941234</v>
+      </c>
+      <c r="W2">
+        <v>3.631638635425558</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>271.4</v>
+      </c>
+      <c r="AB2">
+        <v>0.1110740947755822</v>
+      </c>
+      <c r="AC2">
+        <v>0.09181467889908257</v>
+      </c>
+      <c r="AD2">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>29.7</v>
+      </c>
+      <c r="AH2">
+        <v>15.2</v>
+      </c>
+      <c r="AI2">
+        <v>106.7</v>
+      </c>
+      <c r="AJ2">
+        <v>124.7</v>
+      </c>
+      <c r="AK2">
+        <v>124.7</v>
+      </c>
+      <c r="AL2">
+        <v>18</v>
+      </c>
+      <c r="AM2">
+        <v>124.7</v>
+      </c>
+      <c r="AN2">
+        <v>25.4</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1697575769602442</v>
+      </c>
+      <c r="C2">
+        <v>375.8459140551603</v>
+      </c>
+      <c r="D2">
+        <v>350.4459140551604</v>
+      </c>
+      <c r="E2">
+        <v>-124.7</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>25.4</v>
+      </c>
+      <c r="H2">
+        <v>271.4</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>29.7</v>
+      </c>
+      <c r="K2">
+        <v>15.2</v>
+      </c>
+      <c r="L2">
+        <v>14.5</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>14.5</v>
+      </c>
+      <c r="O2">
+        <v>4.930000000000001</v>
+      </c>
+      <c r="P2">
+        <v>9.569999999999999</v>
+      </c>
+      <c r="Q2">
+        <v>24.77</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1697575769602442</v>
+      </c>
+      <c r="T2">
+        <v>1.179010976635329</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="W2">
+        <v>0.030162</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1692259411985794</v>
+      </c>
+      <c r="C3">
+        <v>373.3133843328436</v>
+      </c>
+      <c r="D3">
+        <v>351.8743843328436</v>
+      </c>
+      <c r="E3">
+        <v>-120.739</v>
+      </c>
+      <c r="F3">
+        <v>3.961</v>
+      </c>
+      <c r="G3">
+        <v>25.4</v>
+      </c>
+      <c r="H3">
+        <v>271.4</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>29.7</v>
+      </c>
+      <c r="K3">
+        <v>15.2</v>
+      </c>
+      <c r="L3">
+        <v>14.5</v>
+      </c>
+      <c r="M3">
+        <v>0.1810177</v>
+      </c>
+      <c r="N3">
+        <v>14.3189823</v>
+      </c>
+      <c r="O3">
+        <v>4.868453982000001</v>
+      </c>
+      <c r="P3">
+        <v>9.450528318</v>
+      </c>
+      <c r="Q3">
+        <v>24.650528318</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1706306274733125</v>
+      </c>
+      <c r="T3">
+        <v>1.186871049812898</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="W3">
+        <v>0.030162</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>80.10266399363157</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1686943054369145</v>
+      </c>
+      <c r="C4">
+        <v>370.7925475924715</v>
+      </c>
+      <c r="D4">
+        <v>353.3145475924716</v>
+      </c>
+      <c r="E4">
+        <v>-116.778</v>
+      </c>
+      <c r="F4">
+        <v>7.922</v>
+      </c>
+      <c r="G4">
+        <v>25.4</v>
+      </c>
+      <c r="H4">
+        <v>271.4</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>29.7</v>
+      </c>
+      <c r="K4">
+        <v>15.2</v>
+      </c>
+      <c r="L4">
+        <v>14.5</v>
+      </c>
+      <c r="M4">
+        <v>0.3620354</v>
+      </c>
+      <c r="N4">
+        <v>14.1379646</v>
+      </c>
+      <c r="O4">
+        <v>4.806907964000001</v>
+      </c>
+      <c r="P4">
+        <v>9.331056636</v>
+      </c>
+      <c r="Q4">
+        <v>24.531056636</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1715214953437904</v>
+      </c>
+      <c r="T4">
+        <v>1.194891532647152</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="W4">
+        <v>0.030162</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>40.05133199681578</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1681626696752497</v>
+      </c>
+      <c r="C5">
+        <v>368.2835479963603</v>
+      </c>
+      <c r="D5">
+        <v>354.7665479963603</v>
+      </c>
+      <c r="E5">
+        <v>-112.817</v>
+      </c>
+      <c r="F5">
+        <v>11.883</v>
+      </c>
+      <c r="G5">
+        <v>25.4</v>
+      </c>
+      <c r="H5">
+        <v>271.4</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>29.7</v>
+      </c>
+      <c r="K5">
+        <v>15.2</v>
+      </c>
+      <c r="L5">
+        <v>14.5</v>
+      </c>
+      <c r="M5">
+        <v>0.5430531000000001</v>
+      </c>
+      <c r="N5">
+        <v>13.9569469</v>
+      </c>
+      <c r="O5">
+        <v>4.745361946000001</v>
+      </c>
+      <c r="P5">
+        <v>9.211584953999999</v>
+      </c>
+      <c r="Q5">
+        <v>24.411584954</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1724307316239688</v>
+      </c>
+      <c r="T5">
+        <v>1.203077386261493</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="W5">
+        <v>0.030162</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>26.70088799787719</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1676310339135849</v>
+      </c>
+      <c r="C6">
+        <v>365.7865320864341</v>
+      </c>
+      <c r="D6">
+        <v>356.2305320864341</v>
+      </c>
+      <c r="E6">
+        <v>-108.856</v>
+      </c>
+      <c r="F6">
+        <v>15.844</v>
+      </c>
+      <c r="G6">
+        <v>25.4</v>
+      </c>
+      <c r="H6">
+        <v>271.4</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>29.7</v>
+      </c>
+      <c r="K6">
+        <v>15.2</v>
+      </c>
+      <c r="L6">
+        <v>14.5</v>
+      </c>
+      <c r="M6">
+        <v>0.7240708</v>
+      </c>
+      <c r="N6">
+        <v>13.7759292</v>
+      </c>
+      <c r="O6">
+        <v>4.683815928000001</v>
+      </c>
+      <c r="P6">
+        <v>9.092113271999999</v>
+      </c>
+      <c r="Q6">
+        <v>24.292113272</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.173358910326651</v>
+      </c>
+      <c r="T6">
+        <v>1.211433778492801</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="W6">
+        <v>0.030162</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>20.02566599840789</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.16709939815192</v>
+      </c>
+      <c r="C7">
+        <v>363.3016488335275</v>
+      </c>
+      <c r="D7">
+        <v>357.7066488335275</v>
+      </c>
+      <c r="E7">
+        <v>-104.895</v>
+      </c>
+      <c r="F7">
+        <v>19.805</v>
+      </c>
+      <c r="G7">
+        <v>25.4</v>
+      </c>
+      <c r="H7">
+        <v>271.4</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>29.7</v>
+      </c>
+      <c r="K7">
+        <v>15.2</v>
+      </c>
+      <c r="L7">
+        <v>14.5</v>
+      </c>
+      <c r="M7">
+        <v>0.9050885000000001</v>
+      </c>
+      <c r="N7">
+        <v>13.5949115</v>
+      </c>
+      <c r="O7">
+        <v>4.622269910000001</v>
+      </c>
+      <c r="P7">
+        <v>8.972641589999999</v>
+      </c>
+      <c r="Q7">
+        <v>24.17264159</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1743066296336001</v>
+      </c>
+      <c r="T7">
+        <v>1.219966094771082</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="W7">
+        <v>0.030162</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>16.02053279872631</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1665677623902552</v>
+      </c>
+      <c r="C8">
+        <v>360.8290496879177</v>
+      </c>
+      <c r="D8">
+        <v>359.1950496879177</v>
+      </c>
+      <c r="E8">
+        <v>-100.934</v>
+      </c>
+      <c r="F8">
+        <v>23.766</v>
+      </c>
+      <c r="G8">
+        <v>25.4</v>
+      </c>
+      <c r="H8">
+        <v>271.4</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>29.7</v>
+      </c>
+      <c r="K8">
+        <v>15.2</v>
+      </c>
+      <c r="L8">
+        <v>14.5</v>
+      </c>
+      <c r="M8">
+        <v>1.0861062</v>
+      </c>
+      <c r="N8">
+        <v>13.4138938</v>
+      </c>
+      <c r="O8">
+        <v>4.560723892000001</v>
+      </c>
+      <c r="P8">
+        <v>8.853169907999998</v>
+      </c>
+      <c r="Q8">
+        <v>24.053169908</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1752745131811226</v>
+      </c>
+      <c r="T8">
+        <v>1.228679949693583</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="W8">
+        <v>0.030162</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>13.35044399893859</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1661100466285904</v>
+      </c>
+      <c r="C9">
+        <v>358.1594578690315</v>
+      </c>
+      <c r="D9">
+        <v>360.4864578690315</v>
+      </c>
+      <c r="E9">
+        <v>-96.973</v>
+      </c>
+      <c r="F9">
+        <v>27.727</v>
+      </c>
+      <c r="G9">
+        <v>25.4</v>
+      </c>
+      <c r="H9">
+        <v>271.4</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>29.7</v>
+      </c>
+      <c r="K9">
+        <v>15.2</v>
+      </c>
+      <c r="L9">
+        <v>14.5</v>
+      </c>
+      <c r="M9">
+        <v>1.3114871</v>
+      </c>
+      <c r="N9">
+        <v>13.1885129</v>
+      </c>
+      <c r="O9">
+        <v>4.484094386000001</v>
+      </c>
+      <c r="P9">
+        <v>8.704418513999999</v>
+      </c>
+      <c r="Q9">
+        <v>23.904418514</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1762632114285919</v>
+      </c>
+      <c r="T9">
+        <v>1.2375811993456</v>
+      </c>
+      <c r="U9">
+        <v>0.0473</v>
+      </c>
+      <c r="V9">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="W9">
+        <v>0.031218</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>11.05615144823003</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1657896108669256</v>
+      </c>
+      <c r="C10">
+        <v>355.1080815138993</v>
+      </c>
+      <c r="D10">
+        <v>361.3960815138993</v>
+      </c>
+      <c r="E10">
+        <v>-93.012</v>
+      </c>
+      <c r="F10">
+        <v>31.688</v>
+      </c>
+      <c r="G10">
+        <v>25.4</v>
+      </c>
+      <c r="H10">
+        <v>271.4</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>29.7</v>
+      </c>
+      <c r="K10">
+        <v>15.2</v>
+      </c>
+      <c r="L10">
+        <v>14.5</v>
+      </c>
+      <c r="M10">
+        <v>1.6192568</v>
+      </c>
+      <c r="N10">
+        <v>12.8807432</v>
+      </c>
+      <c r="O10">
+        <v>4.379452688000001</v>
+      </c>
+      <c r="P10">
+        <v>8.501290511999999</v>
+      </c>
+      <c r="Q10">
+        <v>23.701290512</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1772734031162234</v>
+      </c>
+      <c r="T10">
+        <v>1.246675954424835</v>
+      </c>
+      <c r="U10">
+        <v>0.0511</v>
+      </c>
+      <c r="V10">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="W10">
+        <v>0.033726</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>8.954725402419184</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1652936151052607</v>
+      </c>
+      <c r="C11">
+        <v>352.564156396011</v>
+      </c>
+      <c r="D11">
+        <v>362.813156396011</v>
+      </c>
+      <c r="E11">
+        <v>-89.05100000000002</v>
+      </c>
+      <c r="F11">
+        <v>35.64899999999999</v>
+      </c>
+      <c r="G11">
+        <v>25.4</v>
+      </c>
+      <c r="H11">
+        <v>271.4</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>29.7</v>
+      </c>
+      <c r="K11">
+        <v>15.2</v>
+      </c>
+      <c r="L11">
+        <v>14.5</v>
+      </c>
+      <c r="M11">
+        <v>1.8216639</v>
+      </c>
+      <c r="N11">
+        <v>12.6783361</v>
+      </c>
+      <c r="O11">
+        <v>4.310634274000002</v>
+      </c>
+      <c r="P11">
+        <v>8.367701825999999</v>
+      </c>
+      <c r="Q11">
+        <v>23.567701826</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1783057968189679</v>
+      </c>
+      <c r="T11">
+        <v>1.255970594231085</v>
+      </c>
+      <c r="U11">
+        <v>0.0511</v>
+      </c>
+      <c r="V11">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="W11">
+        <v>0.033726</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>7.959755913261499</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1649230193435959</v>
+      </c>
+      <c r="C12">
+        <v>349.6692347275985</v>
+      </c>
+      <c r="D12">
+        <v>363.8792347275985</v>
+      </c>
+      <c r="E12">
+        <v>-85.09</v>
+      </c>
+      <c r="F12">
+        <v>39.61</v>
+      </c>
+      <c r="G12">
+        <v>25.4</v>
+      </c>
+      <c r="H12">
+        <v>271.4</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>29.7</v>
+      </c>
+      <c r="K12">
+        <v>15.2</v>
+      </c>
+      <c r="L12">
+        <v>14.5</v>
+      </c>
+      <c r="M12">
+        <v>2.09933</v>
+      </c>
+      <c r="N12">
+        <v>12.40067</v>
+      </c>
+      <c r="O12">
+        <v>4.216227800000001</v>
+      </c>
+      <c r="P12">
+        <v>8.184442199999999</v>
+      </c>
+      <c r="Q12">
+        <v>23.3844422</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1793611326039954</v>
+      </c>
+      <c r="T12">
+        <v>1.265471781588586</v>
+      </c>
+      <c r="U12">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V12">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="W12">
+        <v>0.03498</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>6.906965555677287</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1644395635819311</v>
+      </c>
+      <c r="C13">
+        <v>347.1084267337139</v>
+      </c>
+      <c r="D13">
+        <v>365.279426733714</v>
+      </c>
+      <c r="E13">
+        <v>-81.129</v>
+      </c>
+      <c r="F13">
+        <v>43.571</v>
+      </c>
+      <c r="G13">
+        <v>25.4</v>
+      </c>
+      <c r="H13">
+        <v>271.4</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>29.7</v>
+      </c>
+      <c r="K13">
+        <v>15.2</v>
+      </c>
+      <c r="L13">
+        <v>14.5</v>
+      </c>
+      <c r="M13">
+        <v>2.309263</v>
+      </c>
+      <c r="N13">
+        <v>12.190737</v>
+      </c>
+      <c r="O13">
+        <v>4.144850580000001</v>
+      </c>
+      <c r="P13">
+        <v>8.045886419999999</v>
+      </c>
+      <c r="Q13">
+        <v>23.24588642</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1804401837999225</v>
+      </c>
+      <c r="T13">
+        <v>1.275186478774345</v>
+      </c>
+      <c r="U13">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V13">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="W13">
+        <v>0.03498</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>6.279059596070262</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1641145078202663</v>
+      </c>
+      <c r="C14">
+        <v>344.0949322088798</v>
+      </c>
+      <c r="D14">
+        <v>366.2269322088798</v>
+      </c>
+      <c r="E14">
+        <v>-77.16800000000001</v>
+      </c>
+      <c r="F14">
+        <v>47.532</v>
+      </c>
+      <c r="G14">
+        <v>25.4</v>
+      </c>
+      <c r="H14">
+        <v>271.4</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>29.7</v>
+      </c>
+      <c r="K14">
+        <v>15.2</v>
+      </c>
+      <c r="L14">
+        <v>14.5</v>
+      </c>
+      <c r="M14">
+        <v>2.61426</v>
+      </c>
+      <c r="N14">
+        <v>11.88574</v>
+      </c>
+      <c r="O14">
+        <v>4.041151600000001</v>
+      </c>
+      <c r="P14">
+        <v>7.844588399999999</v>
+      </c>
+      <c r="Q14">
+        <v>23.0445884</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1815437588866662</v>
+      </c>
+      <c r="T14">
+        <v>1.285121964532509</v>
+      </c>
+      <c r="U14">
+        <v>0.055</v>
+      </c>
+      <c r="V14">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="W14">
+        <v>0.0363</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>5.546502643195398</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1636442520586014</v>
+      </c>
+      <c r="C15">
+        <v>341.5134136195836</v>
+      </c>
+      <c r="D15">
+        <v>367.6064136195836</v>
+      </c>
+      <c r="E15">
+        <v>-73.20700000000001</v>
+      </c>
+      <c r="F15">
+        <v>51.49299999999999</v>
+      </c>
+      <c r="G15">
+        <v>25.4</v>
+      </c>
+      <c r="H15">
+        <v>271.4</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>29.7</v>
+      </c>
+      <c r="K15">
+        <v>15.2</v>
+      </c>
+      <c r="L15">
+        <v>14.5</v>
+      </c>
+      <c r="M15">
+        <v>2.832115</v>
+      </c>
+      <c r="N15">
+        <v>11.667885</v>
+      </c>
+      <c r="O15">
+        <v>3.967080900000001</v>
+      </c>
+      <c r="P15">
+        <v>7.700804099999999</v>
+      </c>
+      <c r="Q15">
+        <v>22.9008041</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1826727035156338</v>
+      </c>
+      <c r="T15">
+        <v>1.295285852262124</v>
+      </c>
+      <c r="U15">
+        <v>0.055</v>
+      </c>
+      <c r="V15">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="W15">
+        <v>0.0363</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>5.119848593718829</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1631739962969366</v>
+      </c>
+      <c r="C16">
+        <v>338.9423266172881</v>
+      </c>
+      <c r="D16">
+        <v>368.9963266172881</v>
+      </c>
+      <c r="E16">
+        <v>-69.24600000000001</v>
+      </c>
+      <c r="F16">
+        <v>55.454</v>
+      </c>
+      <c r="G16">
+        <v>25.4</v>
+      </c>
+      <c r="H16">
+        <v>271.4</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>29.7</v>
+      </c>
+      <c r="K16">
+        <v>15.2</v>
+      </c>
+      <c r="L16">
+        <v>14.5</v>
+      </c>
+      <c r="M16">
+        <v>3.04997</v>
+      </c>
+      <c r="N16">
+        <v>11.45003</v>
+      </c>
+      <c r="O16">
+        <v>3.893010200000001</v>
+      </c>
+      <c r="P16">
+        <v>7.557019799999999</v>
+      </c>
+      <c r="Q16">
+        <v>22.7570198</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1838279026708565</v>
+      </c>
+      <c r="T16">
+        <v>1.305686109473822</v>
+      </c>
+      <c r="U16">
+        <v>0.055</v>
+      </c>
+      <c r="V16">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="W16">
+        <v>0.0363</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>4.754145122738912</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1630799405352718</v>
+      </c>
+      <c r="C17">
+        <v>335.2605851235445</v>
+      </c>
+      <c r="D17">
+        <v>369.2755851235445</v>
+      </c>
+      <c r="E17">
+        <v>-65.28500000000001</v>
+      </c>
+      <c r="F17">
+        <v>59.41499999999999</v>
+      </c>
+      <c r="G17">
+        <v>25.4</v>
+      </c>
+      <c r="H17">
+        <v>271.4</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>29.7</v>
+      </c>
+      <c r="K17">
+        <v>15.2</v>
+      </c>
+      <c r="L17">
+        <v>14.5</v>
+      </c>
+      <c r="M17">
+        <v>3.493602</v>
+      </c>
+      <c r="N17">
+        <v>11.006398</v>
+      </c>
+      <c r="O17">
+        <v>3.742175320000001</v>
+      </c>
+      <c r="P17">
+        <v>7.26422268</v>
+      </c>
+      <c r="Q17">
+        <v>22.46422268</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1850102829826727</v>
+      </c>
+      <c r="T17">
+        <v>1.316331078619914</v>
+      </c>
+      <c r="U17">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V17">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="W17">
+        <v>0.038808</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>4.150444154772067</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1630782847736069</v>
+      </c>
+      <c r="C18">
+        <v>331.304504988336</v>
+      </c>
+      <c r="D18">
+        <v>369.280504988336</v>
+      </c>
+      <c r="E18">
+        <v>-61.32400000000001</v>
+      </c>
+      <c r="F18">
+        <v>63.376</v>
+      </c>
+      <c r="G18">
+        <v>25.4</v>
+      </c>
+      <c r="H18">
+        <v>271.4</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>29.7</v>
+      </c>
+      <c r="K18">
+        <v>15.2</v>
+      </c>
+      <c r="L18">
+        <v>14.5</v>
+      </c>
+      <c r="M18">
+        <v>3.992688</v>
+      </c>
+      <c r="N18">
+        <v>10.507312</v>
+      </c>
+      <c r="O18">
+        <v>3.572486080000001</v>
+      </c>
+      <c r="P18">
+        <v>6.93482592</v>
+      </c>
+      <c r="Q18">
+        <v>22.13482592</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1862208152066749</v>
+      </c>
+      <c r="T18">
+        <v>1.327229499412342</v>
+      </c>
+      <c r="U18">
+        <v>0.063</v>
+      </c>
+      <c r="V18">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="W18">
+        <v>0.04157999999999999</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>3.631638635425558</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1634574490119421</v>
+      </c>
+      <c r="C19">
+        <v>326.2202832112521</v>
+      </c>
+      <c r="D19">
+        <v>368.1572832112521</v>
+      </c>
+      <c r="E19">
+        <v>-57.363</v>
+      </c>
+      <c r="F19">
+        <v>67.337</v>
+      </c>
+      <c r="G19">
+        <v>25.4</v>
+      </c>
+      <c r="H19">
+        <v>271.4</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>29.7</v>
+      </c>
+      <c r="K19">
+        <v>15.2</v>
+      </c>
+      <c r="L19">
+        <v>14.5</v>
+      </c>
+      <c r="M19">
+        <v>4.7203237</v>
+      </c>
+      <c r="N19">
+        <v>9.7796763</v>
+      </c>
+      <c r="O19">
+        <v>3.325089942000001</v>
+      </c>
+      <c r="P19">
+        <v>6.454586357999999</v>
+      </c>
+      <c r="Q19">
+        <v>21.654586358</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1874605168818579</v>
+      </c>
+      <c r="T19">
+        <v>1.338390532753984</v>
+      </c>
+      <c r="U19">
+        <v>0.0701</v>
+      </c>
+      <c r="V19">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="W19">
+        <v>0.04626599999999999</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>3.071823231105951</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1656172932502773</v>
+      </c>
+      <c r="C20">
+        <v>315.9891416038636</v>
+      </c>
+      <c r="D20">
+        <v>361.8871416038636</v>
+      </c>
+      <c r="E20">
+        <v>-53.40200000000002</v>
+      </c>
+      <c r="F20">
+        <v>71.29799999999999</v>
+      </c>
+      <c r="G20">
+        <v>25.4</v>
+      </c>
+      <c r="H20">
+        <v>271.4</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>29.7</v>
+      </c>
+      <c r="K20">
+        <v>15.2</v>
+      </c>
+      <c r="L20">
+        <v>14.5</v>
+      </c>
+      <c r="M20">
+        <v>6.5166372</v>
+      </c>
+      <c r="N20">
+        <v>7.9833628</v>
+      </c>
+      <c r="O20">
+        <v>2.714343352000001</v>
+      </c>
+      <c r="P20">
+        <v>5.269019448</v>
+      </c>
+      <c r="Q20">
+        <v>20.469019448</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.188730455183265</v>
+      </c>
+      <c r="T20">
+        <v>1.349823786421033</v>
+      </c>
+      <c r="U20">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V20">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="W20">
+        <v>0.060324</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>2.225073999823099</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1653872774886125</v>
+      </c>
+      <c r="C21">
+        <v>312.6857096325322</v>
+      </c>
+      <c r="D21">
+        <v>362.5447096325323</v>
+      </c>
+      <c r="E21">
+        <v>-49.441</v>
+      </c>
+      <c r="F21">
+        <v>75.259</v>
+      </c>
+      <c r="G21">
+        <v>25.4</v>
+      </c>
+      <c r="H21">
+        <v>271.4</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>29.7</v>
+      </c>
+      <c r="K21">
+        <v>15.2</v>
+      </c>
+      <c r="L21">
+        <v>14.5</v>
+      </c>
+      <c r="M21">
+        <v>6.878672600000001</v>
+      </c>
+      <c r="N21">
+        <v>7.621327399999999</v>
+      </c>
+      <c r="O21">
+        <v>2.591251316000001</v>
+      </c>
+      <c r="P21">
+        <v>5.030076083999999</v>
+      </c>
+      <c r="Q21">
+        <v>20.230076084</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1900317499859413</v>
+      </c>
+      <c r="T21">
+        <v>1.361539342647761</v>
+      </c>
+      <c r="U21">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V21">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="W21">
+        <v>0.060324</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>2.107964841937672</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1651572617269476</v>
+      </c>
+      <c r="C22">
+        <v>309.3846716828645</v>
+      </c>
+      <c r="D22">
+        <v>363.2046716828645</v>
+      </c>
+      <c r="E22">
+        <v>-45.48</v>
+      </c>
+      <c r="F22">
+        <v>79.22</v>
+      </c>
+      <c r="G22">
+        <v>25.4</v>
+      </c>
+      <c r="H22">
+        <v>271.4</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>29.7</v>
+      </c>
+      <c r="K22">
+        <v>15.2</v>
+      </c>
+      <c r="L22">
+        <v>14.5</v>
+      </c>
+      <c r="M22">
+        <v>7.240708000000001</v>
+      </c>
+      <c r="N22">
+        <v>7.259291999999999</v>
+      </c>
+      <c r="O22">
+        <v>2.468159280000001</v>
+      </c>
+      <c r="P22">
+        <v>4.791132719999998</v>
+      </c>
+      <c r="Q22">
+        <v>19.99113272</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1913655771586845</v>
+      </c>
+      <c r="T22">
+        <v>1.373547787780158</v>
+      </c>
+      <c r="U22">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V22">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="W22">
+        <v>0.060324</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>2.002566599840789</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1678517059652828</v>
+      </c>
+      <c r="C23">
+        <v>297.8403954477128</v>
+      </c>
+      <c r="D23">
+        <v>355.6213954477128</v>
+      </c>
+      <c r="E23">
+        <v>-41.51900000000002</v>
+      </c>
+      <c r="F23">
+        <v>83.18099999999998</v>
+      </c>
+      <c r="G23">
+        <v>25.4</v>
+      </c>
+      <c r="H23">
+        <v>271.4</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>29.7</v>
+      </c>
+      <c r="K23">
+        <v>15.2</v>
+      </c>
+      <c r="L23">
+        <v>14.5</v>
+      </c>
+      <c r="M23">
+        <v>9.357862499999998</v>
+      </c>
+      <c r="N23">
+        <v>5.142137500000002</v>
+      </c>
+      <c r="O23">
+        <v>1.748326750000001</v>
+      </c>
+      <c r="P23">
+        <v>3.393810750000001</v>
+      </c>
+      <c r="Q23">
+        <v>18.59381075</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1927331721079529</v>
+      </c>
+      <c r="T23">
+        <v>1.38586024418173</v>
+      </c>
+      <c r="U23">
+        <v>0.1125</v>
+      </c>
+      <c r="V23">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="W23">
+        <v>0.07425</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>1.549499151114905</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1837365633253456</v>
+      </c>
+      <c r="C24">
+        <v>254.9037566491519</v>
+      </c>
+      <c r="D24">
+        <v>316.6457566491519</v>
+      </c>
+      <c r="E24">
+        <v>-37.55800000000001</v>
+      </c>
+      <c r="F24">
+        <v>87.142</v>
+      </c>
+      <c r="G24">
+        <v>25.4</v>
+      </c>
+      <c r="H24">
+        <v>271.4</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>29.7</v>
+      </c>
+      <c r="K24">
+        <v>15.2</v>
+      </c>
+      <c r="L24">
+        <v>14.5</v>
+      </c>
+      <c r="M24">
+        <v>17.1321172</v>
+      </c>
+      <c r="N24">
+        <v>-2.6321172</v>
+      </c>
+      <c r="O24">
+        <v>-0.8949198480000001</v>
+      </c>
+      <c r="P24">
+        <v>-1.737197351999999</v>
+      </c>
+      <c r="Q24">
+        <v>13.462802648</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1960652759700975</v>
+      </c>
+      <c r="T24">
+        <v>1.415859172994762</v>
+      </c>
+      <c r="U24">
+        <v>0.1966</v>
+      </c>
+      <c r="V24">
+        <v>0.2877636162797206</v>
+      </c>
+      <c r="W24">
+        <v>0.1400256730394069</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.8463635772932957</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1853145633253456</v>
+      </c>
+      <c r="C25">
+        <v>247.5323993942023</v>
+      </c>
+      <c r="D25">
+        <v>313.2353993942023</v>
+      </c>
+      <c r="E25">
+        <v>-33.59700000000001</v>
+      </c>
+      <c r="F25">
+        <v>91.10299999999999</v>
+      </c>
+      <c r="G25">
+        <v>25.4</v>
+      </c>
+      <c r="H25">
+        <v>271.4</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>29.7</v>
+      </c>
+      <c r="K25">
+        <v>15.2</v>
+      </c>
+      <c r="L25">
+        <v>14.5</v>
+      </c>
+      <c r="M25">
+        <v>17.9108498</v>
+      </c>
+      <c r="N25">
+        <v>-3.410849799999998</v>
+      </c>
+      <c r="O25">
+        <v>-1.159688931999999</v>
+      </c>
+      <c r="P25">
+        <v>-2.251160867999998</v>
+      </c>
+      <c r="Q25">
+        <v>12.948839132</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1981076821515274</v>
+      </c>
+      <c r="T25">
+        <v>1.434246954462226</v>
+      </c>
+      <c r="U25">
+        <v>0.1966</v>
+      </c>
+      <c r="V25">
+        <v>0.2752521547023415</v>
+      </c>
+      <c r="W25">
+        <v>0.1424854263855197</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.8095651608892395</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.191687538916091</v>
+      </c>
+      <c r="C26">
+        <v>230.5144716115383</v>
+      </c>
+      <c r="D26">
+        <v>300.1784716115383</v>
+      </c>
+      <c r="E26">
+        <v>-29.63600000000001</v>
+      </c>
+      <c r="F26">
+        <v>95.06399999999999</v>
+      </c>
+      <c r="G26">
+        <v>25.4</v>
+      </c>
+      <c r="H26">
+        <v>271.4</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>29.7</v>
+      </c>
+      <c r="K26">
+        <v>15.2</v>
+      </c>
+      <c r="L26">
+        <v>14.5</v>
+      </c>
+      <c r="M26">
+        <v>20.3246832</v>
+      </c>
+      <c r="N26">
+        <v>-5.824683199999999</v>
+      </c>
+      <c r="O26">
+        <v>-1.980392288</v>
+      </c>
+      <c r="P26">
+        <v>-3.844290911999999</v>
+      </c>
+      <c r="Q26">
+        <v>11.355709088</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.2010814353255546</v>
+      </c>
+      <c r="T26">
+        <v>1.461019652272958</v>
+      </c>
+      <c r="U26">
+        <v>0.2138</v>
+      </c>
+      <c r="V26">
+        <v>0.2425622063324462</v>
+      </c>
+      <c r="W26">
+        <v>0.161940200286123</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.7134182539189591</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1934375389160911</v>
+      </c>
+      <c r="C27">
+        <v>223.156415961259</v>
+      </c>
+      <c r="D27">
+        <v>296.781415961259</v>
+      </c>
+      <c r="E27">
+        <v>-25.67500000000001</v>
+      </c>
+      <c r="F27">
+        <v>99.02499999999999</v>
+      </c>
+      <c r="G27">
+        <v>25.4</v>
+      </c>
+      <c r="H27">
+        <v>271.4</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>29.7</v>
+      </c>
+      <c r="K27">
+        <v>15.2</v>
+      </c>
+      <c r="L27">
+        <v>14.5</v>
+      </c>
+      <c r="M27">
+        <v>21.171545</v>
+      </c>
+      <c r="N27">
+        <v>-6.671544999999998</v>
+      </c>
+      <c r="O27">
+        <v>-2.2683253</v>
+      </c>
+      <c r="P27">
+        <v>-4.403219699999998</v>
+      </c>
+      <c r="Q27">
+        <v>10.7967803</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.203245187796562</v>
+      </c>
+      <c r="T27">
+        <v>1.480499914303264</v>
+      </c>
+      <c r="U27">
+        <v>0.2138</v>
+      </c>
+      <c r="V27">
+        <v>0.2328597180791483</v>
+      </c>
+      <c r="W27">
+        <v>0.1640145922746781</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.6848815237622007</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.195187538916091</v>
+      </c>
+      <c r="C28">
+        <v>215.8743874347415</v>
+      </c>
+      <c r="D28">
+        <v>293.4603874347415</v>
+      </c>
+      <c r="E28">
+        <v>-21.71400000000001</v>
+      </c>
+      <c r="F28">
+        <v>102.986</v>
+      </c>
+      <c r="G28">
+        <v>25.4</v>
+      </c>
+      <c r="H28">
+        <v>271.4</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>29.7</v>
+      </c>
+      <c r="K28">
+        <v>15.2</v>
+      </c>
+      <c r="L28">
+        <v>14.5</v>
+      </c>
+      <c r="M28">
+        <v>22.0184068</v>
+      </c>
+      <c r="N28">
+        <v>-7.518406799999998</v>
+      </c>
+      <c r="O28">
+        <v>-2.556258312</v>
+      </c>
+      <c r="P28">
+        <v>-4.962148487999998</v>
+      </c>
+      <c r="Q28">
+        <v>10.237851512</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.2054674200640831</v>
+      </c>
+      <c r="T28">
+        <v>1.500506669901957</v>
+      </c>
+      <c r="U28">
+        <v>0.2138</v>
+      </c>
+      <c r="V28">
+        <v>0.2239035750761041</v>
+      </c>
+      <c r="W28">
+        <v>0.1659294156487289</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.6585399266944237</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1969375389160911</v>
+      </c>
+      <c r="C29">
+        <v>208.6658620114243</v>
+      </c>
+      <c r="D29">
+        <v>290.2128620114244</v>
+      </c>
+      <c r="E29">
+        <v>-17.753</v>
+      </c>
+      <c r="F29">
+        <v>106.947</v>
+      </c>
+      <c r="G29">
+        <v>25.4</v>
+      </c>
+      <c r="H29">
+        <v>271.4</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>29.7</v>
+      </c>
+      <c r="K29">
+        <v>15.2</v>
+      </c>
+      <c r="L29">
+        <v>14.5</v>
+      </c>
+      <c r="M29">
+        <v>22.8652686</v>
+      </c>
+      <c r="N29">
+        <v>-8.3652686</v>
+      </c>
+      <c r="O29">
+        <v>-2.844191324000001</v>
+      </c>
+      <c r="P29">
+        <v>-5.521077276</v>
+      </c>
+      <c r="Q29">
+        <v>9.678922724</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.2077505354074267</v>
+      </c>
+      <c r="T29">
+        <v>1.521061555791025</v>
+      </c>
+      <c r="U29">
+        <v>0.2138</v>
+      </c>
+      <c r="V29">
+        <v>0.2156108500732854</v>
+      </c>
+      <c r="W29">
+        <v>0.1677024002543316</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.6341495590390747</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.198687538916091</v>
+      </c>
+      <c r="C30">
+        <v>201.5284261743169</v>
+      </c>
+      <c r="D30">
+        <v>287.0364261743169</v>
+      </c>
+      <c r="E30">
+        <v>-13.792</v>
+      </c>
+      <c r="F30">
+        <v>110.908</v>
+      </c>
+      <c r="G30">
+        <v>25.4</v>
+      </c>
+      <c r="H30">
+        <v>271.4</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>29.7</v>
+      </c>
+      <c r="K30">
+        <v>15.2</v>
+      </c>
+      <c r="L30">
+        <v>14.5</v>
+      </c>
+      <c r="M30">
+        <v>23.7121304</v>
+      </c>
+      <c r="N30">
+        <v>-9.212130399999999</v>
+      </c>
+      <c r="O30">
+        <v>-3.132124336</v>
+      </c>
+      <c r="P30">
+        <v>-6.080006063999999</v>
+      </c>
+      <c r="Q30">
+        <v>9.119993936</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.2100970706214188</v>
+      </c>
+      <c r="T30">
+        <v>1.542187410732567</v>
+      </c>
+      <c r="U30">
+        <v>0.2138</v>
+      </c>
+      <c r="V30">
+        <v>0.2079104625706681</v>
+      </c>
+      <c r="W30">
+        <v>0.1693487431023911</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.6115013605019648</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.200437538916091</v>
+      </c>
+      <c r="C31">
+        <v>194.4597709280575</v>
+      </c>
+      <c r="D31">
+        <v>283.9287709280575</v>
+      </c>
+      <c r="E31">
+        <v>-9.831000000000017</v>
+      </c>
+      <c r="F31">
+        <v>114.869</v>
+      </c>
+      <c r="G31">
+        <v>25.4</v>
+      </c>
+      <c r="H31">
+        <v>271.4</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>29.7</v>
+      </c>
+      <c r="K31">
+        <v>15.2</v>
+      </c>
+      <c r="L31">
+        <v>14.5</v>
+      </c>
+      <c r="M31">
+        <v>24.5589922</v>
+      </c>
+      <c r="N31">
+        <v>-10.0589922</v>
+      </c>
+      <c r="O31">
+        <v>-3.420057347999999</v>
+      </c>
+      <c r="P31">
+        <v>-6.638934851999997</v>
+      </c>
+      <c r="Q31">
+        <v>8.561065148000003</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.2125097054189035</v>
+      </c>
+      <c r="T31">
+        <v>1.563908360179504</v>
+      </c>
+      <c r="U31">
+        <v>0.2138</v>
+      </c>
+      <c r="V31">
+        <v>0.2007411362751279</v>
+      </c>
+      <c r="W31">
+        <v>0.1708815450643776</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.5904151066915524</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.202187538916091</v>
+      </c>
+      <c r="C32">
+        <v>187.4576862013986</v>
+      </c>
+      <c r="D32">
+        <v>280.8876862013987</v>
+      </c>
+      <c r="E32">
+        <v>-5.870000000000019</v>
+      </c>
+      <c r="F32">
+        <v>118.83</v>
+      </c>
+      <c r="G32">
+        <v>25.4</v>
+      </c>
+      <c r="H32">
+        <v>271.4</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>29.7</v>
+      </c>
+      <c r="K32">
+        <v>15.2</v>
+      </c>
+      <c r="L32">
+        <v>14.5</v>
+      </c>
+      <c r="M32">
+        <v>25.40585399999999</v>
+      </c>
+      <c r="N32">
+        <v>-10.90585399999999</v>
+      </c>
+      <c r="O32">
+        <v>-3.707990359999999</v>
+      </c>
+      <c r="P32">
+        <v>-7.197863639999996</v>
+      </c>
+      <c r="Q32">
+        <v>8.002136360000003</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.2149912726391736</v>
+      </c>
+      <c r="T32">
+        <v>1.586249908182069</v>
+      </c>
+      <c r="U32">
+        <v>0.2138</v>
+      </c>
+      <c r="V32">
+        <v>0.1940497650659569</v>
+      </c>
+      <c r="W32">
+        <v>0.1723121602288984</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.5707346031351673</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.203937538916091</v>
+      </c>
+      <c r="C33">
+        <v>180.5200556056005</v>
+      </c>
+      <c r="D33">
+        <v>277.9110556056006</v>
+      </c>
+      <c r="E33">
+        <v>-1.90900000000002</v>
+      </c>
+      <c r="F33">
+        <v>122.791</v>
+      </c>
+      <c r="G33">
+        <v>25.4</v>
+      </c>
+      <c r="H33">
+        <v>271.4</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>29.7</v>
+      </c>
+      <c r="K33">
+        <v>15.2</v>
+      </c>
+      <c r="L33">
+        <v>14.5</v>
+      </c>
+      <c r="M33">
+        <v>26.25271579999999</v>
+      </c>
+      <c r="N33">
+        <v>-11.75271579999999</v>
+      </c>
+      <c r="O33">
+        <v>-3.995923371999999</v>
+      </c>
+      <c r="P33">
+        <v>-7.756792427999995</v>
+      </c>
+      <c r="Q33">
+        <v>7.443207572000004</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.2175447693440891</v>
+      </c>
+      <c r="T33">
+        <v>1.609239037286156</v>
+      </c>
+      <c r="U33">
+        <v>0.2138</v>
+      </c>
+      <c r="V33">
+        <v>0.1877900952251196</v>
+      </c>
+      <c r="W33">
+        <v>0.1736504776408694</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.5523238094856457</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.205687538916091</v>
+      </c>
+      <c r="C34">
+        <v>173.6448515226082</v>
+      </c>
+      <c r="D34">
+        <v>274.9968515226082</v>
+      </c>
+      <c r="E34">
+        <v>2.051999999999992</v>
+      </c>
+      <c r="F34">
+        <v>126.752</v>
+      </c>
+      <c r="G34">
+        <v>25.4</v>
+      </c>
+      <c r="H34">
+        <v>271.4</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>29.7</v>
+      </c>
+      <c r="K34">
+        <v>15.2</v>
+      </c>
+      <c r="L34">
+        <v>14.5</v>
+      </c>
+      <c r="M34">
+        <v>27.0995776</v>
+      </c>
+      <c r="N34">
+        <v>-12.5995776</v>
+      </c>
+      <c r="O34">
+        <v>-4.283856384</v>
+      </c>
+      <c r="P34">
+        <v>-8.315721215999996</v>
+      </c>
+      <c r="Q34">
+        <v>6.884278784000003</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.2201733688932669</v>
+      </c>
+      <c r="T34">
+        <v>1.632904317246247</v>
+      </c>
+      <c r="U34">
+        <v>0.2138</v>
+      </c>
+      <c r="V34">
+        <v>0.1819216547493346</v>
+      </c>
+      <c r="W34">
+        <v>0.1749051502145922</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.5350636904392193</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.207437538916091</v>
+      </c>
+      <c r="C35">
+        <v>166.8301304990583</v>
+      </c>
+      <c r="D35">
+        <v>272.1431304990583</v>
+      </c>
+      <c r="E35">
+        <v>6.012999999999991</v>
+      </c>
+      <c r="F35">
+        <v>130.713</v>
+      </c>
+      <c r="G35">
+        <v>25.4</v>
+      </c>
+      <c r="H35">
+        <v>271.4</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>29.7</v>
+      </c>
+      <c r="K35">
+        <v>15.2</v>
+      </c>
+      <c r="L35">
+        <v>14.5</v>
+      </c>
+      <c r="M35">
+        <v>27.9464394</v>
+      </c>
+      <c r="N35">
+        <v>-13.4464394</v>
+      </c>
+      <c r="O35">
+        <v>-4.571789396000001</v>
+      </c>
+      <c r="P35">
+        <v>-8.874650003999999</v>
+      </c>
+      <c r="Q35">
+        <v>6.325349996</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2228804341006291</v>
+      </c>
+      <c r="T35">
+        <v>1.657276023473803</v>
+      </c>
+      <c r="U35">
+        <v>0.2138</v>
+      </c>
+      <c r="V35">
+        <v>0.1764088773326881</v>
+      </c>
+      <c r="W35">
+        <v>0.1760837820262713</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.5188496392137883</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.209187538916091</v>
+      </c>
+      <c r="C36">
+        <v>160.0740289241251</v>
+      </c>
+      <c r="D36">
+        <v>269.3480289241252</v>
+      </c>
+      <c r="E36">
+        <v>9.974000000000004</v>
+      </c>
+      <c r="F36">
+        <v>134.674</v>
+      </c>
+      <c r="G36">
+        <v>25.4</v>
+      </c>
+      <c r="H36">
+        <v>271.4</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>29.7</v>
+      </c>
+      <c r="K36">
+        <v>15.2</v>
+      </c>
+      <c r="L36">
+        <v>14.5</v>
+      </c>
+      <c r="M36">
+        <v>28.7933012</v>
+      </c>
+      <c r="N36">
+        <v>-14.2933012</v>
+      </c>
+      <c r="O36">
+        <v>-4.859722408000001</v>
+      </c>
+      <c r="P36">
+        <v>-9.433578791999999</v>
+      </c>
+      <c r="Q36">
+        <v>5.766421208000001</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.2256695315870023</v>
+      </c>
+      <c r="T36">
+        <v>1.682386266253709</v>
+      </c>
+      <c r="U36">
+        <v>0.2138</v>
+      </c>
+      <c r="V36">
+        <v>0.1712203809405502</v>
+      </c>
+      <c r="W36">
+        <v>0.1771930825549103</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.5035893557075005</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.220485663509142</v>
+      </c>
+      <c r="C37">
+        <v>139.3636193620199</v>
+      </c>
+      <c r="D37">
+        <v>252.5986193620199</v>
+      </c>
+      <c r="E37">
+        <v>13.93499999999999</v>
+      </c>
+      <c r="F37">
+        <v>138.635</v>
+      </c>
+      <c r="G37">
+        <v>25.4</v>
+      </c>
+      <c r="H37">
+        <v>271.4</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>29.7</v>
+      </c>
+      <c r="K37">
+        <v>15.2</v>
+      </c>
+      <c r="L37">
+        <v>14.5</v>
+      </c>
+      <c r="M37">
+        <v>33.106038</v>
+      </c>
+      <c r="N37">
+        <v>-18.606038</v>
+      </c>
+      <c r="O37">
+        <v>-6.32605292</v>
+      </c>
+      <c r="P37">
+        <v>-12.27998508</v>
+      </c>
+      <c r="Q37">
+        <v>2.920014920000002</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.2297723314468807</v>
+      </c>
+      <c r="T37">
+        <v>1.719323770612109</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.1489154334928269</v>
+      </c>
+      <c r="W37">
+        <v>0.203238994481913</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.4379865690965498</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.222485663509142</v>
+      </c>
+      <c r="C38">
+        <v>132.6522836576828</v>
+      </c>
+      <c r="D38">
+        <v>249.8482836576828</v>
+      </c>
+      <c r="E38">
+        <v>17.89599999999997</v>
+      </c>
+      <c r="F38">
+        <v>142.596</v>
+      </c>
+      <c r="G38">
+        <v>25.4</v>
+      </c>
+      <c r="H38">
+        <v>271.4</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>29.7</v>
+      </c>
+      <c r="K38">
+        <v>15.2</v>
+      </c>
+      <c r="L38">
+        <v>14.5</v>
+      </c>
+      <c r="M38">
+        <v>34.05192479999999</v>
+      </c>
+      <c r="N38">
+        <v>-19.55192479999999</v>
+      </c>
+      <c r="O38">
+        <v>-6.647654432</v>
+      </c>
+      <c r="P38">
+        <v>-12.904270368</v>
+      </c>
+      <c r="Q38">
+        <v>2.295729632000004</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.2327562741257382</v>
+      </c>
+      <c r="T38">
+        <v>1.746188204527923</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.1447788936735818</v>
+      </c>
+      <c r="W38">
+        <v>0.2042268001907487</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.4258202755105345</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.224485663509142</v>
+      </c>
+      <c r="C39">
+        <v>126.0001950842736</v>
+      </c>
+      <c r="D39">
+        <v>247.1571950842736</v>
+      </c>
+      <c r="E39">
+        <v>21.85699999999999</v>
+      </c>
+      <c r="F39">
+        <v>146.557</v>
+      </c>
+      <c r="G39">
+        <v>25.4</v>
+      </c>
+      <c r="H39">
+        <v>271.4</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>29.7</v>
+      </c>
+      <c r="K39">
+        <v>15.2</v>
+      </c>
+      <c r="L39">
+        <v>14.5</v>
+      </c>
+      <c r="M39">
+        <v>34.9978116</v>
+      </c>
+      <c r="N39">
+        <v>-20.4978116</v>
+      </c>
+      <c r="O39">
+        <v>-6.969255944000001</v>
+      </c>
+      <c r="P39">
+        <v>-13.528555656</v>
+      </c>
+      <c r="Q39">
+        <v>1.671444344000001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.2358349451436071</v>
+      </c>
+      <c r="T39">
+        <v>1.773905477615668</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.1408659506013228</v>
+      </c>
+      <c r="W39">
+        <v>0.2051612109964041</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.4143116194156551</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.226485663509142</v>
+      </c>
+      <c r="C40">
+        <v>119.4054596090839</v>
+      </c>
+      <c r="D40">
+        <v>244.5234596090839</v>
+      </c>
+      <c r="E40">
+        <v>25.818</v>
+      </c>
+      <c r="F40">
+        <v>150.518</v>
+      </c>
+      <c r="G40">
+        <v>25.4</v>
+      </c>
+      <c r="H40">
+        <v>271.4</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>29.7</v>
+      </c>
+      <c r="K40">
+        <v>15.2</v>
+      </c>
+      <c r="L40">
+        <v>14.5</v>
+      </c>
+      <c r="M40">
+        <v>35.9436984</v>
+      </c>
+      <c r="N40">
+        <v>-21.4436984</v>
+      </c>
+      <c r="O40">
+        <v>-7.290857456000002</v>
+      </c>
+      <c r="P40">
+        <v>-14.152840944</v>
+      </c>
+      <c r="Q40">
+        <v>1.047159055999998</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.2390129281297943</v>
+      </c>
+      <c r="T40">
+        <v>1.802516856286889</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.137158951901288</v>
+      </c>
+      <c r="W40">
+        <v>0.2060464422859725</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.4034086820626115</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.228485663509142</v>
+      </c>
+      <c r="C41">
+        <v>112.8662630803061</v>
+      </c>
+      <c r="D41">
+        <v>241.9452630803061</v>
+      </c>
+      <c r="E41">
+        <v>29.77899999999998</v>
+      </c>
+      <c r="F41">
+        <v>154.479</v>
+      </c>
+      <c r="G41">
+        <v>25.4</v>
+      </c>
+      <c r="H41">
+        <v>271.4</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>29.7</v>
+      </c>
+      <c r="K41">
+        <v>15.2</v>
+      </c>
+      <c r="L41">
+        <v>14.5</v>
+      </c>
+      <c r="M41">
+        <v>36.8895852</v>
+      </c>
+      <c r="N41">
+        <v>-22.3895852</v>
+      </c>
+      <c r="O41">
+        <v>-7.612458968000001</v>
+      </c>
+      <c r="P41">
+        <v>-14.777126232</v>
+      </c>
+      <c r="Q41">
+        <v>0.4228737680000023</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2422951072794631</v>
+      </c>
+      <c r="T41">
+        <v>1.83206631294733</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.1336420556986908</v>
+      </c>
+      <c r="W41">
+        <v>0.2068862770991526</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.3930648697020318</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.230485663509142</v>
+      </c>
+      <c r="C42">
+        <v>106.3808670597476</v>
+      </c>
+      <c r="D42">
+        <v>239.4208670597476</v>
+      </c>
+      <c r="E42">
+        <v>33.73999999999999</v>
+      </c>
+      <c r="F42">
+        <v>158.44</v>
+      </c>
+      <c r="G42">
+        <v>25.4</v>
+      </c>
+      <c r="H42">
+        <v>271.4</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>29.7</v>
+      </c>
+      <c r="K42">
+        <v>15.2</v>
+      </c>
+      <c r="L42">
+        <v>14.5</v>
+      </c>
+      <c r="M42">
+        <v>37.835472</v>
+      </c>
+      <c r="N42">
+        <v>-23.335472</v>
+      </c>
+      <c r="O42">
+        <v>-7.934060480000003</v>
+      </c>
+      <c r="P42">
+        <v>-15.40141152</v>
+      </c>
+      <c r="Q42">
+        <v>-0.2014115200000006</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.2456866924007874</v>
+      </c>
+      <c r="T42">
+        <v>1.862600751496452</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.1303010043062236</v>
+      </c>
+      <c r="W42">
+        <v>0.2076841201716738</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.3832382479594809</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.232485663509142</v>
+      </c>
+      <c r="C43">
+        <v>99.94760491373233</v>
+      </c>
+      <c r="D43">
+        <v>236.9486049137324</v>
+      </c>
+      <c r="E43">
+        <v>37.70100000000001</v>
+      </c>
+      <c r="F43">
+        <v>162.401</v>
+      </c>
+      <c r="G43">
+        <v>25.4</v>
+      </c>
+      <c r="H43">
+        <v>271.4</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>29.7</v>
+      </c>
+      <c r="K43">
+        <v>15.2</v>
+      </c>
+      <c r="L43">
+        <v>14.5</v>
+      </c>
+      <c r="M43">
+        <v>38.78135880000001</v>
+      </c>
+      <c r="N43">
+        <v>-24.28135880000001</v>
+      </c>
+      <c r="O43">
+        <v>-8.255661992000004</v>
+      </c>
+      <c r="P43">
+        <v>-16.025696808</v>
+      </c>
+      <c r="Q43">
+        <v>-0.8256968080000036</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2491932465092754</v>
+      </c>
+      <c r="T43">
+        <v>1.894170255759103</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.127122931030462</v>
+      </c>
+      <c r="W43">
+        <v>0.2084430440699257</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.3738909736190058</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.234485663509142</v>
+      </c>
+      <c r="C44">
+        <v>93.56487814372127</v>
+      </c>
+      <c r="D44">
+        <v>234.5268781437212</v>
+      </c>
+      <c r="E44">
+        <v>41.66199999999996</v>
+      </c>
+      <c r="F44">
+        <v>166.362</v>
+      </c>
+      <c r="G44">
+        <v>25.4</v>
+      </c>
+      <c r="H44">
+        <v>271.4</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>29.7</v>
+      </c>
+      <c r="K44">
+        <v>15.2</v>
+      </c>
+      <c r="L44">
+        <v>14.5</v>
+      </c>
+      <c r="M44">
+        <v>39.7272456</v>
+      </c>
+      <c r="N44">
+        <v>-25.2272456</v>
+      </c>
+      <c r="O44">
+        <v>-8.577263504000001</v>
+      </c>
+      <c r="P44">
+        <v>-16.649982096</v>
+      </c>
+      <c r="Q44">
+        <v>-1.449982095999996</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2528207162766767</v>
+      </c>
+      <c r="T44">
+        <v>1.926828363617019</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.1240961945773558</v>
+      </c>
+      <c r="W44">
+        <v>0.2091658287349275</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.3649888075804582</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.236485663509142</v>
+      </c>
+      <c r="C45">
+        <v>87.23115293967152</v>
+      </c>
+      <c r="D45">
+        <v>232.1541529396715</v>
+      </c>
+      <c r="E45">
+        <v>45.62299999999998</v>
+      </c>
+      <c r="F45">
+        <v>170.323</v>
+      </c>
+      <c r="G45">
+        <v>25.4</v>
+      </c>
+      <c r="H45">
+        <v>271.4</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>29.7</v>
+      </c>
+      <c r="K45">
+        <v>15.2</v>
+      </c>
+      <c r="L45">
+        <v>14.5</v>
+      </c>
+      <c r="M45">
+        <v>40.6731324</v>
+      </c>
+      <c r="N45">
+        <v>-26.1731324</v>
+      </c>
+      <c r="O45">
+        <v>-8.898865016000002</v>
+      </c>
+      <c r="P45">
+        <v>-17.274267384</v>
+      </c>
+      <c r="Q45">
+        <v>-2.074267383999999</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2565754656850394</v>
+      </c>
+      <c r="T45">
+        <v>1.960632369996265</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.1212102365639289</v>
+      </c>
+      <c r="W45">
+        <v>0.2098549955085338</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.3565006957762614</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.238485663509142</v>
+      </c>
+      <c r="C46">
+        <v>80.94495694052011</v>
+      </c>
+      <c r="D46">
+        <v>229.8289569405201</v>
+      </c>
+      <c r="E46">
+        <v>49.58399999999999</v>
+      </c>
+      <c r="F46">
+        <v>174.284</v>
+      </c>
+      <c r="G46">
+        <v>25.4</v>
+      </c>
+      <c r="H46">
+        <v>271.4</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>29.7</v>
+      </c>
+      <c r="K46">
+        <v>15.2</v>
+      </c>
+      <c r="L46">
+        <v>14.5</v>
+      </c>
+      <c r="M46">
+        <v>41.6190192</v>
+      </c>
+      <c r="N46">
+        <v>-27.1190192</v>
+      </c>
+      <c r="O46">
+        <v>-9.220466528000001</v>
+      </c>
+      <c r="P46">
+        <v>-17.89855267199999</v>
+      </c>
+      <c r="Q46">
+        <v>-2.698552671999995</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.260464313286558</v>
+      </c>
+      <c r="T46">
+        <v>1.995643662317627</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.1184554584602033</v>
+      </c>
+      <c r="W46">
+        <v>0.2105128365197035</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.3483984072358919</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.240485663509142</v>
+      </c>
+      <c r="C47">
+        <v>74.70487618741444</v>
+      </c>
+      <c r="D47">
+        <v>227.5498761874144</v>
+      </c>
+      <c r="E47">
+        <v>53.54499999999997</v>
+      </c>
+      <c r="F47">
+        <v>178.245</v>
+      </c>
+      <c r="G47">
+        <v>25.4</v>
+      </c>
+      <c r="H47">
+        <v>271.4</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>29.7</v>
+      </c>
+      <c r="K47">
+        <v>15.2</v>
+      </c>
+      <c r="L47">
+        <v>14.5</v>
+      </c>
+      <c r="M47">
+        <v>42.56490599999999</v>
+      </c>
+      <c r="N47">
+        <v>-28.06490599999999</v>
+      </c>
+      <c r="O47">
+        <v>-9.54206804</v>
+      </c>
+      <c r="P47">
+        <v>-18.52283795999999</v>
+      </c>
+      <c r="Q47">
+        <v>-3.322837959999994</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2644945735281318</v>
+      </c>
+      <c r="T47">
+        <v>2.031928092541583</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.1158231149388654</v>
+      </c>
+      <c r="W47">
+        <v>0.2111414401525989</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.3406562204084276</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.242485663509142</v>
+      </c>
+      <c r="C48">
+        <v>68.50955225644029</v>
+      </c>
+      <c r="D48">
+        <v>225.3155522564403</v>
+      </c>
+      <c r="E48">
+        <v>57.50599999999999</v>
+      </c>
+      <c r="F48">
+        <v>182.206</v>
+      </c>
+      <c r="G48">
+        <v>25.4</v>
+      </c>
+      <c r="H48">
+        <v>271.4</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>29.7</v>
+      </c>
+      <c r="K48">
+        <v>15.2</v>
+      </c>
+      <c r="L48">
+        <v>14.5</v>
+      </c>
+      <c r="M48">
+        <v>43.5107928</v>
+      </c>
+      <c r="N48">
+        <v>-29.0107928</v>
+      </c>
+      <c r="O48">
+        <v>-9.863669552000001</v>
+      </c>
+      <c r="P48">
+        <v>-19.147123248</v>
+      </c>
+      <c r="Q48">
+        <v>-3.947123247999997</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2686741026675415</v>
+      </c>
+      <c r="T48">
+        <v>2.069556390551613</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.1133052211358466</v>
+      </c>
+      <c r="W48">
+        <v>0.2117427131927598</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.3332506503995487</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.244485663509142</v>
+      </c>
+      <c r="C49">
+        <v>62.35767955863139</v>
+      </c>
+      <c r="D49">
+        <v>223.1246795586314</v>
+      </c>
+      <c r="E49">
+        <v>61.467</v>
+      </c>
+      <c r="F49">
+        <v>186.167</v>
+      </c>
+      <c r="G49">
+        <v>25.4</v>
+      </c>
+      <c r="H49">
+        <v>271.4</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>29.7</v>
+      </c>
+      <c r="K49">
+        <v>15.2</v>
+      </c>
+      <c r="L49">
+        <v>14.5</v>
+      </c>
+      <c r="M49">
+        <v>44.4566796</v>
+      </c>
+      <c r="N49">
+        <v>-29.9566796</v>
+      </c>
+      <c r="O49">
+        <v>-10.185271064</v>
+      </c>
+      <c r="P49">
+        <v>-19.771408536</v>
+      </c>
+      <c r="Q49">
+        <v>-4.571408536</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2730113498876839</v>
+      </c>
+      <c r="T49">
+        <v>2.108604624335606</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.1108944717499775</v>
+      </c>
+      <c r="W49">
+        <v>0.2123184001461054</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.3261602110293456</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.246485663509142</v>
+      </c>
+      <c r="C50">
+        <v>56.24800279598318</v>
+      </c>
+      <c r="D50">
+        <v>220.9760027959832</v>
+      </c>
+      <c r="E50">
+        <v>65.42799999999998</v>
+      </c>
+      <c r="F50">
+        <v>190.128</v>
+      </c>
+      <c r="G50">
+        <v>25.4</v>
+      </c>
+      <c r="H50">
+        <v>271.4</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>29.7</v>
+      </c>
+      <c r="K50">
+        <v>15.2</v>
+      </c>
+      <c r="L50">
+        <v>14.5</v>
+      </c>
+      <c r="M50">
+        <v>45.4025664</v>
+      </c>
+      <c r="N50">
+        <v>-30.9025664</v>
+      </c>
+      <c r="O50">
+        <v>-10.506872576</v>
+      </c>
+      <c r="P50">
+        <v>-20.395693824</v>
+      </c>
+      <c r="Q50">
+        <v>-5.195693823999999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2775154143086009</v>
+      </c>
+      <c r="T50">
+        <v>2.149154713265137</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.1085841702551863</v>
+      </c>
+      <c r="W50">
+        <v>0.2128701001430615</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.3193652066329008</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.248485663509142</v>
+      </c>
+      <c r="C51">
+        <v>50.17931456305504</v>
+      </c>
+      <c r="D51">
+        <v>218.868314563055</v>
+      </c>
+      <c r="E51">
+        <v>69.38899999999997</v>
+      </c>
+      <c r="F51">
+        <v>194.089</v>
+      </c>
+      <c r="G51">
+        <v>25.4</v>
+      </c>
+      <c r="H51">
+        <v>271.4</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>29.7</v>
+      </c>
+      <c r="K51">
+        <v>15.2</v>
+      </c>
+      <c r="L51">
+        <v>14.5</v>
+      </c>
+      <c r="M51">
+        <v>46.34845319999999</v>
+      </c>
+      <c r="N51">
+        <v>-31.84845319999999</v>
+      </c>
+      <c r="O51">
+        <v>-10.828474088</v>
+      </c>
+      <c r="P51">
+        <v>-21.01997911199999</v>
+      </c>
+      <c r="Q51">
+        <v>-5.819979111999995</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2821961087068087</v>
+      </c>
+      <c r="T51">
+        <v>2.191295001760531</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.1063681667805907</v>
+      </c>
+      <c r="W51">
+        <v>0.213399281772795</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.3128475493546784</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.250485663509142</v>
+      </c>
+      <c r="C52">
+        <v>44.15045308453219</v>
+      </c>
+      <c r="D52">
+        <v>216.8004530845322</v>
+      </c>
+      <c r="E52">
+        <v>73.34999999999998</v>
+      </c>
+      <c r="F52">
+        <v>198.05</v>
+      </c>
+      <c r="G52">
+        <v>25.4</v>
+      </c>
+      <c r="H52">
+        <v>271.4</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>29.7</v>
+      </c>
+      <c r="K52">
+        <v>15.2</v>
+      </c>
+      <c r="L52">
+        <v>14.5</v>
+      </c>
+      <c r="M52">
+        <v>47.29434</v>
+      </c>
+      <c r="N52">
+        <v>-32.79434</v>
+      </c>
+      <c r="O52">
+        <v>-11.1500756</v>
+      </c>
+      <c r="P52">
+        <v>-21.6442644</v>
+      </c>
+      <c r="Q52">
+        <v>-6.444264399999998</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2870640308809449</v>
+      </c>
+      <c r="T52">
+        <v>2.235120901795742</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.1042408034449789</v>
+      </c>
+      <c r="W52">
+        <v>0.2139072961373391</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.3065905983675848</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.252485663509142</v>
+      </c>
+      <c r="C53">
+        <v>38.16030007984071</v>
+      </c>
+      <c r="D53">
+        <v>214.7713000798407</v>
+      </c>
+      <c r="E53">
+        <v>77.31099999999999</v>
+      </c>
+      <c r="F53">
+        <v>202.011</v>
+      </c>
+      <c r="G53">
+        <v>25.4</v>
+      </c>
+      <c r="H53">
+        <v>271.4</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>29.7</v>
+      </c>
+      <c r="K53">
+        <v>15.2</v>
+      </c>
+      <c r="L53">
+        <v>14.5</v>
+      </c>
+      <c r="M53">
+        <v>48.2402268</v>
+      </c>
+      <c r="N53">
+        <v>-33.7402268</v>
+      </c>
+      <c r="O53">
+        <v>-11.471677112</v>
+      </c>
+      <c r="P53">
+        <v>-22.268549688</v>
+      </c>
+      <c r="Q53">
+        <v>-7.068549688000001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2921306437560662</v>
+      </c>
+      <c r="T53">
+        <v>2.280735614077288</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.1021968661225283</v>
+      </c>
+      <c r="W53">
+        <v>0.2143953883699402</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.300579018007436</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.254485663509142</v>
+      </c>
+      <c r="C54">
+        <v>32.20777874656724</v>
+      </c>
+      <c r="D54">
+        <v>212.7797787465672</v>
+      </c>
+      <c r="E54">
+        <v>81.27199999999998</v>
+      </c>
+      <c r="F54">
+        <v>205.972</v>
+      </c>
+      <c r="G54">
+        <v>25.4</v>
+      </c>
+      <c r="H54">
+        <v>271.4</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>29.7</v>
+      </c>
+      <c r="K54">
+        <v>15.2</v>
+      </c>
+      <c r="L54">
+        <v>14.5</v>
+      </c>
+      <c r="M54">
+        <v>49.1861136</v>
+      </c>
+      <c r="N54">
+        <v>-34.6861136</v>
+      </c>
+      <c r="O54">
+        <v>-11.793278624</v>
+      </c>
+      <c r="P54">
+        <v>-22.892834976</v>
+      </c>
+      <c r="Q54">
+        <v>-7.692834975999997</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2974083655009843</v>
+      </c>
+      <c r="T54">
+        <v>2.328250939370565</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.1002315417740181</v>
+      </c>
+      <c r="W54">
+        <v>0.2148647078243645</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.2947986522765238</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.256485663509142</v>
+      </c>
+      <c r="C55">
+        <v>26.29185185504383</v>
+      </c>
+      <c r="D55">
+        <v>210.8248518550438</v>
+      </c>
+      <c r="E55">
+        <v>85.23299999999999</v>
+      </c>
+      <c r="F55">
+        <v>209.933</v>
+      </c>
+      <c r="G55">
+        <v>25.4</v>
+      </c>
+      <c r="H55">
+        <v>271.4</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>29.7</v>
+      </c>
+      <c r="K55">
+        <v>15.2</v>
+      </c>
+      <c r="L55">
+        <v>14.5</v>
+      </c>
+      <c r="M55">
+        <v>50.1320004</v>
+      </c>
+      <c r="N55">
+        <v>-35.6320004</v>
+      </c>
+      <c r="O55">
+        <v>-12.114880136</v>
+      </c>
+      <c r="P55">
+        <v>-23.517120264</v>
+      </c>
+      <c r="Q55">
+        <v>-8.317120264</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.3029106711499415</v>
+      </c>
+      <c r="T55">
+        <v>2.377788193399726</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.09834038060847061</v>
+      </c>
+      <c r="W55">
+        <v>0.2153163171106972</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.2892364135543253</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.258485663509142</v>
+      </c>
+      <c r="C56">
+        <v>20.41151994701272</v>
+      </c>
+      <c r="D56">
+        <v>208.9055199470127</v>
+      </c>
+      <c r="E56">
+        <v>89.194</v>
+      </c>
+      <c r="F56">
+        <v>213.894</v>
+      </c>
+      <c r="G56">
+        <v>25.4</v>
+      </c>
+      <c r="H56">
+        <v>271.4</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>29.7</v>
+      </c>
+      <c r="K56">
+        <v>15.2</v>
+      </c>
+      <c r="L56">
+        <v>14.5</v>
+      </c>
+      <c r="M56">
+        <v>51.07788720000001</v>
+      </c>
+      <c r="N56">
+        <v>-36.57788720000001</v>
+      </c>
+      <c r="O56">
+        <v>-12.436481648</v>
+      </c>
+      <c r="P56">
+        <v>-24.141405552</v>
+      </c>
+      <c r="Q56">
+        <v>-8.941405552000003</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.3086522074792881</v>
+      </c>
+      <c r="T56">
+        <v>2.429479241082329</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.09651926244905447</v>
+      </c>
+      <c r="W56">
+        <v>0.2157512001271658</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.2838801836736896</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.260485663509142</v>
+      </c>
+      <c r="C57">
+        <v>14.56581963179912</v>
+      </c>
+      <c r="D57">
+        <v>207.0208196317991</v>
+      </c>
+      <c r="E57">
+        <v>93.15499999999999</v>
+      </c>
+      <c r="F57">
+        <v>217.855</v>
+      </c>
+      <c r="G57">
+        <v>25.4</v>
+      </c>
+      <c r="H57">
+        <v>271.4</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>29.7</v>
+      </c>
+      <c r="K57">
+        <v>15.2</v>
+      </c>
+      <c r="L57">
+        <v>14.5</v>
+      </c>
+      <c r="M57">
+        <v>52.023774</v>
+      </c>
+      <c r="N57">
+        <v>-37.523774</v>
+      </c>
+      <c r="O57">
+        <v>-12.75808316</v>
+      </c>
+      <c r="P57">
+        <v>-24.76569084</v>
+      </c>
+      <c r="Q57">
+        <v>-9.565690839999998</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.3146489232010499</v>
+      </c>
+      <c r="T57">
+        <v>2.483467668661936</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.09476436676816259</v>
+      </c>
+      <c r="W57">
+        <v>0.2161702692157628</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.2787187257887134</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.262485663509142</v>
+      </c>
+      <c r="C58">
+        <v>8.753821973888506</v>
+      </c>
+      <c r="D58">
+        <v>205.1698219738885</v>
+      </c>
+      <c r="E58">
+        <v>97.116</v>
+      </c>
+      <c r="F58">
+        <v>221.816</v>
+      </c>
+      <c r="G58">
+        <v>25.4</v>
+      </c>
+      <c r="H58">
+        <v>271.4</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>29.7</v>
+      </c>
+      <c r="K58">
+        <v>15.2</v>
+      </c>
+      <c r="L58">
+        <v>14.5</v>
+      </c>
+      <c r="M58">
+        <v>52.9696608</v>
+      </c>
+      <c r="N58">
+        <v>-38.4696608</v>
+      </c>
+      <c r="O58">
+        <v>-13.079684672</v>
+      </c>
+      <c r="P58">
+        <v>-25.389976128</v>
+      </c>
+      <c r="Q58">
+        <v>-10.189976128</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.3209182169101647</v>
+      </c>
+      <c r="T58">
+        <v>2.539910115676979</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.09307214593301683</v>
+      </c>
+      <c r="W58">
+        <v>0.2165743715511956</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.2737416056853436</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.264485663509142</v>
+      </c>
+      <c r="C59">
+        <v>2.97463096623872</v>
+      </c>
+      <c r="D59">
+        <v>203.3516309662387</v>
+      </c>
+      <c r="E59">
+        <v>101.077</v>
+      </c>
+      <c r="F59">
+        <v>225.777</v>
+      </c>
+      <c r="G59">
+        <v>25.4</v>
+      </c>
+      <c r="H59">
+        <v>271.4</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>29.7</v>
+      </c>
+      <c r="K59">
+        <v>15.2</v>
+      </c>
+      <c r="L59">
+        <v>14.5</v>
+      </c>
+      <c r="M59">
+        <v>53.9155476</v>
+      </c>
+      <c r="N59">
+        <v>-39.4155476</v>
+      </c>
+      <c r="O59">
+        <v>-13.401286184</v>
+      </c>
+      <c r="P59">
+        <v>-26.014261416</v>
+      </c>
+      <c r="Q59">
+        <v>-10.814261416</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.3274791056755175</v>
+      </c>
+      <c r="T59">
+        <v>2.598977792785747</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.09143930126752531</v>
+      </c>
+      <c r="W59">
+        <v>0.216964294857315</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.2689391213750744</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.266485663509142</v>
+      </c>
+      <c r="C60">
+        <v>-2.772617915944949</v>
+      </c>
+      <c r="D60">
+        <v>201.565382084055</v>
+      </c>
+      <c r="E60">
+        <v>105.038</v>
+      </c>
+      <c r="F60">
+        <v>229.738</v>
+      </c>
+      <c r="G60">
+        <v>25.4</v>
+      </c>
+      <c r="H60">
+        <v>271.4</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>29.7</v>
+      </c>
+      <c r="K60">
+        <v>15.2</v>
+      </c>
+      <c r="L60">
+        <v>14.5</v>
+      </c>
+      <c r="M60">
+        <v>54.86143439999999</v>
+      </c>
+      <c r="N60">
+        <v>-40.36143439999999</v>
+      </c>
+      <c r="O60">
+        <v>-13.722887696</v>
+      </c>
+      <c r="P60">
+        <v>-26.63854670399999</v>
+      </c>
+      <c r="Q60">
+        <v>-11.43854670399999</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.3343524177154106</v>
+      </c>
+      <c r="T60">
+        <v>2.660858216423502</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.08986276159049902</v>
+      </c>
+      <c r="W60">
+        <v>0.2173407725321889</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.2643022399720559</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.268485663509142</v>
+      </c>
+      <c r="C61">
+        <v>-8.488759085877263</v>
+      </c>
+      <c r="D61">
+        <v>199.8102409141227</v>
+      </c>
+      <c r="E61">
+        <v>108.999</v>
+      </c>
+      <c r="F61">
+        <v>233.699</v>
+      </c>
+      <c r="G61">
+        <v>25.4</v>
+      </c>
+      <c r="H61">
+        <v>271.4</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>29.7</v>
+      </c>
+      <c r="K61">
+        <v>15.2</v>
+      </c>
+      <c r="L61">
+        <v>14.5</v>
+      </c>
+      <c r="M61">
+        <v>55.80732119999999</v>
+      </c>
+      <c r="N61">
+        <v>-41.30732119999999</v>
+      </c>
+      <c r="O61">
+        <v>-14.044489208</v>
+      </c>
+      <c r="P61">
+        <v>-27.26283199199999</v>
+      </c>
+      <c r="Q61">
+        <v>-12.06283199199999</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.341561013269445</v>
+      </c>
+      <c r="T61">
+        <v>2.72575719731188</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.08833966393642276</v>
+      </c>
+      <c r="W61">
+        <v>0.2177044882519822</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.2598225409894787</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.270485663509142</v>
+      </c>
+      <c r="C62">
+        <v>-14.17459814486577</v>
+      </c>
+      <c r="D62">
+        <v>198.0854018551342</v>
+      </c>
+      <c r="E62">
+        <v>112.96</v>
+      </c>
+      <c r="F62">
+        <v>237.66</v>
+      </c>
+      <c r="G62">
+        <v>25.4</v>
+      </c>
+      <c r="H62">
+        <v>271.4</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>29.7</v>
+      </c>
+      <c r="K62">
+        <v>15.2</v>
+      </c>
+      <c r="L62">
+        <v>14.5</v>
+      </c>
+      <c r="M62">
+        <v>56.75320799999999</v>
+      </c>
+      <c r="N62">
+        <v>-42.25320799999999</v>
+      </c>
+      <c r="O62">
+        <v>-14.36609072</v>
+      </c>
+      <c r="P62">
+        <v>-27.88711727999999</v>
+      </c>
+      <c r="Q62">
+        <v>-12.68711727999999</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.3491300386011811</v>
+      </c>
+      <c r="T62">
+        <v>2.793901127244677</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.08686733620414905</v>
+      </c>
+      <c r="W62">
+        <v>0.2180560801144492</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.2554921653063207</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.272485663509142</v>
+      </c>
+      <c r="C63">
+        <v>-19.83091311524598</v>
+      </c>
+      <c r="D63">
+        <v>196.390086884754</v>
+      </c>
+      <c r="E63">
+        <v>116.921</v>
+      </c>
+      <c r="F63">
+        <v>241.621</v>
+      </c>
+      <c r="G63">
+        <v>25.4</v>
+      </c>
+      <c r="H63">
+        <v>271.4</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>29.7</v>
+      </c>
+      <c r="K63">
+        <v>15.2</v>
+      </c>
+      <c r="L63">
+        <v>14.5</v>
+      </c>
+      <c r="M63">
+        <v>57.6990948</v>
+      </c>
+      <c r="N63">
+        <v>-43.1990948</v>
+      </c>
+      <c r="O63">
+        <v>-14.687692232</v>
+      </c>
+      <c r="P63">
+        <v>-28.51140256799999</v>
+      </c>
+      <c r="Q63">
+        <v>-13.31140256799999</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.3570872190781345</v>
+      </c>
+      <c r="T63">
+        <v>2.865539617686849</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.08544328151227774</v>
+      </c>
+      <c r="W63">
+        <v>0.2183961443748681</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.2513037691537581</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2744856635091419</v>
+      </c>
+      <c r="C64">
+        <v>-25.45845561053974</v>
+      </c>
+      <c r="D64">
+        <v>194.7235443894602</v>
+      </c>
+      <c r="E64">
+        <v>120.882</v>
+      </c>
+      <c r="F64">
+        <v>245.582</v>
+      </c>
+      <c r="G64">
+        <v>25.4</v>
+      </c>
+      <c r="H64">
+        <v>271.4</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>29.7</v>
+      </c>
+      <c r="K64">
+        <v>15.2</v>
+      </c>
+      <c r="L64">
+        <v>14.5</v>
+      </c>
+      <c r="M64">
+        <v>58.64498159999999</v>
+      </c>
+      <c r="N64">
+        <v>-44.14498159999999</v>
+      </c>
+      <c r="O64">
+        <v>-15.009293744</v>
+      </c>
+      <c r="P64">
+        <v>-29.13568785599999</v>
+      </c>
+      <c r="Q64">
+        <v>-13.93568785599999</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.3654631985275591</v>
+      </c>
+      <c r="T64">
+        <v>2.940948554994397</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.08406516406853135</v>
+      </c>
+      <c r="W64">
+        <v>0.2187252388204347</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.2472504825545039</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.276485663509142</v>
+      </c>
+      <c r="C65">
+        <v>-31.05795194653754</v>
+      </c>
+      <c r="D65">
+        <v>193.0850480534624</v>
+      </c>
+      <c r="E65">
+        <v>124.843</v>
+      </c>
+      <c r="F65">
+        <v>249.543</v>
+      </c>
+      <c r="G65">
+        <v>25.4</v>
+      </c>
+      <c r="H65">
+        <v>271.4</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>29.7</v>
+      </c>
+      <c r="K65">
+        <v>15.2</v>
+      </c>
+      <c r="L65">
+        <v>14.5</v>
+      </c>
+      <c r="M65">
+        <v>59.5908684</v>
+      </c>
+      <c r="N65">
+        <v>-45.0908684</v>
+      </c>
+      <c r="O65">
+        <v>-15.330895256</v>
+      </c>
+      <c r="P65">
+        <v>-29.75997314399999</v>
+      </c>
+      <c r="Q65">
+        <v>-14.55997314399999</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.3742919336228986</v>
+      </c>
+      <c r="T65">
+        <v>3.020433651075327</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.08273079638490385</v>
+      </c>
+      <c r="W65">
+        <v>0.219043885823285</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.2433258717203054</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.278485663509142</v>
+      </c>
+      <c r="C66">
+        <v>-36.63010419675209</v>
+      </c>
+      <c r="D66">
+        <v>191.4738958032479</v>
+      </c>
+      <c r="E66">
+        <v>128.804</v>
+      </c>
+      <c r="F66">
+        <v>253.504</v>
+      </c>
+      <c r="G66">
+        <v>25.4</v>
+      </c>
+      <c r="H66">
+        <v>271.4</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>29.7</v>
+      </c>
+      <c r="K66">
+        <v>15.2</v>
+      </c>
+      <c r="L66">
+        <v>14.5</v>
+      </c>
+      <c r="M66">
+        <v>60.5367552</v>
+      </c>
+      <c r="N66">
+        <v>-46.0367552</v>
+      </c>
+      <c r="O66">
+        <v>-15.652496768</v>
+      </c>
+      <c r="P66">
+        <v>-30.384258432</v>
+      </c>
+      <c r="Q66">
+        <v>-15.184258432</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.3836111540013124</v>
+      </c>
+      <c r="T66">
+        <v>3.10433458582742</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.08143812769138972</v>
+      </c>
+      <c r="W66">
+        <v>0.2193525751072962</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2395239049746756</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2804856635091421</v>
+      </c>
+      <c r="C67">
+        <v>-42.175591195469</v>
+      </c>
+      <c r="D67">
+        <v>189.889408804531</v>
+      </c>
+      <c r="E67">
+        <v>132.765</v>
+      </c>
+      <c r="F67">
+        <v>257.465</v>
+      </c>
+      <c r="G67">
+        <v>25.4</v>
+      </c>
+      <c r="H67">
+        <v>271.4</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>29.7</v>
+      </c>
+      <c r="K67">
+        <v>15.2</v>
+      </c>
+      <c r="L67">
+        <v>14.5</v>
+      </c>
+      <c r="M67">
+        <v>61.482642</v>
+      </c>
+      <c r="N67">
+        <v>-46.982642</v>
+      </c>
+      <c r="O67">
+        <v>-15.97409828</v>
+      </c>
+      <c r="P67">
+        <v>-31.00854372</v>
+      </c>
+      <c r="Q67">
+        <v>-15.80854372</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.3934629012584928</v>
+      </c>
+      <c r="T67">
+        <v>3.193029859708203</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.0801852334192145</v>
+      </c>
+      <c r="W67">
+        <v>0.2196517662594916</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.2358389218212191</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.282485663509142</v>
+      </c>
+      <c r="C68">
+        <v>-47.69506949140211</v>
+      </c>
+      <c r="D68">
+        <v>188.3309305085979</v>
+      </c>
+      <c r="E68">
+        <v>136.726</v>
+      </c>
+      <c r="F68">
+        <v>261.426</v>
+      </c>
+      <c r="G68">
+        <v>25.4</v>
+      </c>
+      <c r="H68">
+        <v>271.4</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>29.7</v>
+      </c>
+      <c r="K68">
+        <v>15.2</v>
+      </c>
+      <c r="L68">
+        <v>14.5</v>
+      </c>
+      <c r="M68">
+        <v>62.4285288</v>
+      </c>
+      <c r="N68">
+        <v>-47.9285288</v>
+      </c>
+      <c r="O68">
+        <v>-16.295699792</v>
+      </c>
+      <c r="P68">
+        <v>-31.632829008</v>
+      </c>
+      <c r="Q68">
+        <v>-16.432829008</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.4038941630602131</v>
+      </c>
+      <c r="T68">
+        <v>3.286942502640797</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.07897030564013549</v>
+      </c>
+      <c r="W68">
+        <v>0.2199418910131357</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.2322656048239279</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.284485663509142</v>
+      </c>
+      <c r="C69">
+        <v>-53.18917425477051</v>
+      </c>
+      <c r="D69">
+        <v>186.7978257452295</v>
+      </c>
+      <c r="E69">
+        <v>140.687</v>
+      </c>
+      <c r="F69">
+        <v>265.387</v>
+      </c>
+      <c r="G69">
+        <v>25.4</v>
+      </c>
+      <c r="H69">
+        <v>271.4</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>29.7</v>
+      </c>
+      <c r="K69">
+        <v>15.2</v>
+      </c>
+      <c r="L69">
+        <v>14.5</v>
+      </c>
+      <c r="M69">
+        <v>63.37441560000001</v>
+      </c>
+      <c r="N69">
+        <v>-48.87441560000001</v>
+      </c>
+      <c r="O69">
+        <v>-16.61730130400001</v>
+      </c>
+      <c r="P69">
+        <v>-32.257114296</v>
+      </c>
+      <c r="Q69">
+        <v>-17.057114296</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.4149576225468863</v>
+      </c>
+      <c r="T69">
+        <v>3.38654682090264</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.07779164436192451</v>
+      </c>
+      <c r="W69">
+        <v>0.2202233553263724</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.2287989540056603</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.286485663509142</v>
+      </c>
+      <c r="C70">
+        <v>-58.65852014042844</v>
+      </c>
+      <c r="D70">
+        <v>185.2894798595716</v>
+      </c>
+      <c r="E70">
+        <v>144.648</v>
+      </c>
+      <c r="F70">
+        <v>269.348</v>
+      </c>
+      <c r="G70">
+        <v>25.4</v>
+      </c>
+      <c r="H70">
+        <v>271.4</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>29.7</v>
+      </c>
+      <c r="K70">
+        <v>15.2</v>
+      </c>
+      <c r="L70">
+        <v>14.5</v>
+      </c>
+      <c r="M70">
+        <v>64.3203024</v>
+      </c>
+      <c r="N70">
+        <v>-49.8203024</v>
+      </c>
+      <c r="O70">
+        <v>-16.93890281600001</v>
+      </c>
+      <c r="P70">
+        <v>-32.88139958399999</v>
+      </c>
+      <c r="Q70">
+        <v>-17.68139958399999</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.4267125482514765</v>
+      </c>
+      <c r="T70">
+        <v>3.492376409055848</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.07664764959189621</v>
+      </c>
+      <c r="W70">
+        <v>0.2204965412774552</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.225434263505577</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2884856635091421</v>
+      </c>
+      <c r="C71">
+        <v>-64.10370210951288</v>
+      </c>
+      <c r="D71">
+        <v>183.8052978904871</v>
+      </c>
+      <c r="E71">
+        <v>148.609</v>
+      </c>
+      <c r="F71">
+        <v>273.309</v>
+      </c>
+      <c r="G71">
+        <v>25.4</v>
+      </c>
+      <c r="H71">
+        <v>271.4</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>29.7</v>
+      </c>
+      <c r="K71">
+        <v>15.2</v>
+      </c>
+      <c r="L71">
+        <v>14.5</v>
+      </c>
+      <c r="M71">
+        <v>65.26618920000001</v>
+      </c>
+      <c r="N71">
+        <v>-50.76618920000001</v>
+      </c>
+      <c r="O71">
+        <v>-17.26050432800001</v>
+      </c>
+      <c r="P71">
+        <v>-33.505684872</v>
+      </c>
+      <c r="Q71">
+        <v>-18.305684872</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.4392258562595887</v>
+      </c>
+      <c r="T71">
+        <v>3.605033712573778</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.07553681409056437</v>
+      </c>
+      <c r="W71">
+        <v>0.2207618087951732</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.2221671002663658</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.290485663509142</v>
+      </c>
+      <c r="C72">
+        <v>-69.52529621191636</v>
+      </c>
+      <c r="D72">
+        <v>182.3447037880836</v>
+      </c>
+      <c r="E72">
+        <v>152.57</v>
+      </c>
+      <c r="F72">
+        <v>277.27</v>
+      </c>
+      <c r="G72">
+        <v>25.4</v>
+      </c>
+      <c r="H72">
+        <v>271.4</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>29.7</v>
+      </c>
+      <c r="K72">
+        <v>15.2</v>
+      </c>
+      <c r="L72">
+        <v>14.5</v>
+      </c>
+      <c r="M72">
+        <v>66.212076</v>
+      </c>
+      <c r="N72">
+        <v>-51.712076</v>
+      </c>
+      <c r="O72">
+        <v>-17.58210584</v>
+      </c>
+      <c r="P72">
+        <v>-34.12997015999999</v>
+      </c>
+      <c r="Q72">
+        <v>-18.92997015999999</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.4525733848015749</v>
+      </c>
+      <c r="T72">
+        <v>3.725201502992904</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.07445771674641347</v>
+      </c>
+      <c r="W72">
+        <v>0.2210194972409565</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.2189932845482748</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.292485663509142</v>
+      </c>
+      <c r="C73">
+        <v>-74.92386033174691</v>
+      </c>
+      <c r="D73">
+        <v>180.907139668253</v>
+      </c>
+      <c r="E73">
+        <v>156.5309999999999</v>
+      </c>
+      <c r="F73">
+        <v>281.2309999999999</v>
+      </c>
+      <c r="G73">
+        <v>25.4</v>
+      </c>
+      <c r="H73">
+        <v>271.4</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>29.7</v>
+      </c>
+      <c r="K73">
+        <v>15.2</v>
+      </c>
+      <c r="L73">
+        <v>14.5</v>
+      </c>
+      <c r="M73">
+        <v>67.15796279999999</v>
+      </c>
+      <c r="N73">
+        <v>-52.65796279999999</v>
+      </c>
+      <c r="O73">
+        <v>-17.903707352</v>
+      </c>
+      <c r="P73">
+        <v>-34.75425544799999</v>
+      </c>
+      <c r="Q73">
+        <v>-19.554255448</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.4668414325533533</v>
+      </c>
+      <c r="T73">
+        <v>3.853656727234038</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.0734090165105485</v>
+      </c>
+      <c r="W73">
+        <v>0.221269926857281</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2159088720898484</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.294485663509142</v>
+      </c>
+      <c r="C74">
+        <v>-80.29993489780119</v>
+      </c>
+      <c r="D74">
+        <v>179.4920651021988</v>
+      </c>
+      <c r="E74">
+        <v>160.492</v>
+      </c>
+      <c r="F74">
+        <v>285.192</v>
+      </c>
+      <c r="G74">
+        <v>25.4</v>
+      </c>
+      <c r="H74">
+        <v>271.4</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>29.7</v>
+      </c>
+      <c r="K74">
+        <v>15.2</v>
+      </c>
+      <c r="L74">
+        <v>14.5</v>
+      </c>
+      <c r="M74">
+        <v>68.10384959999999</v>
+      </c>
+      <c r="N74">
+        <v>-53.60384959999999</v>
+      </c>
+      <c r="O74">
+        <v>-18.225308864</v>
+      </c>
+      <c r="P74">
+        <v>-35.37854073599999</v>
+      </c>
+      <c r="Q74">
+        <v>-20.17854073599999</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.4821286265731159</v>
+      </c>
+      <c r="T74">
+        <v>3.991287324635253</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.07238944683679088</v>
+      </c>
+      <c r="W74">
+        <v>0.2215134000953743</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2129101377552672</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.296485663509142</v>
+      </c>
+      <c r="C75">
+        <v>-85.65404356095226</v>
+      </c>
+      <c r="D75">
+        <v>178.0989564390477</v>
+      </c>
+      <c r="E75">
+        <v>164.453</v>
+      </c>
+      <c r="F75">
+        <v>289.153</v>
+      </c>
+      <c r="G75">
+        <v>25.4</v>
+      </c>
+      <c r="H75">
+        <v>271.4</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>29.7</v>
+      </c>
+      <c r="K75">
+        <v>15.2</v>
+      </c>
+      <c r="L75">
+        <v>14.5</v>
+      </c>
+      <c r="M75">
+        <v>69.0497364</v>
+      </c>
+      <c r="N75">
+        <v>-54.5497364</v>
+      </c>
+      <c r="O75">
+        <v>-18.546910376</v>
+      </c>
+      <c r="P75">
+        <v>-36.002826024</v>
+      </c>
+      <c r="Q75">
+        <v>-20.802826024</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.4985482053350831</v>
+      </c>
+      <c r="T75">
+        <v>4.139112781103226</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.07139781057875264</v>
+      </c>
+      <c r="W75">
+        <v>0.2217502028337939</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.209993560525743</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.298485663509142</v>
+      </c>
+      <c r="C76">
+        <v>-90.9866938402352</v>
+      </c>
+      <c r="D76">
+        <v>176.7273061597648</v>
+      </c>
+      <c r="E76">
+        <v>168.414</v>
+      </c>
+      <c r="F76">
+        <v>293.114</v>
+      </c>
+      <c r="G76">
+        <v>25.4</v>
+      </c>
+      <c r="H76">
+        <v>271.4</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>29.7</v>
+      </c>
+      <c r="K76">
+        <v>15.2</v>
+      </c>
+      <c r="L76">
+        <v>14.5</v>
+      </c>
+      <c r="M76">
+        <v>69.9956232</v>
+      </c>
+      <c r="N76">
+        <v>-55.4956232</v>
+      </c>
+      <c r="O76">
+        <v>-18.868511888</v>
+      </c>
+      <c r="P76">
+        <v>-36.627111312</v>
+      </c>
+      <c r="Q76">
+        <v>-21.427111312</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.5162308286172017</v>
+      </c>
+      <c r="T76">
+        <v>4.298309426530273</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.07043297530066139</v>
+      </c>
+      <c r="W76">
+        <v>0.2219806054982021</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.2071558097078275</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.300485663509142</v>
+      </c>
+      <c r="C77">
+        <v>-96.29837773930629</v>
+      </c>
+      <c r="D77">
+        <v>175.3766222606937</v>
+      </c>
+      <c r="E77">
+        <v>172.375</v>
+      </c>
+      <c r="F77">
+        <v>297.075</v>
+      </c>
+      <c r="G77">
+        <v>25.4</v>
+      </c>
+      <c r="H77">
+        <v>271.4</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>29.7</v>
+      </c>
+      <c r="K77">
+        <v>15.2</v>
+      </c>
+      <c r="L77">
+        <v>14.5</v>
+      </c>
+      <c r="M77">
+        <v>70.94150999999999</v>
+      </c>
+      <c r="N77">
+        <v>-56.44150999999999</v>
+      </c>
+      <c r="O77">
+        <v>-19.1901134</v>
+      </c>
+      <c r="P77">
+        <v>-37.25139659999999</v>
+      </c>
+      <c r="Q77">
+        <v>-22.05139659999999</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.5353280617618899</v>
+      </c>
+      <c r="T77">
+        <v>4.470241803591484</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.06949386896331924</v>
+      </c>
+      <c r="W77">
+        <v>0.2222048640915594</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2043937322450565</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.3024856635091421</v>
+      </c>
+      <c r="C78">
+        <v>-101.5895723348469</v>
+      </c>
+      <c r="D78">
+        <v>174.0464276651531</v>
+      </c>
+      <c r="E78">
+        <v>176.336</v>
+      </c>
+      <c r="F78">
+        <v>301.036</v>
+      </c>
+      <c r="G78">
+        <v>25.4</v>
+      </c>
+      <c r="H78">
+        <v>271.4</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>29.7</v>
+      </c>
+      <c r="K78">
+        <v>15.2</v>
+      </c>
+      <c r="L78">
+        <v>14.5</v>
+      </c>
+      <c r="M78">
+        <v>71.8873968</v>
+      </c>
+      <c r="N78">
+        <v>-57.3873968</v>
+      </c>
+      <c r="O78">
+        <v>-19.51171491200001</v>
+      </c>
+      <c r="P78">
+        <v>-37.875681888</v>
+      </c>
+      <c r="Q78">
+        <v>-22.675681888</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.5560167310019688</v>
+      </c>
+      <c r="T78">
+        <v>4.65650187874113</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.06857947595064398</v>
+      </c>
+      <c r="W78">
+        <v>0.2224232211429862</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2017043410313057</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.304485663509142</v>
+      </c>
+      <c r="C79">
+        <v>-106.8607403383919</v>
+      </c>
+      <c r="D79">
+        <v>172.7362596616081</v>
+      </c>
+      <c r="E79">
+        <v>180.297</v>
+      </c>
+      <c r="F79">
+        <v>304.997</v>
+      </c>
+      <c r="G79">
+        <v>25.4</v>
+      </c>
+      <c r="H79">
+        <v>271.4</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>29.7</v>
+      </c>
+      <c r="K79">
+        <v>15.2</v>
+      </c>
+      <c r="L79">
+        <v>14.5</v>
+      </c>
+      <c r="M79">
+        <v>72.83328359999999</v>
+      </c>
+      <c r="N79">
+        <v>-58.33328359999999</v>
+      </c>
+      <c r="O79">
+        <v>-19.833316424</v>
+      </c>
+      <c r="P79">
+        <v>-38.49996717599998</v>
+      </c>
+      <c r="Q79">
+        <v>-23.29996717599998</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.5785044149585761</v>
+      </c>
+      <c r="T79">
+        <v>4.858958482164658</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.06768883340583043</v>
+      </c>
+      <c r="W79">
+        <v>0.2226359065826877</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1990848041347953</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.306485663509142</v>
+      </c>
+      <c r="C80">
+        <v>-112.1123306329723</v>
+      </c>
+      <c r="D80">
+        <v>171.4456693670277</v>
+      </c>
+      <c r="E80">
+        <v>184.258</v>
+      </c>
+      <c r="F80">
+        <v>308.958</v>
+      </c>
+      <c r="G80">
+        <v>25.4</v>
+      </c>
+      <c r="H80">
+        <v>271.4</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>29.7</v>
+      </c>
+      <c r="K80">
+        <v>15.2</v>
+      </c>
+      <c r="L80">
+        <v>14.5</v>
+      </c>
+      <c r="M80">
+        <v>73.7791704</v>
+      </c>
+      <c r="N80">
+        <v>-59.2791704</v>
+      </c>
+      <c r="O80">
+        <v>-20.154917936</v>
+      </c>
+      <c r="P80">
+        <v>-39.12425246399999</v>
+      </c>
+      <c r="Q80">
+        <v>-23.92425246399999</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.6030364338203293</v>
+      </c>
+      <c r="T80">
+        <v>5.079820231353959</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.06682102784934542</v>
+      </c>
+      <c r="W80">
+        <v>0.2228431385495763</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1965324348510159</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.308485663509142</v>
+      </c>
+      <c r="C81">
+        <v>-117.3447787858787</v>
+      </c>
+      <c r="D81">
+        <v>170.1742212141212</v>
+      </c>
+      <c r="E81">
+        <v>188.219</v>
+      </c>
+      <c r="F81">
+        <v>312.919</v>
+      </c>
+      <c r="G81">
+        <v>25.4</v>
+      </c>
+      <c r="H81">
+        <v>271.4</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>29.7</v>
+      </c>
+      <c r="K81">
+        <v>15.2</v>
+      </c>
+      <c r="L81">
+        <v>14.5</v>
+      </c>
+      <c r="M81">
+        <v>74.72505719999999</v>
+      </c>
+      <c r="N81">
+        <v>-60.22505719999999</v>
+      </c>
+      <c r="O81">
+        <v>-20.476519448</v>
+      </c>
+      <c r="P81">
+        <v>-39.74853775199999</v>
+      </c>
+      <c r="Q81">
+        <v>-24.54853775199999</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.6299048354308214</v>
+      </c>
+      <c r="T81">
+        <v>5.321716432847006</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.06597519205378409</v>
+      </c>
+      <c r="W81">
+        <v>0.2230451241375564</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1940446825111296</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.310485663509142</v>
+      </c>
+      <c r="C82">
+        <v>-122.5585075387774</v>
+      </c>
+      <c r="D82">
+        <v>168.9214924612226</v>
+      </c>
+      <c r="E82">
+        <v>192.18</v>
+      </c>
+      <c r="F82">
+        <v>316.88</v>
+      </c>
+      <c r="G82">
+        <v>25.4</v>
+      </c>
+      <c r="H82">
+        <v>271.4</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>29.7</v>
+      </c>
+      <c r="K82">
+        <v>15.2</v>
+      </c>
+      <c r="L82">
+        <v>14.5</v>
+      </c>
+      <c r="M82">
+        <v>75.67094400000001</v>
+      </c>
+      <c r="N82">
+        <v>-61.17094400000001</v>
+      </c>
+      <c r="O82">
+        <v>-20.79812096000001</v>
+      </c>
+      <c r="P82">
+        <v>-40.37282304</v>
+      </c>
+      <c r="Q82">
+        <v>-25.17282304</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.6594600772023624</v>
+      </c>
+      <c r="T82">
+        <v>5.587802254489356</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.06515050215311179</v>
+      </c>
+      <c r="W82">
+        <v>0.2232420600858369</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1916191239797405</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.312485663509142</v>
+      </c>
+      <c r="C83">
+        <v>-127.7539272763358</v>
+      </c>
+      <c r="D83">
+        <v>167.6870727236642</v>
+      </c>
+      <c r="E83">
+        <v>196.141</v>
+      </c>
+      <c r="F83">
+        <v>320.841</v>
+      </c>
+      <c r="G83">
+        <v>25.4</v>
+      </c>
+      <c r="H83">
+        <v>271.4</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>29.7</v>
+      </c>
+      <c r="K83">
+        <v>15.2</v>
+      </c>
+      <c r="L83">
+        <v>14.5</v>
+      </c>
+      <c r="M83">
+        <v>76.6168308</v>
+      </c>
+      <c r="N83">
+        <v>-62.1168308</v>
+      </c>
+      <c r="O83">
+        <v>-21.11972247200001</v>
+      </c>
+      <c r="P83">
+        <v>-40.997108328</v>
+      </c>
+      <c r="Q83">
+        <v>-25.797108328</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.6921263970551184</v>
+      </c>
+      <c r="T83">
+        <v>5.881897109988795</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.06434617496603633</v>
+      </c>
+      <c r="W83">
+        <v>0.2234341334181105</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1892534557824598</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.314485663509142</v>
+      </c>
+      <c r="C84">
+        <v>-132.9314364744509</v>
+      </c>
+      <c r="D84">
+        <v>166.4705635255492</v>
+      </c>
+      <c r="E84">
+        <v>200.102</v>
+      </c>
+      <c r="F84">
+        <v>324.802</v>
+      </c>
+      <c r="G84">
+        <v>25.4</v>
+      </c>
+      <c r="H84">
+        <v>271.4</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>29.7</v>
+      </c>
+      <c r="K84">
+        <v>15.2</v>
+      </c>
+      <c r="L84">
+        <v>14.5</v>
+      </c>
+      <c r="M84">
+        <v>77.56271760000001</v>
+      </c>
+      <c r="N84">
+        <v>-63.06271760000001</v>
+      </c>
+      <c r="O84">
+        <v>-21.44132398400001</v>
+      </c>
+      <c r="P84">
+        <v>-41.62139361600001</v>
+      </c>
+      <c r="Q84">
+        <v>-26.42139361600001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.7284223080026249</v>
+      </c>
+      <c r="T84">
+        <v>6.20866917165484</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.06356146551523099</v>
+      </c>
+      <c r="W84">
+        <v>0.2236215220349629</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1869454868095028</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.316485663509142</v>
+      </c>
+      <c r="C85">
+        <v>-138.0914221291068</v>
+      </c>
+      <c r="D85">
+        <v>165.2715778708931</v>
+      </c>
+      <c r="E85">
+        <v>204.063</v>
+      </c>
+      <c r="F85">
+        <v>328.763</v>
+      </c>
+      <c r="G85">
+        <v>25.4</v>
+      </c>
+      <c r="H85">
+        <v>271.4</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>29.7</v>
+      </c>
+      <c r="K85">
+        <v>15.2</v>
+      </c>
+      <c r="L85">
+        <v>14.5</v>
+      </c>
+      <c r="M85">
+        <v>78.5086044</v>
+      </c>
+      <c r="N85">
+        <v>-64.0086044</v>
+      </c>
+      <c r="O85">
+        <v>-21.762925496</v>
+      </c>
+      <c r="P85">
+        <v>-42.24567890399999</v>
+      </c>
+      <c r="Q85">
+        <v>-27.04567890399999</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.7689883261204264</v>
+      </c>
+      <c r="T85">
+        <v>6.573885005281596</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.06279566472589088</v>
+      </c>
+      <c r="W85">
+        <v>0.2238043952634572</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1846931315467378</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.318485663509142</v>
+      </c>
+      <c r="C86">
+        <v>-143.2342601668329</v>
+      </c>
+      <c r="D86">
+        <v>164.089739833167</v>
+      </c>
+      <c r="E86">
+        <v>208.0239999999999</v>
+      </c>
+      <c r="F86">
+        <v>332.7239999999999</v>
+      </c>
+      <c r="G86">
+        <v>25.4</v>
+      </c>
+      <c r="H86">
+        <v>271.4</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>29.7</v>
+      </c>
+      <c r="K86">
+        <v>15.2</v>
+      </c>
+      <c r="L86">
+        <v>14.5</v>
+      </c>
+      <c r="M86">
+        <v>79.45449119999999</v>
+      </c>
+      <c r="N86">
+        <v>-64.95449119999999</v>
+      </c>
+      <c r="O86">
+        <v>-22.084527008</v>
+      </c>
+      <c r="P86">
+        <v>-42.86996419199999</v>
+      </c>
+      <c r="Q86">
+        <v>-27.66996419199999</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.8146250965029527</v>
+      </c>
+      <c r="T86">
+        <v>6.984752818111692</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.06204809728867789</v>
+      </c>
+      <c r="W86">
+        <v>0.2239829143674637</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1824944037902291</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.320485663509142</v>
+      </c>
+      <c r="C87">
+        <v>-148.3603158376754</v>
+      </c>
+      <c r="D87">
+        <v>162.9246841623246</v>
+      </c>
+      <c r="E87">
+        <v>211.985</v>
+      </c>
+      <c r="F87">
+        <v>336.6849999999999</v>
+      </c>
+      <c r="G87">
+        <v>25.4</v>
+      </c>
+      <c r="H87">
+        <v>271.4</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>29.7</v>
+      </c>
+      <c r="K87">
+        <v>15.2</v>
+      </c>
+      <c r="L87">
+        <v>14.5</v>
+      </c>
+      <c r="M87">
+        <v>80.40037799999999</v>
+      </c>
+      <c r="N87">
+        <v>-65.90037799999999</v>
+      </c>
+      <c r="O87">
+        <v>-22.40612852</v>
+      </c>
+      <c r="P87">
+        <v>-43.49424947999999</v>
+      </c>
+      <c r="Q87">
+        <v>-28.29424947999999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.8663467696031497</v>
+      </c>
+      <c r="T87">
+        <v>7.450403005985806</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.06131811967351698</v>
+      </c>
+      <c r="W87">
+        <v>0.2241572330219642</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1803474108044617</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.322485663509142</v>
+      </c>
+      <c r="C88">
+        <v>-153.4699440915461</v>
+      </c>
+      <c r="D88">
+        <v>161.7760559084539</v>
+      </c>
+      <c r="E88">
+        <v>215.946</v>
+      </c>
+      <c r="F88">
+        <v>340.646</v>
+      </c>
+      <c r="G88">
+        <v>25.4</v>
+      </c>
+      <c r="H88">
+        <v>271.4</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>29.7</v>
+      </c>
+      <c r="K88">
+        <v>15.2</v>
+      </c>
+      <c r="L88">
+        <v>14.5</v>
+      </c>
+      <c r="M88">
+        <v>81.3462648</v>
+      </c>
+      <c r="N88">
+        <v>-66.8462648</v>
+      </c>
+      <c r="O88">
+        <v>-22.727730032</v>
+      </c>
+      <c r="P88">
+        <v>-44.118534768</v>
+      </c>
+      <c r="Q88">
+        <v>-28.918534768</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.9254572531462317</v>
+      </c>
+      <c r="T88">
+        <v>7.982574649270506</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.06060511828196444</v>
+      </c>
+      <c r="W88">
+        <v>0.2243274977542669</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1782503478881307</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.324485663509142</v>
+      </c>
+      <c r="C89">
+        <v>-158.5634899387638</v>
+      </c>
+      <c r="D89">
+        <v>160.6435100612362</v>
+      </c>
+      <c r="E89">
+        <v>219.907</v>
+      </c>
+      <c r="F89">
+        <v>344.607</v>
+      </c>
+      <c r="G89">
+        <v>25.4</v>
+      </c>
+      <c r="H89">
+        <v>271.4</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>29.7</v>
+      </c>
+      <c r="K89">
+        <v>15.2</v>
+      </c>
+      <c r="L89">
+        <v>14.5</v>
+      </c>
+      <c r="M89">
+        <v>82.2921516</v>
+      </c>
+      <c r="N89">
+        <v>-67.7921516</v>
+      </c>
+      <c r="O89">
+        <v>-23.049331544</v>
+      </c>
+      <c r="P89">
+        <v>-44.74282005599999</v>
+      </c>
+      <c r="Q89">
+        <v>-29.54282005599999</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.9936616572344035</v>
+      </c>
+      <c r="T89">
+        <v>8.596618853060546</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.05990850772699934</v>
+      </c>
+      <c r="W89">
+        <v>0.2244938483547926</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1762014933147039</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.326485663509142</v>
+      </c>
+      <c r="C90">
+        <v>-163.6412887955558</v>
+      </c>
+      <c r="D90">
+        <v>159.5267112044442</v>
+      </c>
+      <c r="E90">
+        <v>223.868</v>
+      </c>
+      <c r="F90">
+        <v>348.568</v>
+      </c>
+      <c r="G90">
+        <v>25.4</v>
+      </c>
+      <c r="H90">
+        <v>271.4</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>29.7</v>
+      </c>
+      <c r="K90">
+        <v>15.2</v>
+      </c>
+      <c r="L90">
+        <v>14.5</v>
+      </c>
+      <c r="M90">
+        <v>83.23803839999999</v>
+      </c>
+      <c r="N90">
+        <v>-68.73803839999999</v>
+      </c>
+      <c r="O90">
+        <v>-23.370933056</v>
+      </c>
+      <c r="P90">
+        <v>-45.367105344</v>
+      </c>
+      <c r="Q90">
+        <v>-30.167105344</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.073233462003937</v>
+      </c>
+      <c r="T90">
+        <v>9.313003757482258</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.05922772923010163</v>
+      </c>
+      <c r="W90">
+        <v>0.2246564182598517</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1741992036179459</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.328485663509142</v>
+      </c>
+      <c r="C91">
+        <v>-168.7036668152479</v>
+      </c>
+      <c r="D91">
+        <v>158.425333184752</v>
+      </c>
+      <c r="E91">
+        <v>227.829</v>
+      </c>
+      <c r="F91">
+        <v>352.529</v>
+      </c>
+      <c r="G91">
+        <v>25.4</v>
+      </c>
+      <c r="H91">
+        <v>271.4</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>29.7</v>
+      </c>
+      <c r="K91">
+        <v>15.2</v>
+      </c>
+      <c r="L91">
+        <v>14.5</v>
+      </c>
+      <c r="M91">
+        <v>84.1839252</v>
+      </c>
+      <c r="N91">
+        <v>-69.6839252</v>
+      </c>
+      <c r="O91">
+        <v>-23.69253456800001</v>
+      </c>
+      <c r="P91">
+        <v>-45.991390632</v>
+      </c>
+      <c r="Q91">
+        <v>-30.791390632</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.167272867640659</v>
+      </c>
+      <c r="T91">
+        <v>10.15964046270792</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.05856224912639262</v>
+      </c>
+      <c r="W91">
+        <v>0.2248153349086175</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1722419091952724</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.330485663509142</v>
+      </c>
+      <c r="C92">
+        <v>-173.7509412058285</v>
+      </c>
+      <c r="D92">
+        <v>157.3390587941714</v>
+      </c>
+      <c r="E92">
+        <v>231.79</v>
+      </c>
+      <c r="F92">
+        <v>356.49</v>
+      </c>
+      <c r="G92">
+        <v>25.4</v>
+      </c>
+      <c r="H92">
+        <v>271.4</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>29.7</v>
+      </c>
+      <c r="K92">
+        <v>15.2</v>
+      </c>
+      <c r="L92">
+        <v>14.5</v>
+      </c>
+      <c r="M92">
+        <v>85.12981199999999</v>
+      </c>
+      <c r="N92">
+        <v>-70.62981199999999</v>
+      </c>
+      <c r="O92">
+        <v>-24.01413608</v>
+      </c>
+      <c r="P92">
+        <v>-46.61567591999999</v>
+      </c>
+      <c r="Q92">
+        <v>-31.41567591999999</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.280120154404725</v>
+      </c>
+      <c r="T92">
+        <v>11.17560450897871</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.0579115574694327</v>
+      </c>
+      <c r="W92">
+        <v>0.2249707200762995</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1703281102042138</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.332485663509142</v>
+      </c>
+      <c r="C93">
+        <v>-178.7834205345379</v>
+      </c>
+      <c r="D93">
+        <v>156.267579465462</v>
+      </c>
+      <c r="E93">
+        <v>235.751</v>
+      </c>
+      <c r="F93">
+        <v>360.451</v>
+      </c>
+      <c r="G93">
+        <v>25.4</v>
+      </c>
+      <c r="H93">
+        <v>271.4</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>29.7</v>
+      </c>
+      <c r="K93">
+        <v>15.2</v>
+      </c>
+      <c r="L93">
+        <v>14.5</v>
+      </c>
+      <c r="M93">
+        <v>86.0756988</v>
+      </c>
+      <c r="N93">
+        <v>-71.5756988</v>
+      </c>
+      <c r="O93">
+        <v>-24.335737592</v>
+      </c>
+      <c r="P93">
+        <v>-47.239961208</v>
+      </c>
+      <c r="Q93">
+        <v>-32.03996120799999</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.41804461600525</v>
+      </c>
+      <c r="T93">
+        <v>12.41733834330968</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.05727516672801036</v>
+      </c>
+      <c r="W93">
+        <v>0.2251226901853511</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1684563727294422</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.334485663509142</v>
+      </c>
+      <c r="C94">
+        <v>-183.8014050200954</v>
+      </c>
+      <c r="D94">
+        <v>155.2105949799046</v>
+      </c>
+      <c r="E94">
+        <v>239.712</v>
+      </c>
+      <c r="F94">
+        <v>364.412</v>
+      </c>
+      <c r="G94">
+        <v>25.4</v>
+      </c>
+      <c r="H94">
+        <v>271.4</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>29.7</v>
+      </c>
+      <c r="K94">
+        <v>15.2</v>
+      </c>
+      <c r="L94">
+        <v>14.5</v>
+      </c>
+      <c r="M94">
+        <v>87.02158559999999</v>
+      </c>
+      <c r="N94">
+        <v>-72.52158559999999</v>
+      </c>
+      <c r="O94">
+        <v>-24.65733910400001</v>
+      </c>
+      <c r="P94">
+        <v>-47.86424649599999</v>
+      </c>
+      <c r="Q94">
+        <v>-32.66424649599999</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.590450193005907</v>
+      </c>
+      <c r="T94">
+        <v>13.9695056362234</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.05665261056792329</v>
+      </c>
+      <c r="W94">
+        <v>0.22527135659638</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1666253251997744</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.336485663509142</v>
+      </c>
+      <c r="C95">
+        <v>-188.805186813147</v>
+      </c>
+      <c r="D95">
+        <v>154.167813186853</v>
+      </c>
+      <c r="E95">
+        <v>243.673</v>
+      </c>
+      <c r="F95">
+        <v>368.373</v>
+      </c>
+      <c r="G95">
+        <v>25.4</v>
+      </c>
+      <c r="H95">
+        <v>271.4</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>29.7</v>
+      </c>
+      <c r="K95">
+        <v>15.2</v>
+      </c>
+      <c r="L95">
+        <v>14.5</v>
+      </c>
+      <c r="M95">
+        <v>87.96747240000001</v>
+      </c>
+      <c r="N95">
+        <v>-73.46747240000001</v>
+      </c>
+      <c r="O95">
+        <v>-24.97894061600001</v>
+      </c>
+      <c r="P95">
+        <v>-48.488531784</v>
+      </c>
+      <c r="Q95">
+        <v>-33.288531784</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.812114506292465</v>
+      </c>
+      <c r="T95">
+        <v>15.96514929854103</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.05604344271235422</v>
+      </c>
+      <c r="W95">
+        <v>0.2254168258802898</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1648336550363358</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.338485663509142</v>
+      </c>
+      <c r="C96">
+        <v>-193.7950502654833</v>
+      </c>
+      <c r="D96">
+        <v>153.1389497345167</v>
+      </c>
+      <c r="E96">
+        <v>247.634</v>
+      </c>
+      <c r="F96">
+        <v>372.334</v>
+      </c>
+      <c r="G96">
+        <v>25.4</v>
+      </c>
+      <c r="H96">
+        <v>271.4</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>29.7</v>
+      </c>
+      <c r="K96">
+        <v>15.2</v>
+      </c>
+      <c r="L96">
+        <v>14.5</v>
+      </c>
+      <c r="M96">
+        <v>88.9133592</v>
+      </c>
+      <c r="N96">
+        <v>-74.4133592</v>
+      </c>
+      <c r="O96">
+        <v>-25.30054212800001</v>
+      </c>
+      <c r="P96">
+        <v>-49.112817072</v>
+      </c>
+      <c r="Q96">
+        <v>-33.912817072</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>2.107666924007876</v>
+      </c>
+      <c r="T96">
+        <v>18.62600751496453</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.05544723587498875</v>
+      </c>
+      <c r="W96">
+        <v>0.2255592000730527</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1630801055146728</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3404856635091421</v>
+      </c>
+      <c r="C97">
+        <v>-198.7712721885488</v>
+      </c>
+      <c r="D97">
+        <v>152.1237278114512</v>
+      </c>
+      <c r="E97">
+        <v>251.595</v>
+      </c>
+      <c r="F97">
+        <v>376.295</v>
+      </c>
+      <c r="G97">
+        <v>25.4</v>
+      </c>
+      <c r="H97">
+        <v>271.4</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>29.7</v>
+      </c>
+      <c r="K97">
+        <v>15.2</v>
+      </c>
+      <c r="L97">
+        <v>14.5</v>
+      </c>
+      <c r="M97">
+        <v>89.85924600000001</v>
+      </c>
+      <c r="N97">
+        <v>-75.35924600000001</v>
+      </c>
+      <c r="O97">
+        <v>-25.62214364000001</v>
+      </c>
+      <c r="P97">
+        <v>-49.73710236</v>
+      </c>
+      <c r="Q97">
+        <v>-34.53710236000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.521440308809453</v>
+      </c>
+      <c r="T97">
+        <v>22.35120901795745</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.05486358076051517</v>
+      </c>
+      <c r="W97">
+        <v>0.225698576914389</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1613634728250446</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.342485663509142</v>
+      </c>
+      <c r="C98">
+        <v>-203.7341221017361</v>
+      </c>
+      <c r="D98">
+        <v>151.1218778982638</v>
+      </c>
+      <c r="E98">
+        <v>255.556</v>
+      </c>
+      <c r="F98">
+        <v>380.256</v>
+      </c>
+      <c r="G98">
+        <v>25.4</v>
+      </c>
+      <c r="H98">
+        <v>271.4</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>29.7</v>
+      </c>
+      <c r="K98">
+        <v>15.2</v>
+      </c>
+      <c r="L98">
+        <v>14.5</v>
+      </c>
+      <c r="M98">
+        <v>90.8051328</v>
+      </c>
+      <c r="N98">
+        <v>-76.3051328</v>
+      </c>
+      <c r="O98">
+        <v>-25.94374515200001</v>
+      </c>
+      <c r="P98">
+        <v>-50.36138764799999</v>
+      </c>
+      <c r="Q98">
+        <v>-35.16138764799999</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>3.142100386011809</v>
+      </c>
+      <c r="T98">
+        <v>27.93901127244675</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.05429208512759316</v>
+      </c>
+      <c r="W98">
+        <v>0.2258350500715308</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1596826033164505</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.344485663509142</v>
+      </c>
+      <c r="C99">
+        <v>-208.683862470934</v>
+      </c>
+      <c r="D99">
+        <v>150.1331375290659</v>
+      </c>
+      <c r="E99">
+        <v>259.517</v>
+      </c>
+      <c r="F99">
+        <v>384.217</v>
+      </c>
+      <c r="G99">
+        <v>25.4</v>
+      </c>
+      <c r="H99">
+        <v>271.4</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>29.7</v>
+      </c>
+      <c r="K99">
+        <v>15.2</v>
+      </c>
+      <c r="L99">
+        <v>14.5</v>
+      </c>
+      <c r="M99">
+        <v>91.75101960000001</v>
+      </c>
+      <c r="N99">
+        <v>-77.25101960000001</v>
+      </c>
+      <c r="O99">
+        <v>-26.26534666400001</v>
+      </c>
+      <c r="P99">
+        <v>-50.985672936</v>
+      </c>
+      <c r="Q99">
+        <v>-35.785672936</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>4.176533848015746</v>
+      </c>
+      <c r="T99">
+        <v>37.25201502992901</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.05373237290978291</v>
+      </c>
+      <c r="W99">
+        <v>0.2259687093491438</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1580363909111262</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.346485663509142</v>
+      </c>
+      <c r="C100">
+        <v>-213.6207489377703</v>
+      </c>
+      <c r="D100">
+        <v>149.1572510622296</v>
+      </c>
+      <c r="E100">
+        <v>263.478</v>
+      </c>
+      <c r="F100">
+        <v>388.1779999999999</v>
+      </c>
+      <c r="G100">
+        <v>25.4</v>
+      </c>
+      <c r="H100">
+        <v>271.4</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>29.7</v>
+      </c>
+      <c r="K100">
+        <v>15.2</v>
+      </c>
+      <c r="L100">
+        <v>14.5</v>
+      </c>
+      <c r="M100">
+        <v>92.69690639999999</v>
+      </c>
+      <c r="N100">
+        <v>-78.19690639999999</v>
+      </c>
+      <c r="O100">
+        <v>-26.586948176</v>
+      </c>
+      <c r="P100">
+        <v>-51.60995822399998</v>
+      </c>
+      <c r="Q100">
+        <v>-36.40995822399998</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>6.245400772023618</v>
+      </c>
+      <c r="T100">
+        <v>55.8780225448935</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.05318408339029534</v>
+      </c>
+      <c r="W100">
+        <v>0.2260996408863975</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1564237746773391</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.348485663509142</v>
+      </c>
+      <c r="C101">
+        <v>-218.5450305399736</v>
+      </c>
+      <c r="D101">
+        <v>148.1939694600264</v>
+      </c>
+      <c r="E101">
+        <v>267.439</v>
+      </c>
+      <c r="F101">
+        <v>392.139</v>
+      </c>
+      <c r="G101">
+        <v>25.4</v>
+      </c>
+      <c r="H101">
+        <v>271.4</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>29.7</v>
+      </c>
+      <c r="K101">
+        <v>15.2</v>
+      </c>
+      <c r="L101">
+        <v>14.5</v>
+      </c>
+      <c r="M101">
+        <v>93.6427932</v>
+      </c>
+      <c r="N101">
+        <v>-79.1427932</v>
+      </c>
+      <c r="O101">
+        <v>-26.90854968800001</v>
+      </c>
+      <c r="P101">
+        <v>-52.23424351199999</v>
+      </c>
+      <c r="Q101">
+        <v>-37.03424351199999</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>12.45200154404724</v>
+      </c>
+      <c r="T101">
+        <v>111.756045089787</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.052646870426757</v>
+      </c>
+      <c r="W101">
+        <v>0.2262279273420904</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1548437365492853</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/brazil/brazil_advertising.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_advertising.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1391951059373666</v>
+        <v>0.1387515425771795</v>
       </c>
       <c r="C2">
-        <v>767.1589959863255</v>
+        <v>762.3769047777164</v>
       </c>
       <c r="D2">
-        <v>685.8589959863256</v>
+        <v>689.1319047777164</v>
       </c>
       <c r="E2">
-        <v>-161.3</v>
+        <v>-153.245</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8.055</v>
       </c>
       <c r="G2">
         <v>81.3</v>
@@ -1445,28 +1445,28 @@
         <v>74.7</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4051665</v>
       </c>
       <c r="N2">
-        <v>74.7</v>
+        <v>74.29483350000001</v>
       </c>
       <c r="O2">
-        <v>25.398</v>
+        <v>25.26024339000001</v>
       </c>
       <c r="P2">
-        <v>49.302</v>
+        <v>49.03459011</v>
       </c>
       <c r="Q2">
-        <v>74.602</v>
+        <v>74.33459010999999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1391951059373666</v>
+        <v>0.139817739976949</v>
       </c>
       <c r="T2">
-        <v>1.217251318914063</v>
+        <v>1.225366327706823</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>184.3686484445284</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1387515425771795</v>
+        <v>0.1383079792169924</v>
       </c>
       <c r="C3">
-        <v>762.3769047777164</v>
+        <v>757.6261998869882</v>
       </c>
       <c r="D3">
-        <v>689.1319047777164</v>
+        <v>692.4361998869882</v>
       </c>
       <c r="E3">
-        <v>-153.245</v>
+        <v>-145.19</v>
       </c>
       <c r="F3">
-        <v>8.055</v>
+        <v>16.11</v>
       </c>
       <c r="G3">
         <v>81.3</v>
@@ -1527,28 +1527,28 @@
         <v>74.7</v>
       </c>
       <c r="M3">
-        <v>0.4051665</v>
+        <v>0.810333</v>
       </c>
       <c r="N3">
-        <v>74.29483350000001</v>
+        <v>73.889667</v>
       </c>
       <c r="O3">
-        <v>25.26024339000001</v>
+        <v>25.12248678</v>
       </c>
       <c r="P3">
-        <v>49.03459011</v>
+        <v>48.76718022</v>
       </c>
       <c r="Q3">
-        <v>74.33459010999999</v>
+        <v>74.06718022</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.139817739976949</v>
+        <v>0.1404530808336658</v>
       </c>
       <c r="T3">
-        <v>1.225366327706823</v>
+        <v>1.233646948923926</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>184.3686484445284</v>
+        <v>92.18432422226418</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1383079792169924</v>
+        <v>0.1378644158568055</v>
       </c>
       <c r="C4">
-        <v>757.6261998869882</v>
+        <v>752.9073349689151</v>
       </c>
       <c r="D4">
-        <v>692.4361998869882</v>
+        <v>695.7723349689151</v>
       </c>
       <c r="E4">
-        <v>-145.19</v>
+        <v>-137.135</v>
       </c>
       <c r="F4">
-        <v>16.11</v>
+        <v>24.165</v>
       </c>
       <c r="G4">
         <v>81.3</v>
@@ -1609,28 +1609,28 @@
         <v>74.7</v>
       </c>
       <c r="M4">
-        <v>0.810333</v>
+        <v>1.2154995</v>
       </c>
       <c r="N4">
-        <v>73.889667</v>
+        <v>73.4845005</v>
       </c>
       <c r="O4">
-        <v>25.12248678</v>
+        <v>24.98473017</v>
       </c>
       <c r="P4">
-        <v>48.76718022</v>
+        <v>48.49977033</v>
       </c>
       <c r="Q4">
-        <v>74.06718022</v>
+        <v>73.79977033</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1404530808336658</v>
+        <v>0.1411015215018613</v>
       </c>
       <c r="T4">
-        <v>1.233646948923926</v>
+        <v>1.242098304599113</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>92.18432422226418</v>
+        <v>61.45621614817612</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1378644158568055</v>
+        <v>0.1374208524966184</v>
       </c>
       <c r="C5">
-        <v>752.9073349689151</v>
+        <v>748.2207724633751</v>
       </c>
       <c r="D5">
-        <v>695.7723349689151</v>
+        <v>699.1407724633751</v>
       </c>
       <c r="E5">
-        <v>-137.135</v>
+        <v>-129.08</v>
       </c>
       <c r="F5">
-        <v>24.165</v>
+        <v>32.22</v>
       </c>
       <c r="G5">
         <v>81.3</v>
@@ -1691,28 +1691,28 @@
         <v>74.7</v>
       </c>
       <c r="M5">
-        <v>1.2154995</v>
+        <v>1.620666</v>
       </c>
       <c r="N5">
-        <v>73.4845005</v>
+        <v>73.079334</v>
       </c>
       <c r="O5">
-        <v>24.98473017</v>
+        <v>24.84697356</v>
       </c>
       <c r="P5">
-        <v>48.49977033</v>
+        <v>48.23236044</v>
       </c>
       <c r="Q5">
-        <v>73.79977033</v>
+        <v>73.53236043999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1411015215018613</v>
+        <v>0.1417634713506442</v>
       </c>
       <c r="T5">
-        <v>1.242098304599113</v>
+        <v>1.2507257301842</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>61.45621614817612</v>
+        <v>46.09216211113209</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1374208524966184</v>
+        <v>0.1369772891364313</v>
       </c>
       <c r="C6">
-        <v>748.2207724633751</v>
+        <v>743.5669838090383</v>
       </c>
       <c r="D6">
-        <v>699.1407724633751</v>
+        <v>702.5419838090384</v>
       </c>
       <c r="E6">
-        <v>-129.08</v>
+        <v>-121.025</v>
       </c>
       <c r="F6">
-        <v>32.22</v>
+        <v>40.27500000000001</v>
       </c>
       <c r="G6">
         <v>81.3</v>
@@ -1773,28 +1773,28 @@
         <v>74.7</v>
       </c>
       <c r="M6">
-        <v>1.620666</v>
+        <v>2.0258325</v>
       </c>
       <c r="N6">
-        <v>73.079334</v>
+        <v>72.6741675</v>
       </c>
       <c r="O6">
-        <v>24.84697356</v>
+        <v>24.70921695</v>
       </c>
       <c r="P6">
-        <v>48.23236044</v>
+        <v>47.96495055</v>
       </c>
       <c r="Q6">
-        <v>73.53236043999999</v>
+        <v>73.26495054999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1417634713506442</v>
+        <v>0.1424393569857172</v>
       </c>
       <c r="T6">
-        <v>1.2507257301842</v>
+        <v>1.259534785781604</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>46.09216211113209</v>
+        <v>36.87372968890566</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1369772891364313</v>
+        <v>0.1365337257762443</v>
       </c>
       <c r="C7">
-        <v>743.5669838090383</v>
+        <v>738.9464496633258</v>
       </c>
       <c r="D7">
-        <v>702.5419838090384</v>
+        <v>705.9764496633259</v>
       </c>
       <c r="E7">
-        <v>-121.025</v>
+        <v>-112.97</v>
       </c>
       <c r="F7">
-        <v>40.27500000000001</v>
+        <v>48.33000000000001</v>
       </c>
       <c r="G7">
         <v>81.3</v>
@@ -1855,28 +1855,28 @@
         <v>74.7</v>
       </c>
       <c r="M7">
-        <v>2.0258325</v>
+        <v>2.430999</v>
       </c>
       <c r="N7">
-        <v>72.6741675</v>
+        <v>72.269001</v>
       </c>
       <c r="O7">
-        <v>24.70921695</v>
+        <v>24.57146034</v>
       </c>
       <c r="P7">
-        <v>47.96495055</v>
+        <v>47.69754066</v>
       </c>
       <c r="Q7">
-        <v>73.26495054999999</v>
+        <v>72.99754066</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1424393569857172</v>
+        <v>0.1431296231662173</v>
       </c>
       <c r="T7">
-        <v>1.259534785781604</v>
+        <v>1.268531268093847</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>36.87372968890566</v>
+        <v>30.72810807408806</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1365337257762443</v>
+        <v>0.1360901624160573</v>
       </c>
       <c r="C8">
-        <v>738.9464496633258</v>
+        <v>734.3596601288536</v>
       </c>
       <c r="D8">
-        <v>705.9764496633259</v>
+        <v>709.4446601288537</v>
       </c>
       <c r="E8">
-        <v>-112.97</v>
+        <v>-104.915</v>
       </c>
       <c r="F8">
-        <v>48.33</v>
+        <v>56.38499999999999</v>
       </c>
       <c r="G8">
         <v>81.3</v>
@@ -1937,28 +1937,28 @@
         <v>74.7</v>
       </c>
       <c r="M8">
-        <v>2.430999</v>
+        <v>2.836165499999999</v>
       </c>
       <c r="N8">
-        <v>72.269001</v>
+        <v>71.86383450000001</v>
       </c>
       <c r="O8">
-        <v>24.57146034</v>
+        <v>24.43370373</v>
       </c>
       <c r="P8">
-        <v>47.69754066</v>
+        <v>47.43013077000001</v>
       </c>
       <c r="Q8">
-        <v>72.99754066</v>
+        <v>72.73013077</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1431296231662173</v>
+        <v>0.1438347337807067</v>
       </c>
       <c r="T8">
-        <v>1.268531268093847</v>
+        <v>1.277721223143987</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>30.72810807408806</v>
+        <v>26.33837834921835</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1360901624160573</v>
+        <v>0.1356465990558702</v>
       </c>
       <c r="C9">
-        <v>734.3596601288536</v>
+        <v>729.8071149865809</v>
       </c>
       <c r="D9">
-        <v>709.4446601288537</v>
+        <v>712.947114986581</v>
       </c>
       <c r="E9">
-        <v>-104.915</v>
+        <v>-96.86000000000001</v>
       </c>
       <c r="F9">
-        <v>56.38500000000001</v>
+        <v>64.44</v>
       </c>
       <c r="G9">
         <v>81.3</v>
@@ -2019,28 +2019,28 @@
         <v>74.7</v>
       </c>
       <c r="M9">
-        <v>2.8361655</v>
+        <v>3.241332</v>
       </c>
       <c r="N9">
-        <v>71.8638345</v>
+        <v>71.458668</v>
       </c>
       <c r="O9">
-        <v>24.43370373</v>
+        <v>24.29594712</v>
       </c>
       <c r="P9">
-        <v>47.43013076999999</v>
+        <v>47.16272088</v>
       </c>
       <c r="Q9">
-        <v>72.73013076999999</v>
+        <v>72.46272088000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1438347337807067</v>
+        <v>0.1445551728868154</v>
       </c>
       <c r="T9">
-        <v>1.277721223143987</v>
+        <v>1.287110959825652</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.33837834921834</v>
+        <v>23.04608105556605</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1356465990558702</v>
+        <v>0.1352030356956831</v>
       </c>
       <c r="C10">
-        <v>729.8071149865809</v>
+        <v>725.2893239359006</v>
       </c>
       <c r="D10">
-        <v>712.947114986581</v>
+        <v>716.4843239359006</v>
       </c>
       <c r="E10">
-        <v>-96.86000000000001</v>
+        <v>-88.80500000000002</v>
       </c>
       <c r="F10">
-        <v>64.44</v>
+        <v>72.49499999999999</v>
       </c>
       <c r="G10">
         <v>81.3</v>
@@ -2101,28 +2101,28 @@
         <v>74.7</v>
       </c>
       <c r="M10">
-        <v>3.241332</v>
+        <v>3.646498499999999</v>
       </c>
       <c r="N10">
-        <v>71.458668</v>
+        <v>71.05350150000001</v>
       </c>
       <c r="O10">
-        <v>24.29594712</v>
+        <v>24.15819051</v>
       </c>
       <c r="P10">
-        <v>47.16272088</v>
+        <v>46.89531099000001</v>
       </c>
       <c r="Q10">
-        <v>72.46272088000001</v>
+        <v>72.19531099</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1445551728868154</v>
+        <v>0.145291445819432</v>
       </c>
       <c r="T10">
-        <v>1.287110959825652</v>
+        <v>1.296707064346475</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.04608105556605</v>
+        <v>20.48540538272538</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1352030356956831</v>
+        <v>0.1347594723354961</v>
       </c>
       <c r="C11">
-        <v>725.2893239359006</v>
+        <v>720.8068068419119</v>
       </c>
       <c r="D11">
-        <v>716.4843239359006</v>
+        <v>720.0568068419119</v>
       </c>
       <c r="E11">
-        <v>-88.80500000000002</v>
+        <v>-80.75000000000001</v>
       </c>
       <c r="F11">
-        <v>72.49499999999999</v>
+        <v>80.55</v>
       </c>
       <c r="G11">
         <v>81.3</v>
@@ -2183,28 +2183,28 @@
         <v>74.7</v>
       </c>
       <c r="M11">
-        <v>3.646498499999999</v>
+        <v>4.051665</v>
       </c>
       <c r="N11">
-        <v>71.05350150000001</v>
+        <v>70.648335</v>
       </c>
       <c r="O11">
-        <v>24.15819051</v>
+        <v>24.0204339</v>
       </c>
       <c r="P11">
-        <v>46.89531099000001</v>
+        <v>46.6279011</v>
       </c>
       <c r="Q11">
-        <v>72.19531099</v>
+        <v>71.9279011</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.145291445819432</v>
+        <v>0.1460440803727734</v>
       </c>
       <c r="T11">
-        <v>1.296707064346475</v>
+        <v>1.306516415634427</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.48540538272538</v>
+        <v>18.43686484445284</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1347594723354961</v>
+        <v>0.1343159089753091</v>
       </c>
       <c r="C12">
-        <v>720.8068068419118</v>
+        <v>716.3600939901289</v>
       </c>
       <c r="D12">
-        <v>720.0568068419119</v>
+        <v>723.665093990129</v>
       </c>
       <c r="E12">
-        <v>-80.75</v>
+        <v>-72.69500000000001</v>
       </c>
       <c r="F12">
-        <v>80.55000000000001</v>
+        <v>88.605</v>
       </c>
       <c r="G12">
         <v>81.3</v>
@@ -2265,28 +2265,28 @@
         <v>74.7</v>
       </c>
       <c r="M12">
-        <v>4.051665000000001</v>
+        <v>4.4568315</v>
       </c>
       <c r="N12">
-        <v>70.648335</v>
+        <v>70.2431685</v>
       </c>
       <c r="O12">
-        <v>24.0204339</v>
+        <v>23.88267729</v>
       </c>
       <c r="P12">
-        <v>46.6279011</v>
+        <v>46.36049120999999</v>
       </c>
       <c r="Q12">
-        <v>71.9279011</v>
+        <v>71.66049120999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1460440803727734</v>
+        <v>0.146813628062145</v>
       </c>
       <c r="T12">
-        <v>1.306516415634427</v>
+        <v>1.316546201782783</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.43686484445283</v>
+        <v>16.76078622222985</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1343159089753091</v>
+        <v>0.133872345615122</v>
       </c>
       <c r="C13">
-        <v>716.3600939901289</v>
+        <v>711.9497263488842</v>
       </c>
       <c r="D13">
-        <v>723.665093990129</v>
+        <v>727.3097263488842</v>
       </c>
       <c r="E13">
-        <v>-72.69500000000001</v>
+        <v>-64.64000000000001</v>
       </c>
       <c r="F13">
-        <v>88.605</v>
+        <v>96.66</v>
       </c>
       <c r="G13">
         <v>81.3</v>
@@ -2347,28 +2347,28 @@
         <v>74.7</v>
       </c>
       <c r="M13">
-        <v>4.4568315</v>
+        <v>4.861998</v>
       </c>
       <c r="N13">
-        <v>70.2431685</v>
+        <v>69.838002</v>
       </c>
       <c r="O13">
-        <v>23.88267729</v>
+        <v>23.74492068</v>
       </c>
       <c r="P13">
-        <v>46.36049120999999</v>
+        <v>46.09308132</v>
       </c>
       <c r="Q13">
-        <v>71.66049120999999</v>
+        <v>71.39308131999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.146813628062145</v>
+        <v>0.1476006654717296</v>
       </c>
       <c r="T13">
-        <v>1.316546201782783</v>
+        <v>1.326803937616329</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.76078622222985</v>
+        <v>15.36405403704403</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.133872345615122</v>
+        <v>0.133428782254935</v>
       </c>
       <c r="C14">
-        <v>711.9497263488842</v>
+        <v>707.5762558397021</v>
       </c>
       <c r="D14">
-        <v>727.3097263488842</v>
+        <v>730.9912558397021</v>
       </c>
       <c r="E14">
-        <v>-64.64000000000001</v>
+        <v>-56.58500000000001</v>
       </c>
       <c r="F14">
-        <v>96.66</v>
+        <v>104.715</v>
       </c>
       <c r="G14">
         <v>81.3</v>
@@ -2429,28 +2429,28 @@
         <v>74.7</v>
       </c>
       <c r="M14">
-        <v>4.861998</v>
+        <v>5.2671645</v>
       </c>
       <c r="N14">
-        <v>69.838002</v>
+        <v>69.43283550000001</v>
       </c>
       <c r="O14">
-        <v>23.74492068</v>
+        <v>23.60716407000001</v>
       </c>
       <c r="P14">
-        <v>46.09308132</v>
+        <v>45.82567143</v>
       </c>
       <c r="Q14">
-        <v>71.39308131999999</v>
+        <v>71.12567143</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1476006654717296</v>
+        <v>0.1484057956953276</v>
       </c>
       <c r="T14">
-        <v>1.326803937616329</v>
+        <v>1.337297483469036</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.36405403704403</v>
+        <v>14.18220372650218</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.133428782254935</v>
+        <v>0.1329852188947479</v>
       </c>
       <c r="C15">
-        <v>707.5762558397021</v>
+        <v>703.2402456159286</v>
       </c>
       <c r="D15">
-        <v>730.9912558397021</v>
+        <v>734.7102456159287</v>
       </c>
       <c r="E15">
-        <v>-56.58500000000001</v>
+        <v>-48.53</v>
       </c>
       <c r="F15">
-        <v>104.715</v>
+        <v>112.77</v>
       </c>
       <c r="G15">
         <v>81.3</v>
@@ -2511,28 +2511,28 @@
         <v>74.7</v>
       </c>
       <c r="M15">
-        <v>5.2671645</v>
+        <v>5.672331</v>
       </c>
       <c r="N15">
-        <v>69.43283550000001</v>
+        <v>69.027669</v>
       </c>
       <c r="O15">
-        <v>23.60716407000001</v>
+        <v>23.46940746</v>
       </c>
       <c r="P15">
-        <v>45.82567143</v>
+        <v>45.55826154</v>
       </c>
       <c r="Q15">
-        <v>71.12567143</v>
+        <v>70.85826154</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1484057956953276</v>
+        <v>0.1492296498776138</v>
       </c>
       <c r="T15">
-        <v>1.337297483469036</v>
+        <v>1.348035065271806</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.18220372650218</v>
+        <v>13.16918917460917</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1329852188947479</v>
+        <v>0.1326901555345609</v>
       </c>
       <c r="C16">
-        <v>703.2402456159286</v>
+        <v>697.6801896346333</v>
       </c>
       <c r="D16">
-        <v>734.7102456159287</v>
+        <v>737.2051896346334</v>
       </c>
       <c r="E16">
-        <v>-48.53</v>
+        <v>-40.47499999999999</v>
       </c>
       <c r="F16">
-        <v>112.77</v>
+        <v>120.825</v>
       </c>
       <c r="G16">
         <v>81.3</v>
@@ -2593,45 +2593,45 @@
         <v>74.7</v>
       </c>
       <c r="M16">
-        <v>5.672331</v>
+        <v>6.258735000000001</v>
       </c>
       <c r="N16">
-        <v>69.027669</v>
+        <v>68.441265</v>
       </c>
       <c r="O16">
-        <v>23.46940746</v>
+        <v>23.2700301</v>
       </c>
       <c r="P16">
-        <v>45.55826154</v>
+        <v>45.1712349</v>
       </c>
       <c r="Q16">
-        <v>70.85826154</v>
+        <v>70.4712349</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1492296498776138</v>
+        <v>0.1500728888641893</v>
       </c>
       <c r="T16">
-        <v>1.348035065271806</v>
+        <v>1.359025296058171</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.34</v>
       </c>
       <c r="W16">
-        <v>0.03319799999999999</v>
+        <v>0.034188</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.16918917460917</v>
+        <v>11.93531919788903</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1326901555345609</v>
+        <v>0.1322564921743738</v>
       </c>
       <c r="C17">
-        <v>697.6801896346333</v>
+        <v>693.3229903624203</v>
       </c>
       <c r="D17">
-        <v>737.2051896346334</v>
+        <v>740.9029903624204</v>
       </c>
       <c r="E17">
-        <v>-40.47500000000002</v>
+        <v>-32.42000000000002</v>
       </c>
       <c r="F17">
-        <v>120.825</v>
+        <v>128.88</v>
       </c>
       <c r="G17">
         <v>81.3</v>
@@ -2675,28 +2675,28 @@
         <v>74.7</v>
       </c>
       <c r="M17">
-        <v>6.258734999999999</v>
+        <v>6.675984</v>
       </c>
       <c r="N17">
-        <v>68.441265</v>
+        <v>68.024016</v>
       </c>
       <c r="O17">
-        <v>23.2700301</v>
+        <v>23.12816544</v>
       </c>
       <c r="P17">
-        <v>45.1712349</v>
+        <v>44.89585056</v>
       </c>
       <c r="Q17">
-        <v>70.4712349</v>
+        <v>70.19585056</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1500728888641893</v>
+        <v>0.1509362049694926</v>
       </c>
       <c r="T17">
-        <v>1.359025296058171</v>
+        <v>1.370277199006116</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.93531919788903</v>
+        <v>11.18936174802097</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1322564921743738</v>
+        <v>0.1318228288141868</v>
       </c>
       <c r="C18">
-        <v>693.3229903624203</v>
+        <v>689.0030742326242</v>
       </c>
       <c r="D18">
-        <v>740.9029903624204</v>
+        <v>744.6380742326243</v>
       </c>
       <c r="E18">
-        <v>-32.42000000000002</v>
+        <v>-24.36500000000001</v>
       </c>
       <c r="F18">
-        <v>128.88</v>
+        <v>136.935</v>
       </c>
       <c r="G18">
         <v>81.3</v>
@@ -2757,28 +2757,28 @@
         <v>74.7</v>
       </c>
       <c r="M18">
-        <v>6.675984</v>
+        <v>7.093233</v>
       </c>
       <c r="N18">
-        <v>68.024016</v>
+        <v>67.606767</v>
       </c>
       <c r="O18">
-        <v>23.12816544</v>
+        <v>22.98630078</v>
       </c>
       <c r="P18">
-        <v>44.89585056</v>
+        <v>44.62046622</v>
       </c>
       <c r="Q18">
-        <v>70.19585056</v>
+        <v>69.92046621999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1509362049694926</v>
+        <v>0.1518203238725142</v>
       </c>
       <c r="T18">
-        <v>1.370277199006116</v>
+        <v>1.381800232145578</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.18936174802097</v>
+        <v>10.53116399813738</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1318228288141868</v>
+        <v>0.1313891654539997</v>
       </c>
       <c r="C19">
-        <v>689.0030742326242</v>
+        <v>684.7210079641546</v>
       </c>
       <c r="D19">
-        <v>744.6380742326243</v>
+        <v>748.4110079641547</v>
       </c>
       <c r="E19">
-        <v>-24.36500000000001</v>
+        <v>-16.31</v>
       </c>
       <c r="F19">
-        <v>136.935</v>
+        <v>144.99</v>
       </c>
       <c r="G19">
         <v>81.3</v>
@@ -2839,28 +2839,28 @@
         <v>74.7</v>
       </c>
       <c r="M19">
-        <v>7.093233</v>
+        <v>7.510482000000001</v>
       </c>
       <c r="N19">
-        <v>67.606767</v>
+        <v>67.18951800000001</v>
       </c>
       <c r="O19">
-        <v>22.98630078</v>
+        <v>22.84443612</v>
       </c>
       <c r="P19">
-        <v>44.62046622</v>
+        <v>44.34508188</v>
       </c>
       <c r="Q19">
-        <v>69.92046621999999</v>
+        <v>69.64508187999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1518203238725142</v>
+        <v>0.1527260066512192</v>
       </c>
       <c r="T19">
-        <v>1.381800232145578</v>
+        <v>1.393604314873807</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.53116399813738</v>
+        <v>9.946099331574192</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1313891654539997</v>
+        <v>0.1311686820938127</v>
       </c>
       <c r="C20">
-        <v>684.7210079641546</v>
+        <v>678.5989436706654</v>
       </c>
       <c r="D20">
-        <v>748.4110079641547</v>
+        <v>750.3439436706655</v>
       </c>
       <c r="E20">
-        <v>-16.31000000000003</v>
+        <v>-8.254999999999995</v>
       </c>
       <c r="F20">
-        <v>144.99</v>
+        <v>153.045</v>
       </c>
       <c r="G20">
         <v>81.3</v>
@@ -2921,45 +2921,45 @@
         <v>74.7</v>
       </c>
       <c r="M20">
-        <v>7.510481999999999</v>
+        <v>8.187907500000001</v>
       </c>
       <c r="N20">
-        <v>67.18951800000001</v>
+        <v>66.51209249999999</v>
       </c>
       <c r="O20">
-        <v>22.84443612</v>
+        <v>22.61411145</v>
       </c>
       <c r="P20">
-        <v>44.34508188</v>
+        <v>43.89798105</v>
       </c>
       <c r="Q20">
-        <v>69.64508187999999</v>
+        <v>69.19798105</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1527260066512192</v>
+        <v>0.15365405196767</v>
       </c>
       <c r="T20">
-        <v>1.393604314873807</v>
+        <v>1.405699856434832</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.34</v>
       </c>
       <c r="W20">
-        <v>0.034188</v>
+        <v>0.03530999999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>9.946099331574194</v>
+        <v>9.123210050919601</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1311686820938127</v>
+        <v>0.1307462387336256</v>
       </c>
       <c r="C21">
-        <v>678.5989436706654</v>
+        <v>674.2754545837525</v>
       </c>
       <c r="D21">
-        <v>750.3439436706655</v>
+        <v>754.0754545837526</v>
       </c>
       <c r="E21">
-        <v>-8.254999999999995</v>
+        <v>-0.1999999999999886</v>
       </c>
       <c r="F21">
-        <v>153.045</v>
+        <v>161.1</v>
       </c>
       <c r="G21">
         <v>81.3</v>
@@ -3003,28 +3003,28 @@
         <v>74.7</v>
       </c>
       <c r="M21">
-        <v>8.187907500000001</v>
+        <v>8.618850000000002</v>
       </c>
       <c r="N21">
-        <v>66.51209249999999</v>
+        <v>66.08115000000001</v>
       </c>
       <c r="O21">
-        <v>22.61411145</v>
+        <v>22.46759100000001</v>
       </c>
       <c r="P21">
-        <v>43.89798105</v>
+        <v>43.613559</v>
       </c>
       <c r="Q21">
-        <v>69.19798105</v>
+        <v>68.91355899999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.15365405196767</v>
+        <v>0.154605298417032</v>
       </c>
       <c r="T21">
-        <v>1.405699856434832</v>
+        <v>1.418097786534883</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.123210050919601</v>
+        <v>8.667049548373623</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1307462387336256</v>
+        <v>0.1303237953734386</v>
       </c>
       <c r="C22">
-        <v>674.2754545837525</v>
+        <v>669.9892650999097</v>
       </c>
       <c r="D22">
-        <v>754.0754545837526</v>
+        <v>757.8442650999099</v>
       </c>
       <c r="E22">
-        <v>-0.1999999999999886</v>
+        <v>7.855000000000018</v>
       </c>
       <c r="F22">
-        <v>161.1</v>
+        <v>169.155</v>
       </c>
       <c r="G22">
         <v>81.3</v>
@@ -3085,28 +3085,28 @@
         <v>74.7</v>
       </c>
       <c r="M22">
-        <v>8.618850000000002</v>
+        <v>9.049792500000001</v>
       </c>
       <c r="N22">
-        <v>66.08115000000001</v>
+        <v>65.65020750000001</v>
       </c>
       <c r="O22">
-        <v>22.46759100000001</v>
+        <v>22.32107055000001</v>
       </c>
       <c r="P22">
-        <v>43.613559</v>
+        <v>43.32913695000001</v>
       </c>
       <c r="Q22">
-        <v>68.91355899999999</v>
+        <v>68.62913695</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.154605298417032</v>
+        <v>0.1555806270549856</v>
       </c>
       <c r="T22">
-        <v>1.418097786534883</v>
+        <v>1.430809588283037</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.667049548373623</v>
+        <v>8.254332903212974</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1303237953734386</v>
+        <v>0.1299013520132516</v>
       </c>
       <c r="C23">
-        <v>669.9892650999099</v>
+        <v>665.7409372898745</v>
       </c>
       <c r="D23">
-        <v>757.8442650999099</v>
+        <v>761.6509372898746</v>
       </c>
       <c r="E23">
-        <v>7.85499999999999</v>
+        <v>15.91</v>
       </c>
       <c r="F23">
-        <v>169.155</v>
+        <v>177.21</v>
       </c>
       <c r="G23">
         <v>81.3</v>
@@ -3167,28 +3167,28 @@
         <v>74.7</v>
       </c>
       <c r="M23">
-        <v>9.049792500000001</v>
+        <v>9.480735000000001</v>
       </c>
       <c r="N23">
-        <v>65.65020750000001</v>
+        <v>65.21926500000001</v>
       </c>
       <c r="O23">
-        <v>22.32107055000001</v>
+        <v>22.1745501</v>
       </c>
       <c r="P23">
-        <v>43.32913695000001</v>
+        <v>43.0447149</v>
       </c>
       <c r="Q23">
-        <v>68.62913695</v>
+        <v>68.3447149</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1555806270549856</v>
+        <v>0.1565809641195533</v>
       </c>
       <c r="T23">
-        <v>1.430809588283036</v>
+        <v>1.443847333665758</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.254332903212974</v>
+        <v>7.87913595306693</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1299013520132516</v>
+        <v>0.1296003486530645</v>
       </c>
       <c r="C24">
-        <v>665.7409372898745</v>
+        <v>660.4217193611762</v>
       </c>
       <c r="D24">
-        <v>761.6509372898746</v>
+        <v>764.3867193611762</v>
       </c>
       <c r="E24">
-        <v>15.91</v>
+        <v>23.965</v>
       </c>
       <c r="F24">
-        <v>177.21</v>
+        <v>185.265</v>
       </c>
       <c r="G24">
         <v>81.3</v>
@@ -3249,45 +3249,45 @@
         <v>74.7</v>
       </c>
       <c r="M24">
-        <v>9.480735000000001</v>
+        <v>10.0598895</v>
       </c>
       <c r="N24">
-        <v>65.21926500000001</v>
+        <v>64.64011050000001</v>
       </c>
       <c r="O24">
-        <v>22.1745501</v>
+        <v>21.97763757</v>
       </c>
       <c r="P24">
-        <v>43.0447149</v>
+        <v>42.66247293000001</v>
       </c>
       <c r="Q24">
-        <v>68.3447149</v>
+        <v>67.96247293</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1565809641195533</v>
+        <v>0.1576072839650188</v>
       </c>
       <c r="T24">
-        <v>1.443847333665758</v>
+        <v>1.457223721785692</v>
       </c>
       <c r="U24">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V24">
         <v>0.34</v>
       </c>
       <c r="W24">
-        <v>0.03530999999999999</v>
+        <v>0.03583799999999999</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>7.87913595306693</v>
+        <v>7.425528878821184</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1296003486530645</v>
+        <v>0.1291831852928775</v>
       </c>
       <c r="C25">
-        <v>660.4217193611762</v>
+        <v>656.1909212216714</v>
       </c>
       <c r="D25">
-        <v>764.3867193611762</v>
+        <v>768.2109212216715</v>
       </c>
       <c r="E25">
-        <v>23.965</v>
+        <v>32.02000000000001</v>
       </c>
       <c r="F25">
-        <v>185.265</v>
+        <v>193.32</v>
       </c>
       <c r="G25">
         <v>81.3</v>
@@ -3331,28 +3331,28 @@
         <v>74.7</v>
       </c>
       <c r="M25">
-        <v>10.0598895</v>
+        <v>10.497276</v>
       </c>
       <c r="N25">
-        <v>64.64011050000001</v>
+        <v>64.202724</v>
       </c>
       <c r="O25">
-        <v>21.97763757</v>
+        <v>21.82892616</v>
       </c>
       <c r="P25">
-        <v>42.66247293000001</v>
+        <v>42.37379784</v>
       </c>
       <c r="Q25">
-        <v>67.96247293</v>
+        <v>67.67379783999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1576072839650188</v>
+        <v>0.1586606122274704</v>
       </c>
       <c r="T25">
-        <v>1.457223721785692</v>
+        <v>1.47095212011931</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.425528878821184</v>
+        <v>7.116131842203634</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1291831852928775</v>
+        <v>0.1287660219326904</v>
       </c>
       <c r="C26">
-        <v>656.1909212216717</v>
+        <v>651.9985801965616</v>
       </c>
       <c r="D26">
-        <v>768.2109212216718</v>
+        <v>772.0735801965617</v>
       </c>
       <c r="E26">
-        <v>32.01999999999998</v>
+        <v>40.07499999999999</v>
       </c>
       <c r="F26">
-        <v>193.32</v>
+        <v>201.375</v>
       </c>
       <c r="G26">
         <v>81.3</v>
@@ -3413,28 +3413,28 @@
         <v>74.7</v>
       </c>
       <c r="M26">
-        <v>10.497276</v>
+        <v>10.9346625</v>
       </c>
       <c r="N26">
-        <v>64.202724</v>
+        <v>63.7653375</v>
       </c>
       <c r="O26">
-        <v>21.82892616</v>
+        <v>21.68021475</v>
       </c>
       <c r="P26">
-        <v>42.37379784</v>
+        <v>42.08512275</v>
       </c>
       <c r="Q26">
-        <v>67.67379783999999</v>
+        <v>67.38512274999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1586606122274703</v>
+        <v>0.1597420292435872</v>
       </c>
       <c r="T26">
-        <v>1.470952120119309</v>
+        <v>1.485046609075157</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.116131842203635</v>
+        <v>6.831486568515489</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1287660219326904</v>
+        <v>0.1283488585725034</v>
       </c>
       <c r="C27">
-        <v>651.9985801965616</v>
+        <v>647.8452793187071</v>
       </c>
       <c r="D27">
-        <v>772.0735801965617</v>
+        <v>775.9752793187071</v>
       </c>
       <c r="E27">
-        <v>40.07499999999999</v>
+        <v>48.13</v>
       </c>
       <c r="F27">
-        <v>201.375</v>
+        <v>209.43</v>
       </c>
       <c r="G27">
         <v>81.3</v>
@@ -3495,28 +3495,28 @@
         <v>74.7</v>
       </c>
       <c r="M27">
-        <v>10.9346625</v>
+        <v>11.372049</v>
       </c>
       <c r="N27">
-        <v>63.7653375</v>
+        <v>63.327951</v>
       </c>
       <c r="O27">
-        <v>21.68021475</v>
+        <v>21.53150334</v>
       </c>
       <c r="P27">
-        <v>42.08512275</v>
+        <v>41.79644766</v>
       </c>
       <c r="Q27">
-        <v>67.38512274999999</v>
+        <v>67.09644766</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1597420292435872</v>
+        <v>0.1608526737466262</v>
       </c>
       <c r="T27">
-        <v>1.485046609075157</v>
+        <v>1.499522030164945</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.831486568515489</v>
+        <v>6.568737085111047</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1283488585725034</v>
+        <v>0.1279316952123163</v>
       </c>
       <c r="C28">
-        <v>647.8452793187071</v>
+        <v>643.7316134663324</v>
       </c>
       <c r="D28">
-        <v>775.9752793187071</v>
+        <v>779.9166134663325</v>
       </c>
       <c r="E28">
-        <v>48.13</v>
+        <v>56.185</v>
       </c>
       <c r="F28">
-        <v>209.43</v>
+        <v>217.485</v>
       </c>
       <c r="G28">
         <v>81.3</v>
@@ -3577,28 +3577,28 @@
         <v>74.7</v>
       </c>
       <c r="M28">
-        <v>11.372049</v>
+        <v>11.8094355</v>
       </c>
       <c r="N28">
-        <v>63.327951</v>
+        <v>62.8905645</v>
       </c>
       <c r="O28">
-        <v>21.53150334</v>
+        <v>21.38279193</v>
       </c>
       <c r="P28">
-        <v>41.79644766</v>
+        <v>41.50777257</v>
       </c>
       <c r="Q28">
-        <v>67.09644766</v>
+        <v>66.80777257</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1608526737466262</v>
+        <v>0.1619937468661867</v>
       </c>
       <c r="T28">
-        <v>1.499522030164945</v>
+        <v>1.514394038133906</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.568737085111047</v>
+        <v>6.32545052640323</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1279316952123163</v>
+        <v>0.1276993318521293</v>
       </c>
       <c r="C29">
-        <v>643.7316134663324</v>
+        <v>637.8893793201239</v>
       </c>
       <c r="D29">
-        <v>779.9166134663325</v>
+        <v>782.129379320124</v>
       </c>
       <c r="E29">
-        <v>56.185</v>
+        <v>64.24000000000001</v>
       </c>
       <c r="F29">
-        <v>217.485</v>
+        <v>225.54</v>
       </c>
       <c r="G29">
         <v>81.3</v>
@@ -3659,45 +3659,45 @@
         <v>74.7</v>
       </c>
       <c r="M29">
-        <v>11.8094355</v>
+        <v>12.472362</v>
       </c>
       <c r="N29">
-        <v>62.8905645</v>
+        <v>62.227638</v>
       </c>
       <c r="O29">
-        <v>21.38279193</v>
+        <v>21.15739692</v>
       </c>
       <c r="P29">
-        <v>41.50777257</v>
+        <v>41.07024108</v>
       </c>
       <c r="Q29">
-        <v>66.80777257</v>
+        <v>66.37024108</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1619937468661867</v>
+        <v>0.1631665164612907</v>
       </c>
       <c r="T29">
-        <v>1.514394038133906</v>
+        <v>1.529679157435339</v>
       </c>
       <c r="U29">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V29">
         <v>0.34</v>
       </c>
       <c r="W29">
-        <v>0.03583799999999999</v>
+        <v>0.036498</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>6.32545052640323</v>
+        <v>5.9892424546369</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1276993318521293</v>
+        <v>0.1272887684919422</v>
       </c>
       <c r="C30">
-        <v>637.8893793201239</v>
+        <v>633.7749673547371</v>
       </c>
       <c r="D30">
-        <v>782.129379320124</v>
+        <v>786.0699673547372</v>
       </c>
       <c r="E30">
-        <v>64.24000000000001</v>
+        <v>72.29500000000002</v>
       </c>
       <c r="F30">
-        <v>225.54</v>
+        <v>233.595</v>
       </c>
       <c r="G30">
         <v>81.3</v>
@@ -3741,28 +3741,28 @@
         <v>74.7</v>
       </c>
       <c r="M30">
-        <v>12.472362</v>
+        <v>12.9178035</v>
       </c>
       <c r="N30">
-        <v>62.227638</v>
+        <v>61.7821965</v>
       </c>
       <c r="O30">
-        <v>21.15739692</v>
+        <v>21.00594681</v>
       </c>
       <c r="P30">
-        <v>41.07024108</v>
+        <v>40.77624969</v>
       </c>
       <c r="Q30">
-        <v>66.37024108</v>
+        <v>66.07624969</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1631665164612907</v>
+        <v>0.1643723218196369</v>
       </c>
       <c r="T30">
-        <v>1.529679157435339</v>
+        <v>1.545394843477657</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.9892424546369</v>
+        <v>5.782716852752869</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1272887684919422</v>
+        <v>0.1268782051317552</v>
       </c>
       <c r="C31">
-        <v>633.7749673547371</v>
+        <v>629.7004640445048</v>
       </c>
       <c r="D31">
-        <v>786.0699673547372</v>
+        <v>790.0504640445048</v>
       </c>
       <c r="E31">
-        <v>72.29499999999996</v>
+        <v>80.34999999999997</v>
       </c>
       <c r="F31">
-        <v>233.595</v>
+        <v>241.65</v>
       </c>
       <c r="G31">
         <v>81.3</v>
@@ -3823,28 +3823,28 @@
         <v>74.7</v>
       </c>
       <c r="M31">
-        <v>12.9178035</v>
+        <v>13.363245</v>
       </c>
       <c r="N31">
-        <v>61.7821965</v>
+        <v>61.336755</v>
       </c>
       <c r="O31">
-        <v>21.00594681</v>
+        <v>20.8544967</v>
       </c>
       <c r="P31">
-        <v>40.77624969</v>
+        <v>40.4822583</v>
       </c>
       <c r="Q31">
-        <v>66.07624969</v>
+        <v>65.7822583</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1643723218196369</v>
+        <v>0.1656125787596503</v>
       </c>
       <c r="T31">
-        <v>1.545394843477657</v>
+        <v>1.561559549121184</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.782716852752871</v>
+        <v>5.589959624327774</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1268782051317552</v>
+        <v>0.1264676417715681</v>
       </c>
       <c r="C32">
-        <v>629.7004640445048</v>
+        <v>625.6664787427401</v>
       </c>
       <c r="D32">
-        <v>790.0504640445048</v>
+        <v>794.0714787427401</v>
       </c>
       <c r="E32">
-        <v>80.34999999999997</v>
+        <v>88.40499999999997</v>
       </c>
       <c r="F32">
-        <v>241.65</v>
+        <v>249.705</v>
       </c>
       <c r="G32">
         <v>81.3</v>
@@ -3905,28 +3905,28 @@
         <v>74.7</v>
       </c>
       <c r="M32">
-        <v>13.363245</v>
+        <v>13.8086865</v>
       </c>
       <c r="N32">
-        <v>61.336755</v>
+        <v>60.8913135</v>
       </c>
       <c r="O32">
-        <v>20.8544967</v>
+        <v>20.70304659</v>
       </c>
       <c r="P32">
-        <v>40.4822583</v>
+        <v>40.18826691</v>
       </c>
       <c r="Q32">
-        <v>65.7822583</v>
+        <v>65.48826690999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1656125787596503</v>
+        <v>0.1668887851761857</v>
       </c>
       <c r="T32">
-        <v>1.561559549121184</v>
+        <v>1.578192796957276</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.589959624327774</v>
+        <v>5.409638346123652</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1264676417715681</v>
+        <v>0.1260570784113811</v>
       </c>
       <c r="C33">
-        <v>625.6664787427401</v>
+        <v>621.6736332715933</v>
       </c>
       <c r="D33">
-        <v>794.0714787427401</v>
+        <v>798.1336332715933</v>
       </c>
       <c r="E33">
-        <v>88.40499999999997</v>
+        <v>96.45999999999998</v>
       </c>
       <c r="F33">
-        <v>249.705</v>
+        <v>257.76</v>
       </c>
       <c r="G33">
         <v>81.3</v>
@@ -3987,28 +3987,28 @@
         <v>74.7</v>
       </c>
       <c r="M33">
-        <v>13.8086865</v>
+        <v>14.254128</v>
       </c>
       <c r="N33">
-        <v>60.8913135</v>
+        <v>60.445872</v>
       </c>
       <c r="O33">
-        <v>20.70304659</v>
+        <v>20.55159648</v>
       </c>
       <c r="P33">
-        <v>40.18826691</v>
+        <v>39.89427552</v>
       </c>
       <c r="Q33">
-        <v>65.48826690999999</v>
+        <v>65.19427551999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1668887851761857</v>
+        <v>0.1682025270755604</v>
       </c>
       <c r="T33">
-        <v>1.578192796957276</v>
+        <v>1.595315257965019</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.409638346123652</v>
+        <v>5.240587147807288</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1260570784113811</v>
+        <v>0.125646515051194</v>
       </c>
       <c r="C34">
-        <v>621.6736332715933</v>
+        <v>617.7225622426222</v>
       </c>
       <c r="D34">
-        <v>798.1336332715933</v>
+        <v>802.2375622426222</v>
       </c>
       <c r="E34">
-        <v>96.45999999999998</v>
+        <v>104.515</v>
       </c>
       <c r="F34">
-        <v>257.76</v>
+        <v>265.815</v>
       </c>
       <c r="G34">
         <v>81.3</v>
@@ -4069,28 +4069,28 @@
         <v>74.7</v>
       </c>
       <c r="M34">
-        <v>14.254128</v>
+        <v>14.6995695</v>
       </c>
       <c r="N34">
-        <v>60.445872</v>
+        <v>60.0004305</v>
       </c>
       <c r="O34">
-        <v>20.55159648</v>
+        <v>20.40014637</v>
       </c>
       <c r="P34">
-        <v>39.89427552</v>
+        <v>39.60028413</v>
       </c>
       <c r="Q34">
-        <v>65.19427551999999</v>
+        <v>64.90028412999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1682025270755604</v>
+        <v>0.1695554851510359</v>
       </c>
       <c r="T34">
-        <v>1.595315257965019</v>
+        <v>1.612948837211798</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.240587147807288</v>
+        <v>5.081781476661612</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.125646515051194</v>
+        <v>0.125235951691007</v>
       </c>
       <c r="C35">
-        <v>617.7225622426222</v>
+        <v>613.8139133873002</v>
       </c>
       <c r="D35">
-        <v>802.2375622426222</v>
+        <v>806.3839133873003</v>
       </c>
       <c r="E35">
-        <v>104.515</v>
+        <v>112.57</v>
       </c>
       <c r="F35">
-        <v>265.815</v>
+        <v>273.87</v>
       </c>
       <c r="G35">
         <v>81.3</v>
@@ -4151,28 +4151,28 @@
         <v>74.7</v>
       </c>
       <c r="M35">
-        <v>14.6995695</v>
+        <v>15.145011</v>
       </c>
       <c r="N35">
-        <v>60.0004305</v>
+        <v>59.55498900000001</v>
       </c>
       <c r="O35">
-        <v>20.40014637</v>
+        <v>20.24869626</v>
       </c>
       <c r="P35">
-        <v>39.60028413</v>
+        <v>39.30629274</v>
       </c>
       <c r="Q35">
-        <v>64.90028412999999</v>
+        <v>64.60629274</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1695554851510359</v>
+        <v>0.1709494419560712</v>
       </c>
       <c r="T35">
-        <v>1.612948837211798</v>
+        <v>1.631116767344844</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.081781476661612</v>
+        <v>4.93231731558333</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.125235951691007</v>
+        <v>0.1248253883308199</v>
       </c>
       <c r="C36">
-        <v>613.8139133873002</v>
+        <v>609.9483478978289</v>
       </c>
       <c r="D36">
-        <v>806.3839133873003</v>
+        <v>810.573347897829</v>
       </c>
       <c r="E36">
-        <v>112.57</v>
+        <v>120.625</v>
       </c>
       <c r="F36">
-        <v>273.87</v>
+        <v>281.925</v>
       </c>
       <c r="G36">
         <v>81.3</v>
@@ -4233,28 +4233,28 @@
         <v>74.7</v>
       </c>
       <c r="M36">
-        <v>15.145011</v>
+        <v>15.5904525</v>
       </c>
       <c r="N36">
-        <v>59.55498900000001</v>
+        <v>59.10954750000001</v>
       </c>
       <c r="O36">
-        <v>20.24869626</v>
+        <v>20.09724615</v>
       </c>
       <c r="P36">
-        <v>39.30629274</v>
+        <v>39.01230135</v>
       </c>
       <c r="Q36">
-        <v>64.60629274</v>
+        <v>64.31230135</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1709494419560712</v>
+        <v>0.172386289739723</v>
       </c>
       <c r="T36">
-        <v>1.631116767344844</v>
+        <v>1.649843710712753</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.93231731558333</v>
+        <v>4.79139396370952</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1248253883308199</v>
+        <v>0.1244148249706329</v>
       </c>
       <c r="C37">
-        <v>609.9483478978289</v>
+        <v>606.1265407786284</v>
       </c>
       <c r="D37">
-        <v>810.573347897829</v>
+        <v>814.8065407786285</v>
       </c>
       <c r="E37">
-        <v>120.625</v>
+        <v>128.68</v>
       </c>
       <c r="F37">
-        <v>281.925</v>
+        <v>289.98</v>
       </c>
       <c r="G37">
         <v>81.3</v>
@@ -4315,28 +4315,28 @@
         <v>74.7</v>
       </c>
       <c r="M37">
-        <v>15.5904525</v>
+        <v>16.035894</v>
       </c>
       <c r="N37">
-        <v>59.10954750000001</v>
+        <v>58.664106</v>
       </c>
       <c r="O37">
-        <v>20.09724615</v>
+        <v>19.94579604</v>
       </c>
       <c r="P37">
-        <v>39.01230135</v>
+        <v>38.71830996</v>
       </c>
       <c r="Q37">
-        <v>64.31230135</v>
+        <v>64.01830996</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.172386289739723</v>
+        <v>0.1738680390166139</v>
       </c>
       <c r="T37">
-        <v>1.649843710712753</v>
+        <v>1.669155871060909</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.79139396370952</v>
+        <v>4.658299686939811</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1244148249706329</v>
+        <v>0.1240042616104459</v>
       </c>
       <c r="C38">
-        <v>606.1265407786284</v>
+        <v>602.3491812089009</v>
       </c>
       <c r="D38">
-        <v>814.8065407786285</v>
+        <v>819.0841812089009</v>
       </c>
       <c r="E38">
-        <v>128.6799999999999</v>
+        <v>136.735</v>
       </c>
       <c r="F38">
-        <v>289.98</v>
+        <v>298.035</v>
       </c>
       <c r="G38">
         <v>81.3</v>
@@ -4397,28 +4397,28 @@
         <v>74.7</v>
       </c>
       <c r="M38">
-        <v>16.035894</v>
+        <v>16.4813355</v>
       </c>
       <c r="N38">
-        <v>58.664106</v>
+        <v>58.2186645</v>
       </c>
       <c r="O38">
-        <v>19.94579604</v>
+        <v>19.79434593</v>
       </c>
       <c r="P38">
-        <v>38.71830996</v>
+        <v>38.42431857</v>
       </c>
       <c r="Q38">
-        <v>64.01830996</v>
+        <v>63.72431856999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1738680390166139</v>
+        <v>0.1753968279530887</v>
       </c>
       <c r="T38">
-        <v>1.669155871060908</v>
+        <v>1.689081115864561</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.658299686939811</v>
+        <v>4.532399695400898</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1240042616104459</v>
+        <v>0.1242206982502588</v>
       </c>
       <c r="C39">
-        <v>602.3491812089009</v>
+        <v>592.033555738071</v>
       </c>
       <c r="D39">
-        <v>819.0841812089009</v>
+        <v>816.823555738071</v>
       </c>
       <c r="E39">
-        <v>136.735</v>
+        <v>144.79</v>
       </c>
       <c r="F39">
-        <v>298.035</v>
+        <v>306.09</v>
       </c>
       <c r="G39">
         <v>81.3</v>
@@ -4479,45 +4479,45 @@
         <v>74.7</v>
       </c>
       <c r="M39">
-        <v>16.4813355</v>
+        <v>17.692002</v>
       </c>
       <c r="N39">
-        <v>58.2186645</v>
+        <v>57.007998</v>
       </c>
       <c r="O39">
-        <v>19.79434593</v>
+        <v>19.38271932</v>
       </c>
       <c r="P39">
-        <v>38.42431857</v>
+        <v>37.62527867999999</v>
       </c>
       <c r="Q39">
-        <v>63.72431856999999</v>
+        <v>62.92527867999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1753968279530887</v>
+        <v>0.1769749326617078</v>
       </c>
       <c r="T39">
-        <v>1.689081115864561</v>
+        <v>1.70964911050059</v>
       </c>
       <c r="U39">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V39">
         <v>0.34</v>
       </c>
       <c r="W39">
-        <v>0.036498</v>
+        <v>0.038148</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.532399695400898</v>
+        <v>4.222246866126286</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1242206982502588</v>
+        <v>0.1238266348900718</v>
       </c>
       <c r="C40">
-        <v>592.033555738071</v>
+        <v>588.1038167532047</v>
       </c>
       <c r="D40">
-        <v>816.823555738071</v>
+        <v>820.9488167532047</v>
       </c>
       <c r="E40">
-        <v>144.79</v>
+        <v>152.845</v>
       </c>
       <c r="F40">
-        <v>306.09</v>
+        <v>314.145</v>
       </c>
       <c r="G40">
         <v>81.3</v>
@@ -4561,28 +4561,28 @@
         <v>74.7</v>
       </c>
       <c r="M40">
-        <v>17.692002</v>
+        <v>18.157581</v>
       </c>
       <c r="N40">
-        <v>57.007998</v>
+        <v>56.542419</v>
       </c>
       <c r="O40">
-        <v>19.38271932</v>
+        <v>19.22442246</v>
       </c>
       <c r="P40">
-        <v>37.62527867999999</v>
+        <v>37.31799654</v>
       </c>
       <c r="Q40">
-        <v>62.92527867999999</v>
+        <v>62.61799653999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1769749326617078</v>
+        <v>0.1786047785083144</v>
       </c>
       <c r="T40">
-        <v>1.70964911050059</v>
+        <v>1.730891465616489</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.222246866126286</v>
+        <v>4.113984125969202</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1238266348900718</v>
+        <v>0.1234325715298847</v>
       </c>
       <c r="C41">
-        <v>588.1038167532047</v>
+        <v>584.2159574635547</v>
       </c>
       <c r="D41">
-        <v>820.9488167532047</v>
+        <v>825.1159574635548</v>
       </c>
       <c r="E41">
-        <v>152.845</v>
+        <v>160.9</v>
       </c>
       <c r="F41">
-        <v>314.145</v>
+        <v>322.2</v>
       </c>
       <c r="G41">
         <v>81.3</v>
@@ -4643,28 +4643,28 @@
         <v>74.7</v>
       </c>
       <c r="M41">
-        <v>18.157581</v>
+        <v>18.62316000000001</v>
       </c>
       <c r="N41">
-        <v>56.542419</v>
+        <v>56.07684</v>
       </c>
       <c r="O41">
-        <v>19.22442246</v>
+        <v>19.0661256</v>
       </c>
       <c r="P41">
-        <v>37.31799654</v>
+        <v>37.0107144</v>
       </c>
       <c r="Q41">
-        <v>62.61799653999999</v>
+        <v>62.31071439999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1786047785083144</v>
+        <v>0.1802889525498079</v>
       </c>
       <c r="T41">
-        <v>1.730891465616489</v>
+        <v>1.75284189923625</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.113984125969202</v>
+        <v>4.011134522819972</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1234325715298847</v>
+        <v>0.1239856081696977</v>
       </c>
       <c r="C42">
-        <v>584.2159574635547</v>
+        <v>570.3245974574875</v>
       </c>
       <c r="D42">
-        <v>825.1159574635548</v>
+        <v>819.2795974574875</v>
       </c>
       <c r="E42">
-        <v>160.9</v>
+        <v>168.955</v>
       </c>
       <c r="F42">
-        <v>322.2</v>
+        <v>330.2550000000001</v>
       </c>
       <c r="G42">
         <v>81.3</v>
@@ -4725,45 +4725,45 @@
         <v>74.7</v>
       </c>
       <c r="M42">
-        <v>18.62316000000001</v>
+        <v>20.2446315</v>
       </c>
       <c r="N42">
-        <v>56.07684</v>
+        <v>54.4553685</v>
       </c>
       <c r="O42">
-        <v>19.0661256</v>
+        <v>18.51482529</v>
       </c>
       <c r="P42">
-        <v>37.0107144</v>
+        <v>35.94054321</v>
       </c>
       <c r="Q42">
-        <v>62.31071439999999</v>
+        <v>61.24054321</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1802889525498079</v>
+        <v>0.1820302172367757</v>
       </c>
       <c r="T42">
-        <v>1.75284189923625</v>
+        <v>1.775536415351597</v>
       </c>
       <c r="U42">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V42">
         <v>0.34</v>
       </c>
       <c r="W42">
-        <v>0.038148</v>
+        <v>0.04045799999999999</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.011134522819972</v>
+        <v>3.689867113659243</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1239856081696977</v>
+        <v>0.1236146448095106</v>
       </c>
       <c r="C43">
-        <v>570.3245974574875</v>
+        <v>566.1753238557702</v>
       </c>
       <c r="D43">
-        <v>819.2795974574875</v>
+        <v>823.1853238557703</v>
       </c>
       <c r="E43">
-        <v>168.955</v>
+        <v>177.01</v>
       </c>
       <c r="F43">
-        <v>330.2550000000001</v>
+        <v>338.3100000000001</v>
       </c>
       <c r="G43">
         <v>81.3</v>
@@ -4807,28 +4807,28 @@
         <v>74.7</v>
       </c>
       <c r="M43">
-        <v>20.2446315</v>
+        <v>20.73840300000001</v>
       </c>
       <c r="N43">
-        <v>54.4553685</v>
+        <v>53.961597</v>
       </c>
       <c r="O43">
-        <v>18.51482529</v>
+        <v>18.34694298</v>
       </c>
       <c r="P43">
-        <v>35.94054321</v>
+        <v>35.61465402</v>
       </c>
       <c r="Q43">
-        <v>61.24054321</v>
+        <v>60.91465401999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1820302172367757</v>
+        <v>0.183831525533639</v>
       </c>
       <c r="T43">
-        <v>1.775536415351597</v>
+        <v>1.799013500988163</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.689867113659243</v>
+        <v>3.602013134762594</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1236146448095106</v>
+        <v>0.1232436814493236</v>
       </c>
       <c r="C44">
-        <v>566.1753238557701</v>
+        <v>562.0634679325922</v>
       </c>
       <c r="D44">
-        <v>823.1853238557702</v>
+        <v>827.1284679325922</v>
       </c>
       <c r="E44">
-        <v>177.01</v>
+        <v>185.065</v>
       </c>
       <c r="F44">
-        <v>338.31</v>
+        <v>346.365</v>
       </c>
       <c r="G44">
         <v>81.3</v>
@@ -4889,28 +4889,28 @@
         <v>74.7</v>
       </c>
       <c r="M44">
-        <v>20.738403</v>
+        <v>21.2321745</v>
       </c>
       <c r="N44">
-        <v>53.961597</v>
+        <v>53.4678255</v>
       </c>
       <c r="O44">
-        <v>18.34694298</v>
+        <v>18.17906067</v>
       </c>
       <c r="P44">
-        <v>35.61465402</v>
+        <v>35.28876483000001</v>
       </c>
       <c r="Q44">
-        <v>60.91465401999999</v>
+        <v>60.58876483</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.183831525533639</v>
+        <v>0.1856960376303922</v>
       </c>
       <c r="T44">
-        <v>1.799013500988163</v>
+        <v>1.823314344015486</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.602013134762594</v>
+        <v>3.518245387442535</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1232436814493236</v>
+        <v>0.1236858380891365</v>
       </c>
       <c r="C45">
-        <v>562.0634679325922</v>
+        <v>549.3128730330911</v>
       </c>
       <c r="D45">
-        <v>827.1284679325922</v>
+        <v>822.4328730330913</v>
       </c>
       <c r="E45">
-        <v>185.065</v>
+        <v>193.12</v>
       </c>
       <c r="F45">
-        <v>346.365</v>
+        <v>354.42</v>
       </c>
       <c r="G45">
         <v>81.3</v>
@@ -4971,45 +4971,45 @@
         <v>74.7</v>
       </c>
       <c r="M45">
-        <v>21.2321745</v>
+        <v>22.718322</v>
       </c>
       <c r="N45">
-        <v>53.4678255</v>
+        <v>51.981678</v>
       </c>
       <c r="O45">
-        <v>18.17906067</v>
+        <v>17.67377052</v>
       </c>
       <c r="P45">
-        <v>35.28876483000001</v>
+        <v>34.30790748</v>
       </c>
       <c r="Q45">
-        <v>60.58876483</v>
+        <v>59.60790747999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1856960376303922</v>
+        <v>0.1876271394448867</v>
       </c>
       <c r="T45">
-        <v>1.823314344015486</v>
+        <v>1.848483074293784</v>
       </c>
       <c r="U45">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V45">
         <v>0.34</v>
       </c>
       <c r="W45">
-        <v>0.04045799999999999</v>
+        <v>0.042306</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.518245387442535</v>
+        <v>3.28809495701311</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1236858380891365</v>
+        <v>0.1233333547289495</v>
       </c>
       <c r="C46">
-        <v>549.3128730330911</v>
+        <v>544.9968303325456</v>
       </c>
       <c r="D46">
-        <v>822.4328730330913</v>
+        <v>826.1718303325457</v>
       </c>
       <c r="E46">
-        <v>193.12</v>
+        <v>201.175</v>
       </c>
       <c r="F46">
-        <v>354.42</v>
+        <v>362.475</v>
       </c>
       <c r="G46">
         <v>81.3</v>
@@ -5053,28 +5053,28 @@
         <v>74.7</v>
       </c>
       <c r="M46">
-        <v>22.718322</v>
+        <v>23.2346475</v>
       </c>
       <c r="N46">
-        <v>51.981678</v>
+        <v>51.4653525</v>
       </c>
       <c r="O46">
-        <v>17.67377052</v>
+        <v>17.49821985</v>
       </c>
       <c r="P46">
-        <v>34.30790748</v>
+        <v>33.96713265</v>
       </c>
       <c r="Q46">
-        <v>59.60790747999999</v>
+        <v>59.26713264999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1876271394448867</v>
+        <v>0.1896284631435445</v>
       </c>
       <c r="T46">
-        <v>1.848483074293784</v>
+        <v>1.874567031127657</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.28809495701311</v>
+        <v>3.215026180190597</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1233333547289495</v>
+        <v>0.1229808713687625</v>
       </c>
       <c r="C47">
-        <v>544.9968303325456</v>
+        <v>540.7149391052635</v>
       </c>
       <c r="D47">
-        <v>826.1718303325457</v>
+        <v>829.9449391052636</v>
       </c>
       <c r="E47">
-        <v>201.175</v>
+        <v>209.23</v>
       </c>
       <c r="F47">
-        <v>362.475</v>
+        <v>370.53</v>
       </c>
       <c r="G47">
         <v>81.3</v>
@@ -5135,28 +5135,28 @@
         <v>74.7</v>
       </c>
       <c r="M47">
-        <v>23.2346475</v>
+        <v>23.750973</v>
       </c>
       <c r="N47">
-        <v>51.4653525</v>
+        <v>50.949027</v>
       </c>
       <c r="O47">
-        <v>17.49821985</v>
+        <v>17.32266918</v>
       </c>
       <c r="P47">
-        <v>33.96713265</v>
+        <v>33.62635782</v>
       </c>
       <c r="Q47">
-        <v>59.26713264999999</v>
+        <v>58.92635781999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1896284631435445</v>
+        <v>0.1917039099421527</v>
       </c>
       <c r="T47">
-        <v>1.874567031127657</v>
+        <v>1.901617060436858</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.215026180190597</v>
+        <v>3.145134306708192</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1229808713687625</v>
+        <v>0.1226283880085754</v>
       </c>
       <c r="C48">
-        <v>540.7149391052635</v>
+        <v>536.4676694050769</v>
       </c>
       <c r="D48">
-        <v>829.9449391052636</v>
+        <v>833.752669405077</v>
       </c>
       <c r="E48">
-        <v>209.23</v>
+        <v>217.285</v>
       </c>
       <c r="F48">
-        <v>370.53</v>
+        <v>378.585</v>
       </c>
       <c r="G48">
         <v>81.3</v>
@@ -5217,28 +5217,28 @@
         <v>74.7</v>
       </c>
       <c r="M48">
-        <v>23.750973</v>
+        <v>24.2672985</v>
       </c>
       <c r="N48">
-        <v>50.949027</v>
+        <v>50.4327015</v>
       </c>
       <c r="O48">
-        <v>17.32266918</v>
+        <v>17.14711851</v>
       </c>
       <c r="P48">
-        <v>33.62635782</v>
+        <v>33.28558298999999</v>
       </c>
       <c r="Q48">
-        <v>58.92635781999999</v>
+        <v>58.58558298999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1917039099421527</v>
+        <v>0.1938576754878781</v>
       </c>
       <c r="T48">
-        <v>1.901617060436858</v>
+        <v>1.929687845569048</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.145134306708192</v>
+        <v>3.078216555501635</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1226283880085754</v>
+        <v>0.1222759046483883</v>
       </c>
       <c r="C49">
-        <v>536.4676694050769</v>
+        <v>532.2554999518745</v>
       </c>
       <c r="D49">
-        <v>833.752669405077</v>
+        <v>837.5954999518747</v>
       </c>
       <c r="E49">
-        <v>217.285</v>
+        <v>225.34</v>
       </c>
       <c r="F49">
-        <v>378.585</v>
+        <v>386.64</v>
       </c>
       <c r="G49">
         <v>81.3</v>
@@ -5299,28 +5299,28 @@
         <v>74.7</v>
       </c>
       <c r="M49">
-        <v>24.2672985</v>
+        <v>24.783624</v>
       </c>
       <c r="N49">
-        <v>50.4327015</v>
+        <v>49.916376</v>
       </c>
       <c r="O49">
-        <v>17.14711851</v>
+        <v>16.97156784</v>
       </c>
       <c r="P49">
-        <v>33.28558298999999</v>
+        <v>32.94480815999999</v>
       </c>
       <c r="Q49">
-        <v>58.58558298999999</v>
+        <v>58.24480815999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1938576754878781</v>
+        <v>0.1960942781699776</v>
       </c>
       <c r="T49">
-        <v>1.929687845569048</v>
+        <v>1.958838276283246</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.078216555501635</v>
+        <v>3.014087043928684</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1222759046483883</v>
+        <v>0.1244459412882013</v>
       </c>
       <c r="C50">
-        <v>532.2554999518749</v>
+        <v>501.0891620434465</v>
       </c>
       <c r="D50">
-        <v>837.5954999518749</v>
+        <v>814.4841620434465</v>
       </c>
       <c r="E50">
-        <v>225.34</v>
+        <v>233.395</v>
       </c>
       <c r="F50">
-        <v>386.64</v>
+        <v>394.695</v>
       </c>
       <c r="G50">
         <v>81.3</v>
@@ -5381,45 +5381,45 @@
         <v>74.7</v>
       </c>
       <c r="M50">
-        <v>24.783624</v>
+        <v>28.3785705</v>
       </c>
       <c r="N50">
-        <v>49.916376</v>
+        <v>46.3214295</v>
       </c>
       <c r="O50">
-        <v>16.97156784</v>
+        <v>15.74928603</v>
       </c>
       <c r="P50">
-        <v>32.94480815999999</v>
+        <v>30.57214347</v>
       </c>
       <c r="Q50">
-        <v>58.24480815999999</v>
+        <v>55.87214347</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1960942781699776</v>
+        <v>0.198418590761179</v>
       </c>
       <c r="T50">
-        <v>1.958838276283245</v>
+        <v>1.989131861143098</v>
       </c>
       <c r="U50">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V50">
         <v>0.34</v>
       </c>
       <c r="W50">
-        <v>0.042306</v>
+        <v>0.047454</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.014087043928685</v>
+        <v>2.632267893832073</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1244459412882013</v>
+        <v>0.1241449379280143</v>
       </c>
       <c r="C51">
-        <v>501.0891620434465</v>
+        <v>496.1634321160003</v>
       </c>
       <c r="D51">
-        <v>814.4841620434465</v>
+        <v>817.6134321160004</v>
       </c>
       <c r="E51">
-        <v>233.395</v>
+        <v>241.45</v>
       </c>
       <c r="F51">
-        <v>394.695</v>
+        <v>402.75</v>
       </c>
       <c r="G51">
         <v>81.3</v>
@@ -5463,28 +5463,28 @@
         <v>74.7</v>
       </c>
       <c r="M51">
-        <v>28.3785705</v>
+        <v>28.957725</v>
       </c>
       <c r="N51">
-        <v>46.3214295</v>
+        <v>45.742275</v>
       </c>
       <c r="O51">
-        <v>15.74928603</v>
+        <v>15.5523735</v>
       </c>
       <c r="P51">
-        <v>30.57214347</v>
+        <v>30.1899015</v>
       </c>
       <c r="Q51">
-        <v>55.87214347</v>
+        <v>55.48990149999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.198418590761179</v>
+        <v>0.2008358758560285</v>
       </c>
       <c r="T51">
-        <v>1.989131861143098</v>
+        <v>2.020637189397344</v>
       </c>
       <c r="U51">
         <v>0.07190000000000001</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.632267893832073</v>
+        <v>2.579622535955432</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1241449379280143</v>
+        <v>0.1238439345678272</v>
       </c>
       <c r="C52">
-        <v>496.1634321160003</v>
+        <v>491.2618404079296</v>
       </c>
       <c r="D52">
-        <v>817.6134321160004</v>
+        <v>820.7668404079296</v>
       </c>
       <c r="E52">
-        <v>241.45</v>
+        <v>249.505</v>
       </c>
       <c r="F52">
-        <v>402.75</v>
+        <v>410.805</v>
       </c>
       <c r="G52">
         <v>81.3</v>
@@ -5545,28 +5545,28 @@
         <v>74.7</v>
       </c>
       <c r="M52">
-        <v>28.957725</v>
+        <v>29.5368795</v>
       </c>
       <c r="N52">
-        <v>45.742275</v>
+        <v>45.16312050000001</v>
       </c>
       <c r="O52">
-        <v>15.5523735</v>
+        <v>15.35546097</v>
       </c>
       <c r="P52">
-        <v>30.1899015</v>
+        <v>29.80765953</v>
       </c>
       <c r="Q52">
-        <v>55.48990149999999</v>
+        <v>55.10765953</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2008358758560285</v>
+        <v>0.203351825648627</v>
       </c>
       <c r="T52">
-        <v>2.020637189397344</v>
+        <v>2.05342844941707</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.579622535955432</v>
+        <v>2.52904170191709</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1238439345678272</v>
+        <v>0.1248814112076402</v>
       </c>
       <c r="C53">
-        <v>491.2618404079296</v>
+        <v>472.4391212859163</v>
       </c>
       <c r="D53">
-        <v>820.7668404079296</v>
+        <v>809.9991212859163</v>
       </c>
       <c r="E53">
-        <v>249.505</v>
+        <v>257.56</v>
       </c>
       <c r="F53">
-        <v>410.805</v>
+        <v>418.86</v>
       </c>
       <c r="G53">
         <v>81.3</v>
@@ -5627,45 +5627,45 @@
         <v>74.7</v>
       </c>
       <c r="M53">
-        <v>29.5368795</v>
+        <v>31.749588</v>
       </c>
       <c r="N53">
-        <v>45.16312050000001</v>
+        <v>42.950412</v>
       </c>
       <c r="O53">
-        <v>15.35546097</v>
+        <v>14.60314008</v>
       </c>
       <c r="P53">
-        <v>29.80765953</v>
+        <v>28.34727192</v>
       </c>
       <c r="Q53">
-        <v>55.10765953</v>
+        <v>53.64727191999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.203351825648627</v>
+        <v>0.2059726066825837</v>
       </c>
       <c r="T53">
-        <v>2.05342844941707</v>
+        <v>2.087586011937618</v>
       </c>
       <c r="U53">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V53">
         <v>0.34</v>
       </c>
       <c r="W53">
-        <v>0.047454</v>
+        <v>0.050028</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.52904170191709</v>
+        <v>2.352786436157849</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1248814112076402</v>
+        <v>0.1246061478474531</v>
       </c>
       <c r="C54">
-        <v>472.4391212859163</v>
+        <v>467.2133812607258</v>
       </c>
       <c r="D54">
-        <v>809.9991212859163</v>
+        <v>812.8283812607259</v>
       </c>
       <c r="E54">
-        <v>257.56</v>
+        <v>265.615</v>
       </c>
       <c r="F54">
-        <v>418.86</v>
+        <v>426.915</v>
       </c>
       <c r="G54">
         <v>81.3</v>
@@ -5709,28 +5709,28 @@
         <v>74.7</v>
       </c>
       <c r="M54">
-        <v>31.749588</v>
+        <v>32.360157</v>
       </c>
       <c r="N54">
-        <v>42.950412</v>
+        <v>42.339843</v>
       </c>
       <c r="O54">
-        <v>14.60314008</v>
+        <v>14.39554662</v>
       </c>
       <c r="P54">
-        <v>28.34727192</v>
+        <v>27.94429638</v>
       </c>
       <c r="Q54">
-        <v>53.64727191999999</v>
+        <v>53.24429637999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2059726066825837</v>
+        <v>0.20870491031373</v>
       </c>
       <c r="T54">
-        <v>2.087586011937618</v>
+        <v>2.123197087756912</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.352786436157849</v>
+        <v>2.30839423924921</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1246061478474531</v>
+        <v>0.1243308844872661</v>
       </c>
       <c r="C55">
-        <v>467.2133812607258</v>
+        <v>462.0074752565724</v>
       </c>
       <c r="D55">
-        <v>812.8283812607259</v>
+        <v>815.6774752565725</v>
       </c>
       <c r="E55">
-        <v>265.615</v>
+        <v>273.67</v>
       </c>
       <c r="F55">
-        <v>426.915</v>
+        <v>434.97</v>
       </c>
       <c r="G55">
         <v>81.3</v>
@@ -5791,28 +5791,28 @@
         <v>74.7</v>
       </c>
       <c r="M55">
-        <v>32.360157</v>
+        <v>32.97072600000001</v>
       </c>
       <c r="N55">
-        <v>42.339843</v>
+        <v>41.729274</v>
       </c>
       <c r="O55">
-        <v>14.39554662</v>
+        <v>14.18795316</v>
       </c>
       <c r="P55">
-        <v>27.94429638</v>
+        <v>27.54132084</v>
       </c>
       <c r="Q55">
-        <v>53.24429637999999</v>
+        <v>52.84132083999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.20870491031373</v>
+        <v>0.2115560097549262</v>
       </c>
       <c r="T55">
-        <v>2.123197087756912</v>
+        <v>2.160356471220524</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.30839423924921</v>
+        <v>2.265646197781632</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1243308844872661</v>
+        <v>0.124055621127079</v>
       </c>
       <c r="C56">
-        <v>462.0074752565724</v>
+        <v>456.821612571366</v>
       </c>
       <c r="D56">
-        <v>815.6774752565725</v>
+        <v>818.546612571366</v>
       </c>
       <c r="E56">
-        <v>273.67</v>
+        <v>281.725</v>
       </c>
       <c r="F56">
-        <v>434.97</v>
+        <v>443.025</v>
       </c>
       <c r="G56">
         <v>81.3</v>
@@ -5873,28 +5873,28 @@
         <v>74.7</v>
       </c>
       <c r="M56">
-        <v>32.97072600000001</v>
+        <v>33.581295</v>
       </c>
       <c r="N56">
-        <v>41.729274</v>
+        <v>41.118705</v>
       </c>
       <c r="O56">
-        <v>14.18795316</v>
+        <v>13.9803597</v>
       </c>
       <c r="P56">
-        <v>27.54132084</v>
+        <v>27.1383453</v>
       </c>
       <c r="Q56">
-        <v>52.84132083999999</v>
+        <v>52.43834529999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2115560097549262</v>
+        <v>0.2145338247268423</v>
       </c>
       <c r="T56">
-        <v>2.160356471220524</v>
+        <v>2.199167382838073</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.265646197781632</v>
+        <v>2.224452630549239</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.124055621127079</v>
+        <v>0.123780357766892</v>
       </c>
       <c r="C57">
-        <v>456.821612571366</v>
+        <v>451.6560054582213</v>
       </c>
       <c r="D57">
-        <v>818.546612571366</v>
+        <v>821.4360054582214</v>
       </c>
       <c r="E57">
-        <v>281.725</v>
+        <v>289.78</v>
       </c>
       <c r="F57">
-        <v>443.025</v>
+        <v>451.08</v>
       </c>
       <c r="G57">
         <v>81.3</v>
@@ -5955,28 +5955,28 @@
         <v>74.7</v>
       </c>
       <c r="M57">
-        <v>33.581295</v>
+        <v>34.191864</v>
       </c>
       <c r="N57">
-        <v>41.118705</v>
+        <v>40.508136</v>
       </c>
       <c r="O57">
-        <v>13.9803597</v>
+        <v>13.77276624</v>
       </c>
       <c r="P57">
-        <v>27.1383453</v>
+        <v>26.73536976</v>
       </c>
       <c r="Q57">
-        <v>52.43834529999999</v>
+        <v>52.03536975999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2145338247268423</v>
+        <v>0.2176469949247545</v>
       </c>
       <c r="T57">
-        <v>2.199167382838073</v>
+        <v>2.239742426801876</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.224452630549239</v>
+        <v>2.184730262146574</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.123780357766892</v>
+        <v>0.1235050944067049</v>
       </c>
       <c r="C58">
-        <v>451.6560054582213</v>
+        <v>446.510869177807</v>
       </c>
       <c r="D58">
-        <v>821.4360054582214</v>
+        <v>824.3458691778071</v>
       </c>
       <c r="E58">
-        <v>289.78</v>
+        <v>297.835</v>
       </c>
       <c r="F58">
-        <v>451.08</v>
+        <v>459.135</v>
       </c>
       <c r="G58">
         <v>81.3</v>
@@ -6037,28 +6037,28 @@
         <v>74.7</v>
       </c>
       <c r="M58">
-        <v>34.191864</v>
+        <v>34.80243300000001</v>
       </c>
       <c r="N58">
-        <v>40.508136</v>
+        <v>39.897567</v>
       </c>
       <c r="O58">
-        <v>13.77276624</v>
+        <v>13.56517278</v>
       </c>
       <c r="P58">
-        <v>26.73536976</v>
+        <v>26.33239422</v>
       </c>
       <c r="Q58">
-        <v>52.03536975999999</v>
+        <v>51.63239421999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2176469949247545</v>
+        <v>0.2209049637365231</v>
       </c>
       <c r="T58">
-        <v>2.239742426801876</v>
+        <v>2.282204682112831</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.184730262146574</v>
+        <v>2.146401661056283</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1235050944067049</v>
+        <v>0.1232298310465179</v>
       </c>
       <c r="C59">
-        <v>446.510869177807</v>
+        <v>441.3864220518007</v>
       </c>
       <c r="D59">
-        <v>824.3458691778071</v>
+        <v>827.2764220518008</v>
       </c>
       <c r="E59">
-        <v>297.835</v>
+        <v>305.89</v>
       </c>
       <c r="F59">
-        <v>459.135</v>
+        <v>467.1900000000001</v>
       </c>
       <c r="G59">
         <v>81.3</v>
@@ -6119,28 +6119,28 @@
         <v>74.7</v>
       </c>
       <c r="M59">
-        <v>34.80243300000001</v>
+        <v>35.41300200000001</v>
       </c>
       <c r="N59">
-        <v>39.897567</v>
+        <v>39.286998</v>
       </c>
       <c r="O59">
-        <v>13.56517278</v>
+        <v>13.35757932</v>
       </c>
       <c r="P59">
-        <v>26.33239422</v>
+        <v>25.92941868</v>
       </c>
       <c r="Q59">
-        <v>51.63239421999999</v>
+        <v>51.22941867999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2209049637365231</v>
+        <v>0.2243180739202807</v>
       </c>
       <c r="T59">
-        <v>2.282204682112831</v>
+        <v>2.326688949581452</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.146401661056283</v>
+        <v>2.109394735865657</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1232298310465179</v>
+        <v>0.1229545676863308</v>
       </c>
       <c r="C60">
-        <v>441.3864220518005</v>
+        <v>436.282885517493</v>
       </c>
       <c r="D60">
-        <v>827.2764220518005</v>
+        <v>830.227885517493</v>
       </c>
       <c r="E60">
-        <v>305.8899999999999</v>
+        <v>313.9449999999999</v>
       </c>
       <c r="F60">
-        <v>467.1899999999999</v>
+        <v>475.2449999999999</v>
       </c>
       <c r="G60">
         <v>81.3</v>
@@ -6201,28 +6201,28 @@
         <v>74.7</v>
       </c>
       <c r="M60">
-        <v>35.413002</v>
+        <v>36.023571</v>
       </c>
       <c r="N60">
-        <v>39.286998</v>
+        <v>38.67642900000001</v>
       </c>
       <c r="O60">
-        <v>13.35757932</v>
+        <v>13.14998586</v>
       </c>
       <c r="P60">
-        <v>25.92941868</v>
+        <v>25.52644314</v>
       </c>
       <c r="Q60">
-        <v>51.22941867999999</v>
+        <v>50.82644314</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2243180739202807</v>
+        <v>0.2278976772837337</v>
       </c>
       <c r="T60">
-        <v>2.326688949581451</v>
+        <v>2.373343181316833</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.109394735865658</v>
+        <v>2.073642282715392</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1229545676863308</v>
+        <v>0.1226793043261438</v>
       </c>
       <c r="C61">
-        <v>436.282885517493</v>
+        <v>431.2004841835662</v>
       </c>
       <c r="D61">
-        <v>830.227885517493</v>
+        <v>833.2004841835662</v>
       </c>
       <c r="E61">
-        <v>313.9449999999999</v>
+        <v>321.9999999999999</v>
       </c>
       <c r="F61">
-        <v>475.2449999999999</v>
+        <v>483.3</v>
       </c>
       <c r="G61">
         <v>81.3</v>
@@ -6283,28 +6283,28 @@
         <v>74.7</v>
       </c>
       <c r="M61">
-        <v>36.023571</v>
+        <v>36.63414</v>
       </c>
       <c r="N61">
-        <v>38.67642900000001</v>
+        <v>38.06586</v>
       </c>
       <c r="O61">
-        <v>13.14998586</v>
+        <v>12.9423924</v>
       </c>
       <c r="P61">
-        <v>25.52644314</v>
+        <v>25.1234676</v>
       </c>
       <c r="Q61">
-        <v>50.82644314</v>
+        <v>50.4234676</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2278976772837337</v>
+        <v>0.2316562608153594</v>
       </c>
       <c r="T61">
-        <v>2.373343181316833</v>
+        <v>2.422330124638985</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.073642282715392</v>
+        <v>2.039081578003469</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1226793043261438</v>
+        <v>0.1224040409659568</v>
       </c>
       <c r="C62">
-        <v>431.2004841835662</v>
+        <v>426.1394458870716</v>
       </c>
       <c r="D62">
-        <v>833.2004841835662</v>
+        <v>836.1944458870717</v>
       </c>
       <c r="E62">
-        <v>321.9999999999999</v>
+        <v>330.0549999999999</v>
       </c>
       <c r="F62">
-        <v>483.3</v>
+        <v>491.355</v>
       </c>
       <c r="G62">
         <v>81.3</v>
@@ -6365,28 +6365,28 @@
         <v>74.7</v>
       </c>
       <c r="M62">
-        <v>36.63414</v>
+        <v>37.244709</v>
       </c>
       <c r="N62">
-        <v>38.06586</v>
+        <v>37.455291</v>
       </c>
       <c r="O62">
-        <v>12.9423924</v>
+        <v>12.73479894</v>
       </c>
       <c r="P62">
-        <v>25.1234676</v>
+        <v>24.72049206</v>
       </c>
       <c r="Q62">
-        <v>50.4234676</v>
+        <v>50.02049206</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2316562608153594</v>
+        <v>0.2356075922204019</v>
       </c>
       <c r="T62">
-        <v>2.422330124638985</v>
+        <v>2.473829218900734</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.039081578003469</v>
+        <v>2.005654011150953</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1224040409659568</v>
+        <v>0.1279394176057697</v>
       </c>
       <c r="C63">
-        <v>426.1394458870716</v>
+        <v>361.733289073178</v>
       </c>
       <c r="D63">
-        <v>836.1944458870717</v>
+        <v>779.843289073178</v>
       </c>
       <c r="E63">
-        <v>330.0549999999999</v>
+        <v>338.11</v>
       </c>
       <c r="F63">
-        <v>491.355</v>
+        <v>499.41</v>
       </c>
       <c r="G63">
         <v>81.3</v>
@@ -6447,45 +6447,45 @@
         <v>74.7</v>
       </c>
       <c r="M63">
-        <v>37.244709</v>
+        <v>44.94689999999999</v>
       </c>
       <c r="N63">
-        <v>37.455291</v>
+        <v>29.75310000000001</v>
       </c>
       <c r="O63">
-        <v>12.73479894</v>
+        <v>10.116054</v>
       </c>
       <c r="P63">
-        <v>24.72049206</v>
+        <v>19.63704600000001</v>
       </c>
       <c r="Q63">
-        <v>50.02049206</v>
+        <v>44.937046</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2356075922204019</v>
+        <v>0.239766888436236</v>
       </c>
       <c r="T63">
-        <v>2.473829218900734</v>
+        <v>2.528038791807838</v>
       </c>
       <c r="U63">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V63">
         <v>0.34</v>
       </c>
       <c r="W63">
-        <v>0.050028</v>
+        <v>0.05939999999999999</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.005654011150953</v>
+        <v>1.661961114114656</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1279394176057697</v>
+        <v>0.1277578742455826</v>
       </c>
       <c r="C64">
-        <v>361.733289073178</v>
+        <v>355.405705412619</v>
       </c>
       <c r="D64">
-        <v>779.843289073178</v>
+        <v>781.5707054126191</v>
       </c>
       <c r="E64">
-        <v>338.11</v>
+        <v>346.165</v>
       </c>
       <c r="F64">
-        <v>499.41</v>
+        <v>507.465</v>
       </c>
       <c r="G64">
         <v>81.3</v>
@@ -6529,28 +6529,28 @@
         <v>74.7</v>
       </c>
       <c r="M64">
-        <v>44.94689999999999</v>
+        <v>45.67185</v>
       </c>
       <c r="N64">
-        <v>29.75310000000001</v>
+        <v>29.02815</v>
       </c>
       <c r="O64">
-        <v>10.116054</v>
+        <v>9.869571000000002</v>
       </c>
       <c r="P64">
-        <v>19.63704600000001</v>
+        <v>19.158579</v>
       </c>
       <c r="Q64">
-        <v>44.937046</v>
+        <v>44.458579</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.239766888436236</v>
+        <v>0.2441510114745477</v>
       </c>
       <c r="T64">
-        <v>2.528038791807838</v>
+        <v>2.58517861189911</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.661961114114656</v>
+        <v>1.635580778969978</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1277578742455826</v>
+        <v>0.1275763308853956</v>
       </c>
       <c r="C65">
-        <v>355.405705412619</v>
+        <v>349.0857914766195</v>
       </c>
       <c r="D65">
-        <v>781.5707054126191</v>
+        <v>783.3057914766196</v>
       </c>
       <c r="E65">
-        <v>346.165</v>
+        <v>354.22</v>
       </c>
       <c r="F65">
-        <v>507.465</v>
+        <v>515.52</v>
       </c>
       <c r="G65">
         <v>81.3</v>
@@ -6611,28 +6611,28 @@
         <v>74.7</v>
       </c>
       <c r="M65">
-        <v>45.67185</v>
+        <v>46.3968</v>
       </c>
       <c r="N65">
-        <v>29.02815</v>
+        <v>28.3032</v>
       </c>
       <c r="O65">
-        <v>9.869571000000002</v>
+        <v>9.623088000000003</v>
       </c>
       <c r="P65">
-        <v>19.158579</v>
+        <v>18.680112</v>
       </c>
       <c r="Q65">
-        <v>44.458579</v>
+        <v>43.980112</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2441510114745477</v>
+        <v>0.2487786969038767</v>
       </c>
       <c r="T65">
-        <v>2.58517861189911</v>
+        <v>2.645492866439897</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.635580778969978</v>
+        <v>1.610024829298572</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1275763308853956</v>
+        <v>0.1273947875252086</v>
       </c>
       <c r="C66">
-        <v>349.0857914766195</v>
+        <v>342.7735984591698</v>
       </c>
       <c r="D66">
-        <v>783.3057914766196</v>
+        <v>785.0485984591699</v>
       </c>
       <c r="E66">
-        <v>354.22</v>
+        <v>362.275</v>
       </c>
       <c r="F66">
-        <v>515.52</v>
+        <v>523.575</v>
       </c>
       <c r="G66">
         <v>81.3</v>
@@ -6693,28 +6693,28 @@
         <v>74.7</v>
       </c>
       <c r="M66">
-        <v>46.3968</v>
+        <v>47.12175000000001</v>
       </c>
       <c r="N66">
-        <v>28.3032</v>
+        <v>27.57825</v>
       </c>
       <c r="O66">
-        <v>9.623088000000003</v>
+        <v>9.376605</v>
       </c>
       <c r="P66">
-        <v>18.680112</v>
+        <v>18.201645</v>
       </c>
       <c r="Q66">
-        <v>43.980112</v>
+        <v>43.501645</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2487786969038767</v>
+        <v>0.2536708215005959</v>
       </c>
       <c r="T66">
-        <v>2.645492866439897</v>
+        <v>2.709253649811586</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.610024829298572</v>
+        <v>1.585255216540133</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1273947875252086</v>
+        <v>0.1272132441650215</v>
       </c>
       <c r="C67">
-        <v>342.7735984591698</v>
+        <v>336.4691780108892</v>
       </c>
       <c r="D67">
-        <v>785.0485984591699</v>
+        <v>786.7991780108892</v>
       </c>
       <c r="E67">
-        <v>362.275</v>
+        <v>370.33</v>
       </c>
       <c r="F67">
-        <v>523.575</v>
+        <v>531.63</v>
       </c>
       <c r="G67">
         <v>81.3</v>
@@ -6775,28 +6775,28 @@
         <v>74.7</v>
       </c>
       <c r="M67">
-        <v>47.12175000000001</v>
+        <v>47.8467</v>
       </c>
       <c r="N67">
-        <v>27.57825</v>
+        <v>26.8533</v>
       </c>
       <c r="O67">
-        <v>9.376605</v>
+        <v>9.130122000000002</v>
       </c>
       <c r="P67">
-        <v>18.201645</v>
+        <v>17.723178</v>
       </c>
       <c r="Q67">
-        <v>43.501645</v>
+        <v>43.023178</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2536708215005959</v>
+        <v>0.2588507181324162</v>
       </c>
       <c r="T67">
-        <v>2.709253649811586</v>
+        <v>2.776765067499256</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.585255216540133</v>
+        <v>1.561236198107707</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1272132441650215</v>
+        <v>0.1270317008048344</v>
       </c>
       <c r="C68">
-        <v>336.4691780108892</v>
+        <v>330.1725822441292</v>
       </c>
       <c r="D68">
-        <v>786.7991780108892</v>
+        <v>788.5575822441293</v>
       </c>
       <c r="E68">
-        <v>370.33</v>
+        <v>378.385</v>
       </c>
       <c r="F68">
-        <v>531.63</v>
+        <v>539.6850000000001</v>
       </c>
       <c r="G68">
         <v>81.3</v>
@@ -6857,28 +6857,28 @@
         <v>74.7</v>
       </c>
       <c r="M68">
-        <v>47.8467</v>
+        <v>48.57165000000001</v>
       </c>
       <c r="N68">
-        <v>26.8533</v>
+        <v>26.12835</v>
       </c>
       <c r="O68">
-        <v>9.130122000000002</v>
+        <v>8.883639000000001</v>
       </c>
       <c r="P68">
-        <v>17.723178</v>
+        <v>17.244711</v>
       </c>
       <c r="Q68">
-        <v>43.023178</v>
+        <v>42.54471099999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2588507181324162</v>
+        <v>0.2643445478934378</v>
       </c>
       <c r="T68">
-        <v>2.776765067499256</v>
+        <v>2.848368086258907</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.561236198107707</v>
+        <v>1.537934165300129</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1270317008048344</v>
+        <v>0.1268501574446474</v>
       </c>
       <c r="C69">
-        <v>330.1725822441292</v>
+        <v>323.8838637381454</v>
       </c>
       <c r="D69">
-        <v>788.5575822441293</v>
+        <v>790.3238637381454</v>
       </c>
       <c r="E69">
-        <v>378.385</v>
+        <v>386.44</v>
       </c>
       <c r="F69">
-        <v>539.6850000000001</v>
+        <v>547.74</v>
       </c>
       <c r="G69">
         <v>81.3</v>
@@ -6939,28 +6939,28 @@
         <v>74.7</v>
       </c>
       <c r="M69">
-        <v>48.57165000000001</v>
+        <v>49.2966</v>
       </c>
       <c r="N69">
-        <v>26.12835</v>
+        <v>25.4034</v>
       </c>
       <c r="O69">
-        <v>8.883639000000001</v>
+        <v>8.637156000000003</v>
       </c>
       <c r="P69">
-        <v>17.244711</v>
+        <v>16.766244</v>
       </c>
       <c r="Q69">
-        <v>42.54471099999999</v>
+        <v>42.066244</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2643445478934378</v>
+        <v>0.2701817420145232</v>
       </c>
       <c r="T69">
-        <v>2.848368086258907</v>
+        <v>2.924446293691036</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.537934165300129</v>
+        <v>1.515317486398656</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1268501574446474</v>
+        <v>0.1572943284606759</v>
       </c>
       <c r="C70">
-        <v>323.8838637381454</v>
+        <v>100.0263633071146</v>
       </c>
       <c r="D70">
-        <v>790.3238637381454</v>
+        <v>574.5213633071147</v>
       </c>
       <c r="E70">
-        <v>386.44</v>
+        <v>394.4950000000001</v>
       </c>
       <c r="F70">
-        <v>547.74</v>
+        <v>555.7950000000001</v>
       </c>
       <c r="G70">
         <v>81.3</v>
@@ -7021,45 +7021,45 @@
         <v>74.7</v>
       </c>
       <c r="M70">
-        <v>49.2966</v>
+        <v>81.59070600000001</v>
       </c>
       <c r="N70">
-        <v>25.4034</v>
+        <v>-6.890706000000009</v>
       </c>
       <c r="O70">
-        <v>8.637156000000003</v>
+        <v>-2.342840040000003</v>
       </c>
       <c r="P70">
-        <v>16.766244</v>
+        <v>-4.547865960000006</v>
       </c>
       <c r="Q70">
-        <v>42.066244</v>
+        <v>20.75213403999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2701817420145232</v>
+        <v>0.28236469263761</v>
       </c>
       <c r="T70">
-        <v>2.924446293691036</v>
+        <v>3.083230981233043</v>
       </c>
       <c r="U70">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.34</v>
+        <v>0.3112854544977218</v>
       </c>
       <c r="W70">
-        <v>0.05939999999999999</v>
+        <v>0.1011032952797344</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y70">
-        <v>1.515317486398656</v>
+        <v>0.9155454544050641</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1572943284606759</v>
+        <v>0.1583043284606759</v>
       </c>
       <c r="C71">
-        <v>100.0263633071146</v>
+        <v>86.813636623354</v>
       </c>
       <c r="D71">
-        <v>574.5213633071147</v>
+        <v>569.3636366233541</v>
       </c>
       <c r="E71">
-        <v>394.4950000000001</v>
+        <v>402.55</v>
       </c>
       <c r="F71">
-        <v>555.7950000000001</v>
+        <v>563.85</v>
       </c>
       <c r="G71">
         <v>81.3</v>
@@ -7103,37 +7103,37 @@
         <v>74.7</v>
       </c>
       <c r="M71">
-        <v>81.59070600000001</v>
+        <v>82.77318000000001</v>
       </c>
       <c r="N71">
-        <v>-6.890706000000009</v>
+        <v>-8.073180000000008</v>
       </c>
       <c r="O71">
-        <v>-2.342840040000003</v>
+        <v>-2.744881200000003</v>
       </c>
       <c r="P71">
-        <v>-4.547865960000006</v>
+        <v>-5.328298800000005</v>
       </c>
       <c r="Q71">
-        <v>20.75213403999999</v>
+        <v>19.97170119999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.28236469263761</v>
+        <v>0.2902501823921971</v>
       </c>
       <c r="T71">
-        <v>3.083230981233043</v>
+        <v>3.186005347274145</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.3112854544977218</v>
+        <v>0.3068385194334687</v>
       </c>
       <c r="W71">
-        <v>0.1011032952797344</v>
+        <v>0.1017561053471668</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.9155454544050641</v>
+        <v>0.9024662336278489</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1583043284606759</v>
+        <v>0.1593143284606759</v>
       </c>
       <c r="C72">
-        <v>86.813636623354</v>
+        <v>73.69269225502865</v>
       </c>
       <c r="D72">
-        <v>569.3636366233541</v>
+        <v>564.2976922550288</v>
       </c>
       <c r="E72">
-        <v>402.55</v>
+        <v>410.6050000000001</v>
       </c>
       <c r="F72">
-        <v>563.85</v>
+        <v>571.9050000000001</v>
       </c>
       <c r="G72">
         <v>81.3</v>
@@ -7185,37 +7185,37 @@
         <v>74.7</v>
       </c>
       <c r="M72">
-        <v>82.77318000000001</v>
+        <v>83.95565400000002</v>
       </c>
       <c r="N72">
-        <v>-8.073180000000008</v>
+        <v>-9.255654000000021</v>
       </c>
       <c r="O72">
-        <v>-2.744881200000003</v>
+        <v>-3.146922360000008</v>
       </c>
       <c r="P72">
-        <v>-5.328298800000005</v>
+        <v>-6.108731640000014</v>
       </c>
       <c r="Q72">
-        <v>19.97170119999999</v>
+        <v>19.19126835999998</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2902501823921971</v>
+        <v>0.2986794990264108</v>
       </c>
       <c r="T72">
-        <v>3.186005347274145</v>
+        <v>3.295867600628426</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.3068385194334687</v>
+        <v>0.3025168501456733</v>
       </c>
       <c r="W72">
-        <v>0.1017561053471668</v>
+        <v>0.1023905263986152</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.9024662336278489</v>
+        <v>0.8897554416049214</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1593143284606759</v>
+        <v>0.1603243284606758</v>
       </c>
       <c r="C73">
-        <v>73.69269225502876</v>
+        <v>60.66110189350354</v>
       </c>
       <c r="D73">
-        <v>564.2976922550288</v>
+        <v>559.3211018935035</v>
       </c>
       <c r="E73">
-        <v>410.605</v>
+        <v>418.6599999999999</v>
       </c>
       <c r="F73">
-        <v>571.905</v>
+        <v>579.9599999999999</v>
       </c>
       <c r="G73">
         <v>81.3</v>
@@ -7267,37 +7267,37 @@
         <v>74.7</v>
       </c>
       <c r="M73">
-        <v>83.95565400000001</v>
+        <v>85.13812799999999</v>
       </c>
       <c r="N73">
-        <v>-9.255654000000007</v>
+        <v>-10.43812799999999</v>
       </c>
       <c r="O73">
-        <v>-3.146922360000003</v>
+        <v>-3.548963519999997</v>
       </c>
       <c r="P73">
-        <v>-6.108731640000004</v>
+        <v>-6.889164479999994</v>
       </c>
       <c r="Q73">
-        <v>19.19126836</v>
+        <v>18.41083552</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2986794990264107</v>
+        <v>0.3077109097059254</v>
       </c>
       <c r="T73">
-        <v>3.295867600628425</v>
+        <v>3.413577157793725</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.3025168501456733</v>
+        <v>0.2983152272269835</v>
       </c>
       <c r="W73">
-        <v>0.1023905263986152</v>
+        <v>0.1030073246430788</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8897554416049215</v>
+        <v>0.8773977271381866</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1603243284606758</v>
+        <v>0.1613343284606759</v>
       </c>
       <c r="C74">
-        <v>60.66110189350354</v>
+        <v>47.71652214314622</v>
       </c>
       <c r="D74">
-        <v>559.3211018935035</v>
+        <v>554.4315221431463</v>
       </c>
       <c r="E74">
-        <v>418.6599999999999</v>
+        <v>426.715</v>
       </c>
       <c r="F74">
-        <v>579.9599999999999</v>
+        <v>588.015</v>
       </c>
       <c r="G74">
         <v>81.3</v>
@@ -7349,37 +7349,37 @@
         <v>74.7</v>
       </c>
       <c r="M74">
-        <v>85.13812799999999</v>
+        <v>86.32060200000001</v>
       </c>
       <c r="N74">
-        <v>-10.43812799999999</v>
+        <v>-11.62060200000001</v>
       </c>
       <c r="O74">
-        <v>-3.548963519999997</v>
+        <v>-3.951004680000002</v>
       </c>
       <c r="P74">
-        <v>-6.889164479999994</v>
+        <v>-7.669597320000003</v>
       </c>
       <c r="Q74">
-        <v>18.41083552</v>
+        <v>17.63040268</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3077109097059254</v>
+        <v>0.3174113137691078</v>
       </c>
       <c r="T74">
-        <v>3.413577157793725</v>
+        <v>3.540005941415715</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2983152272269835</v>
+        <v>0.29422871726497</v>
       </c>
       <c r="W74">
-        <v>0.1030073246430788</v>
+        <v>0.1036072243055024</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8773977271381866</v>
+        <v>0.865378580191088</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1613343284606759</v>
+        <v>0.1623443284606759</v>
       </c>
       <c r="C75">
-        <v>47.71652214314622</v>
+        <v>34.85669084195149</v>
       </c>
       <c r="D75">
-        <v>554.4315221431463</v>
+        <v>549.6266908419515</v>
       </c>
       <c r="E75">
-        <v>426.715</v>
+        <v>434.7699999999999</v>
       </c>
       <c r="F75">
-        <v>588.015</v>
+        <v>596.0699999999999</v>
       </c>
       <c r="G75">
         <v>81.3</v>
@@ -7431,37 +7431,37 @@
         <v>74.7</v>
       </c>
       <c r="M75">
-        <v>86.32060200000001</v>
+        <v>87.50307599999999</v>
       </c>
       <c r="N75">
-        <v>-11.62060200000001</v>
+        <v>-12.80307599999999</v>
       </c>
       <c r="O75">
-        <v>-3.951004680000002</v>
+        <v>-4.353045839999997</v>
       </c>
       <c r="P75">
-        <v>-7.669597320000003</v>
+        <v>-8.450030159999994</v>
       </c>
       <c r="Q75">
-        <v>17.63040268</v>
+        <v>16.84996984</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3174113137691078</v>
+        <v>0.3278579027602274</v>
       </c>
       <c r="T75">
-        <v>3.540005941415715</v>
+        <v>3.676160016085551</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.29422871726497</v>
+        <v>0.2902526535181461</v>
       </c>
       <c r="W75">
-        <v>0.1036072243055024</v>
+        <v>0.1041909104635362</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.865378580191088</v>
+        <v>0.8536842750533709</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1623443284606759</v>
+        <v>0.1633543284606759</v>
       </c>
       <c r="C76">
-        <v>34.85669084195149</v>
+        <v>22.07942357183492</v>
       </c>
       <c r="D76">
-        <v>549.6266908419515</v>
+        <v>544.904423571835</v>
       </c>
       <c r="E76">
-        <v>434.7699999999999</v>
+        <v>442.825</v>
       </c>
       <c r="F76">
-        <v>596.0699999999999</v>
+        <v>604.125</v>
       </c>
       <c r="G76">
         <v>81.3</v>
@@ -7513,37 +7513,37 @@
         <v>74.7</v>
       </c>
       <c r="M76">
-        <v>87.50307599999999</v>
+        <v>88.68555000000001</v>
       </c>
       <c r="N76">
-        <v>-12.80307599999999</v>
+        <v>-13.98555</v>
       </c>
       <c r="O76">
-        <v>-4.353045839999997</v>
+        <v>-4.755087000000001</v>
       </c>
       <c r="P76">
-        <v>-8.450030159999994</v>
+        <v>-9.230463000000002</v>
       </c>
       <c r="Q76">
-        <v>16.84996984</v>
+        <v>16.069537</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3278579027602274</v>
+        <v>0.3391402188706364</v>
       </c>
       <c r="T76">
-        <v>3.676160016085551</v>
+        <v>3.823206416728973</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2902526535181461</v>
+        <v>0.2863826181379041</v>
       </c>
       <c r="W76">
-        <v>0.1041909104635362</v>
+        <v>0.1047590316573557</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8536842750533709</v>
+        <v>0.842301818052659</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1633543284606759</v>
+        <v>0.1643643284606759</v>
       </c>
       <c r="C77">
-        <v>22.07942357183492</v>
+        <v>9.382610347294076</v>
       </c>
       <c r="D77">
-        <v>544.904423571835</v>
+        <v>540.2626103472942</v>
       </c>
       <c r="E77">
-        <v>442.825</v>
+        <v>450.8800000000001</v>
       </c>
       <c r="F77">
-        <v>604.125</v>
+        <v>612.1800000000001</v>
       </c>
       <c r="G77">
         <v>81.3</v>
@@ -7595,37 +7595,37 @@
         <v>74.7</v>
       </c>
       <c r="M77">
-        <v>88.68555000000001</v>
+        <v>89.86802400000002</v>
       </c>
       <c r="N77">
-        <v>-13.98555</v>
+        <v>-15.16802400000002</v>
       </c>
       <c r="O77">
-        <v>-4.755087000000001</v>
+        <v>-5.157128160000006</v>
       </c>
       <c r="P77">
-        <v>-9.230463000000002</v>
+        <v>-10.01089584000001</v>
       </c>
       <c r="Q77">
-        <v>16.069537</v>
+        <v>15.28910415999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3391402188706364</v>
+        <v>0.3513627279902463</v>
       </c>
       <c r="T77">
-        <v>3.823206416728973</v>
+        <v>3.98250668409268</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2863826181379041</v>
+        <v>0.2826144257939843</v>
       </c>
       <c r="W77">
-        <v>0.1047590316573557</v>
+        <v>0.1053122022934431</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.842301818052659</v>
+        <v>0.8312188993940713</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1643643284606759</v>
+        <v>0.1653743284606759</v>
       </c>
       <c r="C78">
-        <v>9.382610347294076</v>
+        <v>-3.235787528113633</v>
       </c>
       <c r="D78">
-        <v>540.2626103472942</v>
+        <v>535.6992124718864</v>
       </c>
       <c r="E78">
-        <v>450.8800000000001</v>
+        <v>458.935</v>
       </c>
       <c r="F78">
-        <v>612.1800000000001</v>
+        <v>620.235</v>
       </c>
       <c r="G78">
         <v>81.3</v>
@@ -7677,37 +7677,37 @@
         <v>74.7</v>
       </c>
       <c r="M78">
-        <v>89.86802400000002</v>
+        <v>91.050498</v>
       </c>
       <c r="N78">
-        <v>-15.16802400000002</v>
+        <v>-16.350498</v>
       </c>
       <c r="O78">
-        <v>-5.157128160000006</v>
+        <v>-5.559169320000001</v>
       </c>
       <c r="P78">
-        <v>-10.01089584000001</v>
+        <v>-10.79132868</v>
       </c>
       <c r="Q78">
-        <v>15.28910415999999</v>
+        <v>14.50867132</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3513627279902463</v>
+        <v>0.3646480639898222</v>
       </c>
       <c r="T78">
-        <v>3.98250668409268</v>
+        <v>4.155659148618449</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2826144257939843</v>
+        <v>0.2789441085758806</v>
       </c>
       <c r="W78">
-        <v>0.1053122022934431</v>
+        <v>0.1058510048610607</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8312188993940713</v>
+        <v>0.82042384875259</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1653743284606759</v>
+        <v>0.1663843284606759</v>
       </c>
       <c r="C79">
-        <v>-3.235787528113633</v>
+        <v>-15.77774044731552</v>
       </c>
       <c r="D79">
-        <v>535.6992124718864</v>
+        <v>531.2122595526846</v>
       </c>
       <c r="E79">
-        <v>458.935</v>
+        <v>466.9900000000001</v>
       </c>
       <c r="F79">
-        <v>620.235</v>
+        <v>628.2900000000001</v>
       </c>
       <c r="G79">
         <v>81.3</v>
@@ -7759,37 +7759,37 @@
         <v>74.7</v>
       </c>
       <c r="M79">
-        <v>91.050498</v>
+        <v>92.23297200000002</v>
       </c>
       <c r="N79">
-        <v>-16.350498</v>
+        <v>-17.53297200000002</v>
       </c>
       <c r="O79">
-        <v>-5.559169320000001</v>
+        <v>-5.961210480000005</v>
       </c>
       <c r="P79">
-        <v>-10.79132868</v>
+        <v>-11.57176152000001</v>
       </c>
       <c r="Q79">
-        <v>14.50867132</v>
+        <v>13.72823847999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3646480639898222</v>
+        <v>0.3791411578075415</v>
       </c>
       <c r="T79">
-        <v>4.155659148618449</v>
+        <v>4.344552746282925</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2789441085758806</v>
+        <v>0.275367902055677</v>
       </c>
       <c r="W79">
-        <v>0.1058510048610607</v>
+        <v>0.1063759919782266</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.82042384875259</v>
+        <v>0.8099055942814029</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1663843284606759</v>
+        <v>0.2154489637488442</v>
       </c>
       <c r="C80">
-        <v>-15.77774044731552</v>
+        <v>-177.4660736525933</v>
       </c>
       <c r="D80">
-        <v>531.2122595526846</v>
+        <v>377.5789263474068</v>
       </c>
       <c r="E80">
-        <v>466.9900000000001</v>
+        <v>475.045</v>
       </c>
       <c r="F80">
-        <v>628.2900000000001</v>
+        <v>636.345</v>
       </c>
       <c r="G80">
         <v>81.3</v>
@@ -7841,45 +7841,45 @@
         <v>74.7</v>
       </c>
       <c r="M80">
-        <v>92.23297200000002</v>
+        <v>127.778076</v>
       </c>
       <c r="N80">
-        <v>-17.53297200000002</v>
+        <v>-53.07807600000001</v>
       </c>
       <c r="O80">
-        <v>-5.961210480000005</v>
+        <v>-18.04654584</v>
       </c>
       <c r="P80">
-        <v>-11.57176152000001</v>
+        <v>-35.03153016</v>
       </c>
       <c r="Q80">
-        <v>13.72823847999999</v>
+        <v>-9.731530160000005</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3791411578075415</v>
+        <v>0.4207032857420356</v>
       </c>
       <c r="T80">
-        <v>4.344552746282925</v>
+        <v>4.886246602051621</v>
       </c>
       <c r="U80">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.275367902055677</v>
+        <v>0.1987664926180294</v>
       </c>
       <c r="W80">
-        <v>0.1063759919782266</v>
+        <v>0.1608876882822997</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.8099055942814029</v>
+        <v>0.5846073312294982</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2154489637488442</v>
+        <v>0.2169989637488443</v>
       </c>
       <c r="C81">
-        <v>-177.4660736525933</v>
+        <v>-188.9395951379049</v>
       </c>
       <c r="D81">
-        <v>377.5789263474068</v>
+        <v>374.1604048620952</v>
       </c>
       <c r="E81">
-        <v>475.045</v>
+        <v>483.1000000000001</v>
       </c>
       <c r="F81">
-        <v>636.345</v>
+        <v>644.4000000000001</v>
       </c>
       <c r="G81">
         <v>81.3</v>
@@ -7923,37 +7923,37 @@
         <v>74.7</v>
       </c>
       <c r="M81">
-        <v>127.778076</v>
+        <v>129.39552</v>
       </c>
       <c r="N81">
-        <v>-53.07807600000001</v>
+        <v>-54.69552000000003</v>
       </c>
       <c r="O81">
-        <v>-18.04654584</v>
+        <v>-18.59647680000001</v>
       </c>
       <c r="P81">
-        <v>-35.03153016</v>
+        <v>-36.09904320000002</v>
       </c>
       <c r="Q81">
-        <v>-9.731530160000005</v>
+        <v>-10.79904320000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4207032857420356</v>
+        <v>0.4394484500291373</v>
       </c>
       <c r="T81">
-        <v>4.886246602051621</v>
+        <v>5.130558932154202</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1987664926180294</v>
+        <v>0.196281911460304</v>
       </c>
       <c r="W81">
-        <v>0.1608876882822997</v>
+        <v>0.161386592178771</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5846073312294982</v>
+        <v>0.5772997395891294</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2169989637488443</v>
+        <v>0.2185489637488442</v>
       </c>
       <c r="C82">
-        <v>-188.9395951379049</v>
+        <v>-200.35177086244</v>
       </c>
       <c r="D82">
-        <v>374.1604048620952</v>
+        <v>370.80322913756</v>
       </c>
       <c r="E82">
-        <v>483.1000000000001</v>
+        <v>491.155</v>
       </c>
       <c r="F82">
-        <v>644.4000000000001</v>
+        <v>652.455</v>
       </c>
       <c r="G82">
         <v>81.3</v>
@@ -8005,37 +8005,37 @@
         <v>74.7</v>
       </c>
       <c r="M82">
-        <v>129.39552</v>
+        <v>131.012964</v>
       </c>
       <c r="N82">
-        <v>-54.69552000000003</v>
+        <v>-56.31296400000001</v>
       </c>
       <c r="O82">
-        <v>-18.59647680000001</v>
+        <v>-19.14640776</v>
       </c>
       <c r="P82">
-        <v>-36.09904320000002</v>
+        <v>-37.16655624000001</v>
       </c>
       <c r="Q82">
-        <v>-10.79904320000002</v>
+        <v>-11.86655624000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4394484500291373</v>
+        <v>0.4601667895043551</v>
       </c>
       <c r="T82">
-        <v>5.130558932154202</v>
+        <v>5.400588349636002</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.196281911460304</v>
+        <v>0.1938586779854855</v>
       </c>
       <c r="W82">
-        <v>0.161386592178771</v>
+        <v>0.1618731774605145</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5772997395891294</v>
+        <v>0.5701725823102514</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2185489637488442</v>
+        <v>0.2200989637488442</v>
       </c>
       <c r="C83">
-        <v>-200.35177086244</v>
+        <v>-211.7042374267933</v>
       </c>
       <c r="D83">
-        <v>370.80322913756</v>
+        <v>367.5057625732068</v>
       </c>
       <c r="E83">
-        <v>491.155</v>
+        <v>499.2100000000001</v>
       </c>
       <c r="F83">
-        <v>652.455</v>
+        <v>660.5100000000001</v>
       </c>
       <c r="G83">
         <v>81.3</v>
@@ -8087,37 +8087,37 @@
         <v>74.7</v>
       </c>
       <c r="M83">
-        <v>131.012964</v>
+        <v>132.630408</v>
       </c>
       <c r="N83">
-        <v>-56.31296400000001</v>
+        <v>-57.93040800000001</v>
       </c>
       <c r="O83">
-        <v>-19.14640776</v>
+        <v>-19.69633872000001</v>
       </c>
       <c r="P83">
-        <v>-37.16655624000001</v>
+        <v>-38.23406928000001</v>
       </c>
       <c r="Q83">
-        <v>-11.86655624000001</v>
+        <v>-12.93406928000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4601667895043551</v>
+        <v>0.4831871666990415</v>
       </c>
       <c r="T83">
-        <v>5.400588349636002</v>
+        <v>5.700621035726891</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1938586779854855</v>
+        <v>0.1914945477661503</v>
       </c>
       <c r="W83">
-        <v>0.1618731774605145</v>
+        <v>0.162347894808557</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5701725823102514</v>
+        <v>0.563219258135736</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2200989637488442</v>
+        <v>0.2216489637488442</v>
       </c>
       <c r="C84">
-        <v>-211.7042374267933</v>
+        <v>-222.9985737290647</v>
       </c>
       <c r="D84">
-        <v>367.5057625732068</v>
+        <v>364.2664262709354</v>
       </c>
       <c r="E84">
-        <v>499.2100000000001</v>
+        <v>507.265</v>
       </c>
       <c r="F84">
-        <v>660.5100000000001</v>
+        <v>668.5650000000001</v>
       </c>
       <c r="G84">
         <v>81.3</v>
@@ -8169,37 +8169,37 @@
         <v>74.7</v>
       </c>
       <c r="M84">
-        <v>132.630408</v>
+        <v>134.247852</v>
       </c>
       <c r="N84">
-        <v>-57.93040800000001</v>
+        <v>-59.54785200000002</v>
       </c>
       <c r="O84">
-        <v>-19.69633872000001</v>
+        <v>-20.24626968000001</v>
       </c>
       <c r="P84">
-        <v>-38.23406928000001</v>
+        <v>-39.30158232000001</v>
       </c>
       <c r="Q84">
-        <v>-12.93406928000001</v>
+        <v>-14.00158232000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4831871666990415</v>
+        <v>0.5089158235636909</v>
       </c>
       <c r="T84">
-        <v>5.700621035726891</v>
+        <v>6.035951684887296</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1914945477661503</v>
+        <v>0.1891873845400521</v>
       </c>
       <c r="W84">
-        <v>0.162347894808557</v>
+        <v>0.1628111731843575</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.563219258135736</v>
+        <v>0.5564334839413296</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2216489637488442</v>
+        <v>0.2231989637488442</v>
       </c>
       <c r="C85">
-        <v>-222.9985737290647</v>
+        <v>-234.2363034857015</v>
       </c>
       <c r="D85">
-        <v>364.2664262709354</v>
+        <v>361.0836965142987</v>
       </c>
       <c r="E85">
-        <v>507.265</v>
+        <v>515.3200000000002</v>
       </c>
       <c r="F85">
-        <v>668.5650000000001</v>
+        <v>676.6200000000001</v>
       </c>
       <c r="G85">
         <v>81.3</v>
@@ -8251,37 +8251,37 @@
         <v>74.7</v>
       </c>
       <c r="M85">
-        <v>134.247852</v>
+        <v>135.865296</v>
       </c>
       <c r="N85">
-        <v>-59.54785200000002</v>
+        <v>-61.16529600000003</v>
       </c>
       <c r="O85">
-        <v>-20.24626968000001</v>
+        <v>-20.79620064000001</v>
       </c>
       <c r="P85">
-        <v>-39.30158232000001</v>
+        <v>-40.36909536000002</v>
       </c>
       <c r="Q85">
-        <v>-14.00158232000001</v>
+        <v>-15.06909536000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5089158235636909</v>
+        <v>0.5378605625364219</v>
       </c>
       <c r="T85">
-        <v>6.035951684887296</v>
+        <v>6.413198665192755</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1891873845400521</v>
+        <v>0.1869351537717181</v>
       </c>
       <c r="W85">
-        <v>0.1628111731843575</v>
+        <v>0.163263421122639</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5564334839413296</v>
+        <v>0.5498092757991708</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2231989637488442</v>
+        <v>0.2247489637488442</v>
       </c>
       <c r="C86">
-        <v>-234.2363034857013</v>
+        <v>-245.4188976213269</v>
       </c>
       <c r="D86">
-        <v>361.0836965142987</v>
+        <v>357.9561023786731</v>
       </c>
       <c r="E86">
-        <v>515.3199999999999</v>
+        <v>523.375</v>
       </c>
       <c r="F86">
-        <v>676.62</v>
+        <v>684.675</v>
       </c>
       <c r="G86">
         <v>81.3</v>
@@ -8333,37 +8333,37 @@
         <v>74.7</v>
       </c>
       <c r="M86">
-        <v>135.865296</v>
+        <v>137.48274</v>
       </c>
       <c r="N86">
-        <v>-61.165296</v>
+        <v>-62.78274</v>
       </c>
       <c r="O86">
-        <v>-20.79620064</v>
+        <v>-21.3461316</v>
       </c>
       <c r="P86">
-        <v>-40.36909536</v>
+        <v>-41.4366084</v>
       </c>
       <c r="Q86">
-        <v>-15.06909536</v>
+        <v>-16.1366084</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5378605625364216</v>
+        <v>0.5706646000388496</v>
       </c>
       <c r="T86">
-        <v>6.41319866519275</v>
+        <v>6.840745242872267</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1869351537717181</v>
+        <v>0.1847359166685214</v>
       </c>
       <c r="W86">
-        <v>0.163263421122639</v>
+        <v>0.1637050279329609</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.549809275799171</v>
+        <v>0.5433409313780042</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2247489637488442</v>
+        <v>0.2262989637488442</v>
       </c>
       <c r="C87">
-        <v>-245.4188976213269</v>
+        <v>-256.5477765354406</v>
       </c>
       <c r="D87">
-        <v>357.9561023786731</v>
+        <v>354.8822234645594</v>
       </c>
       <c r="E87">
-        <v>523.375</v>
+        <v>531.4300000000001</v>
       </c>
       <c r="F87">
-        <v>684.675</v>
+        <v>692.73</v>
       </c>
       <c r="G87">
         <v>81.3</v>
@@ -8415,37 +8415,37 @@
         <v>74.7</v>
       </c>
       <c r="M87">
-        <v>137.48274</v>
+        <v>139.100184</v>
       </c>
       <c r="N87">
-        <v>-62.78274</v>
+        <v>-64.40018400000001</v>
       </c>
       <c r="O87">
-        <v>-21.3461316</v>
+        <v>-21.89606256</v>
       </c>
       <c r="P87">
-        <v>-41.4366084</v>
+        <v>-42.50412144000001</v>
       </c>
       <c r="Q87">
-        <v>-16.1366084</v>
+        <v>-17.20412144000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5706646000388496</v>
+        <v>0.6081549286130531</v>
       </c>
       <c r="T87">
-        <v>6.840745242872267</v>
+        <v>7.329369903077429</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1847359166685214</v>
+        <v>0.1825878246142363</v>
       </c>
       <c r="W87">
-        <v>0.1637050279329609</v>
+        <v>0.1641363648174614</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5433409313780042</v>
+        <v>0.5370230135712832</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2262989637488442</v>
+        <v>0.2278489637488442</v>
       </c>
       <c r="C88">
-        <v>-256.5477765354406</v>
+        <v>-267.6243122533199</v>
       </c>
       <c r="D88">
-        <v>354.8822234645594</v>
+        <v>351.86068774668</v>
       </c>
       <c r="E88">
-        <v>531.4300000000001</v>
+        <v>539.4849999999999</v>
       </c>
       <c r="F88">
-        <v>692.73</v>
+        <v>700.785</v>
       </c>
       <c r="G88">
         <v>81.3</v>
@@ -8497,37 +8497,37 @@
         <v>74.7</v>
       </c>
       <c r="M88">
-        <v>139.100184</v>
+        <v>140.717628</v>
       </c>
       <c r="N88">
-        <v>-64.40018400000001</v>
+        <v>-66.01762799999999</v>
       </c>
       <c r="O88">
-        <v>-21.89606256</v>
+        <v>-22.44599352</v>
       </c>
       <c r="P88">
-        <v>-42.50412144000001</v>
+        <v>-43.57163447999999</v>
       </c>
       <c r="Q88">
-        <v>-17.20412144000001</v>
+        <v>-18.27163447999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6081549286130531</v>
+        <v>0.6514130000448264</v>
       </c>
       <c r="T88">
-        <v>7.329369903077429</v>
+        <v>7.893167587929538</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1825878246142363</v>
+        <v>0.1804891139864865</v>
       </c>
       <c r="W88">
-        <v>0.1641363648174614</v>
+        <v>0.1645577859115135</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5370230135712832</v>
+        <v>0.5308503352543721</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2278489637488442</v>
+        <v>0.2293989637488442</v>
       </c>
       <c r="C89">
-        <v>-267.6243122533199</v>
+        <v>-278.6498304679731</v>
       </c>
       <c r="D89">
-        <v>351.86068774668</v>
+        <v>348.890169532027</v>
       </c>
       <c r="E89">
-        <v>539.4849999999999</v>
+        <v>547.54</v>
       </c>
       <c r="F89">
-        <v>700.785</v>
+        <v>708.84</v>
       </c>
       <c r="G89">
         <v>81.3</v>
@@ -8579,37 +8579,37 @@
         <v>74.7</v>
       </c>
       <c r="M89">
-        <v>140.717628</v>
+        <v>142.335072</v>
       </c>
       <c r="N89">
-        <v>-66.01762799999999</v>
+        <v>-67.63507199999999</v>
       </c>
       <c r="O89">
-        <v>-22.44599352</v>
+        <v>-22.99592448</v>
       </c>
       <c r="P89">
-        <v>-43.57163447999999</v>
+        <v>-44.63914751999999</v>
       </c>
       <c r="Q89">
-        <v>-18.27163447999999</v>
+        <v>-19.33914752</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6514130000448264</v>
+        <v>0.7018807500485621</v>
       </c>
       <c r="T89">
-        <v>7.893167587929538</v>
+        <v>8.550931553590335</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1804891139864865</v>
+        <v>0.1784381013275491</v>
       </c>
       <c r="W89">
-        <v>0.1645577859115135</v>
+        <v>0.1649696292534281</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5308503352543721</v>
+        <v>0.5248179450810269</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2293989637488442</v>
+        <v>0.2309489637488442</v>
       </c>
       <c r="C90">
-        <v>-278.6498304679731</v>
+        <v>-289.6256124795224</v>
       </c>
       <c r="D90">
-        <v>348.890169532027</v>
+        <v>345.9693875204775</v>
       </c>
       <c r="E90">
-        <v>547.54</v>
+        <v>555.595</v>
       </c>
       <c r="F90">
-        <v>708.84</v>
+        <v>716.895</v>
       </c>
       <c r="G90">
         <v>81.3</v>
@@ -8661,37 +8661,37 @@
         <v>74.7</v>
       </c>
       <c r="M90">
-        <v>142.335072</v>
+        <v>143.952516</v>
       </c>
       <c r="N90">
-        <v>-67.63507199999999</v>
+        <v>-69.252516</v>
       </c>
       <c r="O90">
-        <v>-22.99592448</v>
+        <v>-23.54585544</v>
       </c>
       <c r="P90">
-        <v>-44.63914751999999</v>
+        <v>-45.70666056</v>
       </c>
       <c r="Q90">
-        <v>-19.33914752</v>
+        <v>-20.40666056000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7018807500485621</v>
+        <v>0.7615244545984313</v>
       </c>
       <c r="T90">
-        <v>8.550931553590335</v>
+        <v>9.328288967553092</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1784381013275491</v>
+        <v>0.1764331788407228</v>
       </c>
       <c r="W90">
-        <v>0.1649696292534281</v>
+        <v>0.1653722176887829</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5248179450810269</v>
+        <v>0.5189211142374198</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2309489637488442</v>
+        <v>0.2324989637488442</v>
       </c>
       <c r="C91">
-        <v>-289.6256124795224</v>
+        <v>-300.5528970379848</v>
       </c>
       <c r="D91">
-        <v>345.9693875204775</v>
+        <v>343.0971029620152</v>
       </c>
       <c r="E91">
-        <v>555.595</v>
+        <v>563.6500000000001</v>
       </c>
       <c r="F91">
-        <v>716.895</v>
+        <v>724.95</v>
       </c>
       <c r="G91">
         <v>81.3</v>
@@ -8743,37 +8743,37 @@
         <v>74.7</v>
       </c>
       <c r="M91">
-        <v>143.952516</v>
+        <v>145.56996</v>
       </c>
       <c r="N91">
-        <v>-69.252516</v>
+        <v>-70.86996000000001</v>
       </c>
       <c r="O91">
-        <v>-23.54585544</v>
+        <v>-24.09578640000001</v>
       </c>
       <c r="P91">
-        <v>-45.70666056</v>
+        <v>-46.7741736</v>
       </c>
       <c r="Q91">
-        <v>-20.40666056000001</v>
+        <v>-21.4741736</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7615244545984313</v>
+        <v>0.8330969000582746</v>
       </c>
       <c r="T91">
-        <v>9.328288967553092</v>
+        <v>10.2611178643084</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1764331788407228</v>
+        <v>0.1744728101869369</v>
       </c>
       <c r="W91">
-        <v>0.1653722176887829</v>
+        <v>0.1657658597144631</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5189211142374198</v>
+        <v>0.5131553240792261</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2324989637488442</v>
+        <v>0.2340489637488442</v>
       </c>
       <c r="C92">
-        <v>-300.5528970379848</v>
+        <v>-311.4328820950108</v>
       </c>
       <c r="D92">
-        <v>343.0971029620152</v>
+        <v>340.2721179049892</v>
       </c>
       <c r="E92">
-        <v>563.6500000000001</v>
+        <v>571.7049999999999</v>
       </c>
       <c r="F92">
-        <v>724.95</v>
+        <v>733.005</v>
       </c>
       <c r="G92">
         <v>81.3</v>
@@ -8825,37 +8825,37 @@
         <v>74.7</v>
       </c>
       <c r="M92">
-        <v>145.56996</v>
+        <v>147.187404</v>
       </c>
       <c r="N92">
-        <v>-70.86996000000001</v>
+        <v>-72.48740400000001</v>
       </c>
       <c r="O92">
-        <v>-24.09578640000001</v>
+        <v>-24.64571736000001</v>
       </c>
       <c r="P92">
-        <v>-46.7741736</v>
+        <v>-47.84168664000001</v>
       </c>
       <c r="Q92">
-        <v>-21.4741736</v>
+        <v>-22.54168664000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8330969000582746</v>
+        <v>0.9205743333980829</v>
       </c>
       <c r="T92">
-        <v>10.2611178643084</v>
+        <v>11.40124207145378</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1744728101869369</v>
+        <v>0.172555526558509</v>
       </c>
       <c r="W92">
-        <v>0.1657658597144631</v>
+        <v>0.1661508502670514</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5131553240792261</v>
+        <v>0.5075162545838501</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2340489637488442</v>
+        <v>0.2355989637488442</v>
       </c>
       <c r="C93">
-        <v>-311.4328820950108</v>
+        <v>-322.2667264697919</v>
       </c>
       <c r="D93">
-        <v>340.2721179049892</v>
+        <v>337.4932735302082</v>
       </c>
       <c r="E93">
-        <v>571.7049999999999</v>
+        <v>579.76</v>
       </c>
       <c r="F93">
-        <v>733.005</v>
+        <v>741.0600000000001</v>
       </c>
       <c r="G93">
         <v>81.3</v>
@@ -8907,37 +8907,37 @@
         <v>74.7</v>
       </c>
       <c r="M93">
-        <v>147.187404</v>
+        <v>148.804848</v>
       </c>
       <c r="N93">
-        <v>-72.48740400000001</v>
+        <v>-74.10484800000002</v>
       </c>
       <c r="O93">
-        <v>-24.64571736000001</v>
+        <v>-25.19564832000001</v>
       </c>
       <c r="P93">
-        <v>-47.84168664000001</v>
+        <v>-48.90919968000001</v>
       </c>
       <c r="Q93">
-        <v>-22.54168664000001</v>
+        <v>-23.60919968000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9205743333980829</v>
+        <v>1.029921125072844</v>
       </c>
       <c r="T93">
-        <v>11.40124207145378</v>
+        <v>12.82639733038551</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.172555526558509</v>
+        <v>0.17067992300896</v>
       </c>
       <c r="W93">
-        <v>0.1661508502670514</v>
+        <v>0.1665274714598008</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5075162545838501</v>
+        <v>0.5019997735557648</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2355989637488442</v>
+        <v>0.2718757642475884</v>
       </c>
       <c r="C94">
-        <v>-322.2667264697919</v>
+        <v>-384.4769172938524</v>
       </c>
       <c r="D94">
-        <v>337.4932735302082</v>
+        <v>283.3380827061476</v>
       </c>
       <c r="E94">
-        <v>579.76</v>
+        <v>587.8150000000001</v>
       </c>
       <c r="F94">
-        <v>741.0600000000001</v>
+        <v>749.115</v>
       </c>
       <c r="G94">
         <v>81.3</v>
@@ -8989,45 +8989,45 @@
         <v>74.7</v>
       </c>
       <c r="M94">
-        <v>148.804848</v>
+        <v>176.641317</v>
       </c>
       <c r="N94">
-        <v>-74.10484800000002</v>
+        <v>-101.941317</v>
       </c>
       <c r="O94">
-        <v>-25.19564832000001</v>
+        <v>-34.66004778000001</v>
       </c>
       <c r="P94">
-        <v>-48.90919968000001</v>
+        <v>-67.28126922000001</v>
       </c>
       <c r="Q94">
-        <v>-23.60919968000002</v>
+        <v>-41.98126922000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.029921125072844</v>
+        <v>1.201607007208166</v>
       </c>
       <c r="T94">
-        <v>12.82639733038551</v>
+        <v>15.06403991744245</v>
       </c>
       <c r="U94">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.17067992300896</v>
+        <v>0.1437828953686979</v>
       </c>
       <c r="W94">
-        <v>0.1665274714598008</v>
+        <v>0.201895993272061</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.5019997735557648</v>
+        <v>0.4228908687314644</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2718757642475884</v>
+        <v>0.2737757642475884</v>
       </c>
       <c r="C95">
-        <v>-384.4769172938524</v>
+        <v>-394.8933189933639</v>
       </c>
       <c r="D95">
-        <v>283.3380827061476</v>
+        <v>280.9766810066362</v>
       </c>
       <c r="E95">
-        <v>587.8150000000001</v>
+        <v>595.8700000000001</v>
       </c>
       <c r="F95">
-        <v>749.115</v>
+        <v>757.1700000000001</v>
       </c>
       <c r="G95">
         <v>81.3</v>
@@ -9071,37 +9071,37 @@
         <v>74.7</v>
       </c>
       <c r="M95">
-        <v>176.641317</v>
+        <v>178.540686</v>
       </c>
       <c r="N95">
-        <v>-101.941317</v>
+        <v>-103.840686</v>
       </c>
       <c r="O95">
-        <v>-34.66004778000001</v>
+        <v>-35.30583324000001</v>
       </c>
       <c r="P95">
-        <v>-67.28126922000001</v>
+        <v>-68.53485276000001</v>
       </c>
       <c r="Q95">
-        <v>-41.98126922000002</v>
+        <v>-43.23485276000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.201607007208166</v>
+        <v>1.394241508409528</v>
       </c>
       <c r="T95">
-        <v>15.06403991744245</v>
+        <v>17.57471323701619</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1437828953686979</v>
+        <v>0.1422532900988182</v>
       </c>
       <c r="W95">
-        <v>0.201895993272061</v>
+        <v>0.2022566741946987</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4228908687314644</v>
+        <v>0.4183920297024063</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2737757642475884</v>
+        <v>0.2756757642475883</v>
       </c>
       <c r="C96">
-        <v>-394.8933189933639</v>
+        <v>-405.2706851447498</v>
       </c>
       <c r="D96">
-        <v>280.9766810066362</v>
+        <v>278.6543148552502</v>
       </c>
       <c r="E96">
-        <v>595.8700000000001</v>
+        <v>603.925</v>
       </c>
       <c r="F96">
-        <v>757.1700000000001</v>
+        <v>765.225</v>
       </c>
       <c r="G96">
         <v>81.3</v>
@@ -9153,37 +9153,37 @@
         <v>74.7</v>
       </c>
       <c r="M96">
-        <v>178.540686</v>
+        <v>180.440055</v>
       </c>
       <c r="N96">
-        <v>-103.840686</v>
+        <v>-105.740055</v>
       </c>
       <c r="O96">
-        <v>-35.30583324000001</v>
+        <v>-35.9516187</v>
       </c>
       <c r="P96">
-        <v>-68.53485276000001</v>
+        <v>-69.7884363</v>
       </c>
       <c r="Q96">
-        <v>-43.23485276000001</v>
+        <v>-44.4884363</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.394241508409528</v>
+        <v>1.663929810091434</v>
       </c>
       <c r="T96">
-        <v>17.57471323701619</v>
+        <v>21.08965588441944</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1422532900988182</v>
+        <v>0.1407558870451464</v>
       </c>
       <c r="W96">
-        <v>0.2022566741946987</v>
+        <v>0.2026097618347545</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4183920297024063</v>
+        <v>0.4139879030739599</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2756757642475883</v>
+        <v>0.2775757642475883</v>
       </c>
       <c r="C97">
-        <v>-405.2706851447498</v>
+        <v>-415.6099757389098</v>
       </c>
       <c r="D97">
-        <v>278.6543148552502</v>
+        <v>276.3700242610902</v>
       </c>
       <c r="E97">
-        <v>603.925</v>
+        <v>611.98</v>
       </c>
       <c r="F97">
-        <v>765.225</v>
+        <v>773.2800000000001</v>
       </c>
       <c r="G97">
         <v>81.3</v>
@@ -9235,37 +9235,37 @@
         <v>74.7</v>
       </c>
       <c r="M97">
-        <v>180.440055</v>
+        <v>182.339424</v>
       </c>
       <c r="N97">
-        <v>-105.740055</v>
+        <v>-107.639424</v>
       </c>
       <c r="O97">
-        <v>-35.9516187</v>
+        <v>-36.59740416000001</v>
       </c>
       <c r="P97">
-        <v>-69.7884363</v>
+        <v>-71.04201984000002</v>
       </c>
       <c r="Q97">
-        <v>-44.4884363</v>
+        <v>-45.74201984000003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.663929810091434</v>
+        <v>2.068462262614293</v>
       </c>
       <c r="T97">
-        <v>21.08965588441944</v>
+        <v>26.36206985552431</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1407558870451464</v>
+        <v>0.1392896798884261</v>
       </c>
       <c r="W97">
-        <v>0.2026097618347545</v>
+        <v>0.2029554934823091</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4139879030739599</v>
+        <v>0.4096755290836062</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2775757642475883</v>
+        <v>0.2794757642475884</v>
       </c>
       <c r="C98">
-        <v>-415.6099757389097</v>
+        <v>-425.9121195442882</v>
       </c>
       <c r="D98">
-        <v>276.3700242610902</v>
+        <v>274.1228804557117</v>
       </c>
       <c r="E98">
-        <v>611.98</v>
+        <v>620.0349999999999</v>
       </c>
       <c r="F98">
-        <v>773.28</v>
+        <v>781.3349999999999</v>
       </c>
       <c r="G98">
         <v>81.3</v>
@@ -9317,37 +9317,37 @@
         <v>74.7</v>
       </c>
       <c r="M98">
-        <v>182.339424</v>
+        <v>184.238793</v>
       </c>
       <c r="N98">
-        <v>-107.639424</v>
+        <v>-109.538793</v>
       </c>
       <c r="O98">
-        <v>-36.59740416</v>
+        <v>-37.24318962</v>
       </c>
       <c r="P98">
-        <v>-71.04201983999999</v>
+        <v>-72.29560337999999</v>
       </c>
       <c r="Q98">
-        <v>-45.74201984</v>
+        <v>-46.99560337999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.068462262614288</v>
+        <v>2.742683016819051</v>
       </c>
       <c r="T98">
-        <v>26.36206985552425</v>
+        <v>35.14942647403233</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1392896798884261</v>
+        <v>0.1378537038071021</v>
       </c>
       <c r="W98">
-        <v>0.2029554934823091</v>
+        <v>0.2032940966422853</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4096755290836062</v>
+        <v>0.4054520700208887</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2794757642475884</v>
+        <v>0.2813757642475884</v>
       </c>
       <c r="C99">
-        <v>-425.9121195442882</v>
+        <v>-436.1780153659759</v>
       </c>
       <c r="D99">
-        <v>274.1228804557117</v>
+        <v>271.9119846340241</v>
       </c>
       <c r="E99">
-        <v>620.0349999999999</v>
+        <v>628.0899999999999</v>
       </c>
       <c r="F99">
-        <v>781.3349999999999</v>
+        <v>789.39</v>
       </c>
       <c r="G99">
         <v>81.3</v>
@@ -9399,37 +9399,37 @@
         <v>74.7</v>
       </c>
       <c r="M99">
-        <v>184.238793</v>
+        <v>186.138162</v>
       </c>
       <c r="N99">
-        <v>-109.538793</v>
+        <v>-111.438162</v>
       </c>
       <c r="O99">
-        <v>-37.24318962</v>
+        <v>-37.88897508</v>
       </c>
       <c r="P99">
-        <v>-72.29560337999999</v>
+        <v>-73.54918691999998</v>
       </c>
       <c r="Q99">
-        <v>-46.99560337999999</v>
+        <v>-48.24918691999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.742683016819051</v>
+        <v>4.091124525228576</v>
       </c>
       <c r="T99">
-        <v>35.14942647403233</v>
+        <v>52.72413971104849</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1378537038071021</v>
+        <v>0.1364470333600909</v>
       </c>
       <c r="W99">
-        <v>0.2032940966422853</v>
+        <v>0.2036257895336906</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4054520700208887</v>
+        <v>0.4013148040002673</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2813757642475884</v>
+        <v>0.2832757642475884</v>
       </c>
       <c r="C100">
-        <v>-436.1780153659759</v>
+        <v>-446.4085332443645</v>
       </c>
       <c r="D100">
-        <v>271.9119846340241</v>
+        <v>269.7364667556354</v>
       </c>
       <c r="E100">
-        <v>628.0899999999999</v>
+        <v>636.145</v>
       </c>
       <c r="F100">
-        <v>789.39</v>
+        <v>797.4449999999999</v>
       </c>
       <c r="G100">
         <v>81.3</v>
@@ -9481,37 +9481,37 @@
         <v>74.7</v>
       </c>
       <c r="M100">
-        <v>186.138162</v>
+        <v>188.037531</v>
       </c>
       <c r="N100">
-        <v>-111.438162</v>
+        <v>-113.337531</v>
       </c>
       <c r="O100">
-        <v>-37.88897508</v>
+        <v>-38.53476054</v>
       </c>
       <c r="P100">
-        <v>-73.54918691999998</v>
+        <v>-74.80277046</v>
       </c>
       <c r="Q100">
-        <v>-48.24918691999999</v>
+        <v>-49.50277046000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.091124525228576</v>
+        <v>8.136449050457154</v>
       </c>
       <c r="T100">
-        <v>52.72413971104849</v>
+        <v>105.448279422097</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1364470333600909</v>
+        <v>0.1350687804978677</v>
       </c>
       <c r="W100">
-        <v>0.2036257895336906</v>
+        <v>0.2039507815586028</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4013148040002673</v>
+        <v>0.3972611191113757</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2832757642475884</v>
-      </c>
-      <c r="C101">
-        <v>-446.4085332443645</v>
-      </c>
-      <c r="D101">
-        <v>269.7364667556354</v>
-      </c>
-      <c r="E101">
-        <v>636.145</v>
-      </c>
-      <c r="F101">
-        <v>797.4449999999999</v>
-      </c>
-      <c r="G101">
-        <v>81.3</v>
-      </c>
-      <c r="H101">
-        <v>644.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>100</v>
-      </c>
-      <c r="K101">
-        <v>25.3</v>
-      </c>
-      <c r="L101">
-        <v>74.7</v>
-      </c>
-      <c r="M101">
-        <v>188.037531</v>
-      </c>
-      <c r="N101">
-        <v>-113.337531</v>
-      </c>
-      <c r="O101">
-        <v>-38.53476054</v>
-      </c>
-      <c r="P101">
-        <v>-74.80277046</v>
-      </c>
-      <c r="Q101">
-        <v>-49.50277046000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.136449050457154</v>
-      </c>
-      <c r="T101">
-        <v>105.448279422097</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1350687804978677</v>
-      </c>
-      <c r="W101">
-        <v>0.2039507815586028</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3972611191113757</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
